--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>A</t>
   </si>
@@ -52,19 +52,13 @@
     <t>opening_noise_k</t>
   </si>
   <si>
-    <t>PPO_10</t>
-  </si>
-  <si>
-    <t>PPO_13</t>
-  </si>
-  <si>
     <t>PPO_14</t>
   </si>
   <si>
     <t>PPO_16</t>
   </si>
   <si>
-    <t>PPO_401a</t>
+    <t>PPO_402</t>
   </si>
   <si>
     <t>center</t>
@@ -428,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -474,45 +468,45 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>500</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>496</v>
+        <v>249</v>
       </c>
       <c r="G2">
-        <v>0.007</v>
+        <v>0.502</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.4581295258264922</v>
       </c>
       <c r="I2">
-        <v>0.01404724417776211</v>
+        <v>0.5458704741735079</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
       </c>
       <c r="C3">
         <v>500</v>
@@ -521,332 +515,66 @@
         <v>249</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G3">
-        <v>0.499</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>0.4551731554706159</v>
+        <v>0.4562170044263437</v>
       </c>
       <c r="I3">
-        <v>0.5428268445293841</v>
+        <v>0.5437829955736563</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>500</v>
       </c>
       <c r="D4">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G4">
-        <v>0.502</v>
+        <v>0.496</v>
       </c>
       <c r="H4">
-        <v>0.4582173560984033</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I4">
-        <v>0.5457826439015967</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
         <v>16</v>
-      </c>
-      <c r="C5">
-        <v>500</v>
-      </c>
-      <c r="D5">
-        <v>251</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>249</v>
-      </c>
-      <c r="G5">
-        <v>0.502</v>
-      </c>
-      <c r="H5">
-        <v>0.4581295258264922</v>
-      </c>
-      <c r="I5">
-        <v>0.5458704741735079</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>500</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>497</v>
-      </c>
-      <c r="G6">
-        <v>0.006</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0.0127760190132064</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>500</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>493</v>
-      </c>
-      <c r="G7">
-        <v>0.012</v>
-      </c>
-      <c r="H7">
-        <v>0.002858010547901262</v>
-      </c>
-      <c r="I7">
-        <v>0.02114198945209874</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8">
-        <v>500</v>
-      </c>
-      <c r="D8">
-        <v>251</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>249</v>
-      </c>
-      <c r="G8">
-        <v>0.502</v>
-      </c>
-      <c r="H8">
-        <v>0.4581295258264922</v>
-      </c>
-      <c r="I8">
-        <v>0.5458704741735079</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9">
-        <v>500</v>
-      </c>
-      <c r="D9">
-        <v>255</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>245</v>
-      </c>
-      <c r="G9">
-        <v>0.51</v>
-      </c>
-      <c r="H9">
-        <v>0.4661379499011075</v>
-      </c>
-      <c r="I9">
-        <v>0.5538620500988926</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10">
-        <v>500</v>
-      </c>
-      <c r="D10">
-        <v>249</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>249</v>
-      </c>
-      <c r="G10">
-        <v>0.5</v>
-      </c>
-      <c r="H10">
-        <v>0.4562170044263437</v>
-      </c>
-      <c r="I10">
-        <v>0.5437829955736563</v>
-      </c>
-      <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>500</v>
-      </c>
-      <c r="D11">
-        <v>253</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>246</v>
-      </c>
-      <c r="G11">
-        <v>0.507</v>
-      </c>
-      <c r="H11">
-        <v>0.4631773714989907</v>
-      </c>
-      <c r="I11">
-        <v>0.5508226285010094</v>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>A</t>
   </si>
@@ -58,7 +58,10 @@
     <t>PPO_16</t>
   </si>
   <si>
-    <t>PPO_402</t>
+    <t>PPO_403</t>
+  </si>
+  <si>
+    <t>PPO_404</t>
   </si>
   <si>
     <t>center</t>
@@ -422,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -474,69 +477,69 @@
         <v>500</v>
       </c>
       <c r="D2">
-        <v>251</v>
+        <v>495</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>0.502</v>
+        <v>0.992</v>
       </c>
       <c r="H2">
-        <v>0.4581295258264922</v>
+        <v>0.9846926427389733</v>
       </c>
       <c r="I2">
-        <v>0.5458704741735079</v>
+        <v>0.9993073572610267</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>500</v>
       </c>
       <c r="D3">
-        <v>249</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>249</v>
+        <v>488</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.023</v>
       </c>
       <c r="H3">
-        <v>0.4562170044263437</v>
+        <v>0.009994390481107169</v>
       </c>
       <c r="I3">
-        <v>0.5437829955736563</v>
+        <v>0.03600560951889283</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -544,37 +547,151 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>500</v>
       </c>
       <c r="D4">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>249</v>
+      </c>
+      <c r="G4">
+        <v>0.5</v>
+      </c>
+      <c r="H4">
+        <v>0.4562170044263437</v>
+      </c>
+      <c r="I4">
+        <v>0.5437829955736563</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>500</v>
+      </c>
+      <c r="D5">
+        <v>249</v>
+      </c>
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>252</v>
-      </c>
-      <c r="G4">
-        <v>0.496</v>
-      </c>
-      <c r="H4">
-        <v>0.4521305787473543</v>
-      </c>
-      <c r="I4">
-        <v>0.5398694212526457</v>
-      </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="F5">
+        <v>251</v>
+      </c>
+      <c r="G5">
+        <v>0.498</v>
+      </c>
+      <c r="H5">
+        <v>0.4541295258264922</v>
+      </c>
+      <c r="I5">
+        <v>0.5418704741735079</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="L4" t="s">
+      <c r="C6">
+        <v>500</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>494</v>
+      </c>
+      <c r="G6">
+        <v>0.011</v>
+      </c>
+      <c r="H6">
+        <v>0.002061110791571407</v>
+      </c>
+      <c r="I6">
+        <v>0.01993888920842859</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
         <v>16</v>
+      </c>
+      <c r="L6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>500</v>
+      </c>
+      <c r="D7">
+        <v>250</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>250</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I7">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>A</t>
   </si>
@@ -55,13 +55,10 @@
     <t>PPO_14</t>
   </si>
   <si>
-    <t>PPO_16</t>
-  </si>
-  <si>
-    <t>PPO_403</t>
-  </si>
-  <si>
     <t>PPO_404</t>
+  </si>
+  <si>
+    <t>PPO_405</t>
   </si>
   <si>
     <t>center</t>
@@ -425,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -471,37 +468,37 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>500</v>
       </c>
       <c r="D2">
-        <v>495</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>493</v>
       </c>
       <c r="G2">
-        <v>0.992</v>
+        <v>0.012</v>
       </c>
       <c r="H2">
-        <v>0.9846926427389733</v>
+        <v>0.002858010547901262</v>
       </c>
       <c r="I2">
-        <v>0.9993073572610267</v>
+        <v>0.02114198945209874</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
         <v>16</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -509,37 +506,37 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>500</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>494</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>488</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>0.023</v>
+        <v>0.988</v>
       </c>
       <c r="H3">
-        <v>0.009994390481107169</v>
+        <v>0.9784462275337606</v>
       </c>
       <c r="I3">
-        <v>0.03600560951889283</v>
+        <v>0.9975537724662393</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" t="s">
         <v>16</v>
-      </c>
-      <c r="L3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -547,151 +544,37 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>500</v>
       </c>
       <c r="D4">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>249</v>
+        <v>497</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.006</v>
       </c>
       <c r="H4">
-        <v>0.4562170044263437</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.5437829955736563</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" t="s">
         <v>16</v>
-      </c>
-      <c r="L4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5">
-        <v>500</v>
-      </c>
-      <c r="D5">
-        <v>249</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>251</v>
-      </c>
-      <c r="G5">
-        <v>0.498</v>
-      </c>
-      <c r="H5">
-        <v>0.4541295258264922</v>
-      </c>
-      <c r="I5">
-        <v>0.5418704741735079</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>500</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>494</v>
-      </c>
-      <c r="G6">
-        <v>0.011</v>
-      </c>
-      <c r="H6">
-        <v>0.002061110791571407</v>
-      </c>
-      <c r="I6">
-        <v>0.01993888920842859</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>500</v>
-      </c>
-      <c r="D7">
-        <v>250</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>250</v>
-      </c>
-      <c r="G7">
-        <v>0.5</v>
-      </c>
-      <c r="H7">
-        <v>0.4561291748584872</v>
-      </c>
-      <c r="I7">
-        <v>0.5438708251415129</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
@@ -55,10 +55,10 @@
     <t>PPO_14</t>
   </si>
   <si>
-    <t>PPO_404</t>
-  </si>
-  <si>
     <t>PPO_405</t>
+  </si>
+  <si>
+    <t>PPO_408</t>
   </si>
   <si>
     <t>center</t>
@@ -474,22 +474,22 @@
         <v>500</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>495</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>493</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>0.012</v>
+        <v>0.992</v>
       </c>
       <c r="H2">
-        <v>0.002858010547901262</v>
+        <v>0.9846926427389733</v>
       </c>
       <c r="I2">
-        <v>0.02114198945209874</v>
+        <v>0.9993073572610267</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -512,22 +512,22 @@
         <v>500</v>
       </c>
       <c r="D3">
-        <v>494</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>492</v>
       </c>
       <c r="G3">
-        <v>0.988</v>
+        <v>0.016</v>
       </c>
       <c r="H3">
-        <v>0.9784462275337606</v>
+        <v>0.004990607908314968</v>
       </c>
       <c r="I3">
-        <v>0.9975537724662393</v>
+        <v>0.02700939209168503</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -550,22 +550,22 @@
         <v>500</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>497</v>
+        <v>248</v>
       </c>
       <c r="G4">
-        <v>0.006</v>
+        <v>0.504</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.4601305787473543</v>
       </c>
       <c r="I4">
-        <v>0.0127760190132064</v>
+        <v>0.5478694212526457</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
@@ -52,13 +52,13 @@
     <t>opening_noise_k</t>
   </si>
   <si>
-    <t>PPO_14</t>
-  </si>
-  <si>
-    <t>PPO_405</t>
-  </si>
-  <si>
-    <t>PPO_408</t>
+    <t>PPO_413</t>
+  </si>
+  <si>
+    <t>PPO_507</t>
+  </si>
+  <si>
+    <t>PPO_601</t>
   </si>
   <si>
     <t>center</t>
@@ -474,22 +474,22 @@
         <v>500</v>
       </c>
       <c r="D2">
-        <v>495</v>
+        <v>250</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="G2">
-        <v>0.992</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>0.9846926427389733</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I2">
-        <v>0.9993073572610267</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -512,22 +512,22 @@
         <v>500</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="G3">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="H3">
-        <v>0.004990607908314968</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.02700939209168503</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="27">
   <si>
     <t>A</t>
   </si>
@@ -52,13 +52,43 @@
     <t>opening_noise_k</t>
   </si>
   <si>
-    <t>PPO_413</t>
+    <t>PPO_812</t>
   </si>
   <si>
-    <t>PPO_507</t>
+    <t>PPO_817</t>
   </si>
   <si>
-    <t>PPO_601</t>
+    <t>PPO_820</t>
+  </si>
+  <si>
+    <t>PPO_827</t>
+  </si>
+  <si>
+    <t>PPO_832</t>
+  </si>
+  <si>
+    <t>PPO_834</t>
+  </si>
+  <si>
+    <t>PPO_836</t>
+  </si>
+  <si>
+    <t>PPO_838</t>
+  </si>
+  <si>
+    <t>PPO_842</t>
+  </si>
+  <si>
+    <t>PPO_845</t>
+  </si>
+  <si>
+    <t>PPO_846</t>
+  </si>
+  <si>
+    <t>PPO_909</t>
+  </si>
+  <si>
+    <t>PPO_914</t>
   </si>
   <si>
     <t>center</t>
@@ -422,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -468,37 +498,37 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>500</v>
       </c>
       <c r="D2">
-        <v>250</v>
+        <v>494</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.988</v>
       </c>
       <c r="H2">
-        <v>0.4561291748584872</v>
+        <v>0.9784462275337606</v>
       </c>
       <c r="I2">
-        <v>0.5438708251415129</v>
+        <v>0.9975537724662393</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -506,7 +536,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>500</v>
@@ -515,66 +545,2916 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G3">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.0127760190132064</v>
+        <v>0.01404724417776211</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>500</v>
+      </c>
+      <c r="D4">
+        <v>249</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>250</v>
+      </c>
+      <c r="G4">
+        <v>0.499</v>
+      </c>
+      <c r="H4">
+        <v>0.4551731554706159</v>
+      </c>
+      <c r="I4">
+        <v>0.5428268445293841</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>500</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>490</v>
+      </c>
+      <c r="G5">
+        <v>0.019</v>
+      </c>
+      <c r="H5">
+        <v>0.007182857599697888</v>
+      </c>
+      <c r="I5">
+        <v>0.03081714240030211</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6">
+        <v>500</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>493</v>
+      </c>
+      <c r="G6">
+        <v>0.011</v>
+      </c>
+      <c r="H6">
+        <v>0.002502639051671845</v>
+      </c>
+      <c r="I6">
+        <v>0.01949736094832815</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>500</v>
+      </c>
+      <c r="D7">
+        <v>251</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>249</v>
+      </c>
+      <c r="G7">
+        <v>0.502</v>
+      </c>
+      <c r="H7">
+        <v>0.4581295258264922</v>
+      </c>
+      <c r="I7">
+        <v>0.5458704741735079</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>500</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>497</v>
+      </c>
+      <c r="G8">
+        <v>0.006</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.0127760190132064</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>500</v>
+      </c>
+      <c r="D9">
+        <v>249</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>251</v>
+      </c>
+      <c r="G9">
+        <v>0.498</v>
+      </c>
+      <c r="H9">
+        <v>0.4541295258264922</v>
+      </c>
+      <c r="I9">
+        <v>0.5418704741735079</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>500</v>
+      </c>
+      <c r="D10">
+        <v>250</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>250</v>
+      </c>
+      <c r="G10">
+        <v>0.5</v>
+      </c>
+      <c r="H10">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I10">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C4">
-        <v>500</v>
-      </c>
-      <c r="D4">
+      <c r="C11">
+        <v>500</v>
+      </c>
+      <c r="D11">
+        <v>7</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>492</v>
+      </c>
+      <c r="G11">
+        <v>0.015</v>
+      </c>
+      <c r="H11">
+        <v>0.004516800347703959</v>
+      </c>
+      <c r="I11">
+        <v>0.02548319965229604</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>500</v>
+      </c>
+      <c r="D12">
+        <v>495</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>0.99</v>
+      </c>
+      <c r="H12">
+        <v>0.9812698160257387</v>
+      </c>
+      <c r="I12">
+        <v>0.9987301839742613</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>500</v>
+      </c>
+      <c r="D13">
+        <v>251</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>249</v>
+      </c>
+      <c r="G13">
+        <v>0.502</v>
+      </c>
+      <c r="H13">
+        <v>0.4581295258264922</v>
+      </c>
+      <c r="I13">
+        <v>0.5458704741735079</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>500</v>
+      </c>
+      <c r="D14">
+        <v>253</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>247</v>
+      </c>
+      <c r="G14">
+        <v>0.506</v>
+      </c>
+      <c r="H14">
+        <v>0.4621323336716188</v>
+      </c>
+      <c r="I14">
+        <v>0.5498676663283812</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>500</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>496</v>
+      </c>
+      <c r="G15">
+        <v>0.007</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.01404724417776211</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>500</v>
+      </c>
+      <c r="D16">
+        <v>249</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>250</v>
+      </c>
+      <c r="G16">
+        <v>0.499</v>
+      </c>
+      <c r="H16">
+        <v>0.4551731554706159</v>
+      </c>
+      <c r="I16">
+        <v>0.5428268445293841</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>500</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>495</v>
+      </c>
+      <c r="G17">
+        <v>0.01</v>
+      </c>
+      <c r="H17">
+        <v>0.001269816025738698</v>
+      </c>
+      <c r="I17">
+        <v>0.0187301839742613</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18">
+        <v>500</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>494</v>
+      </c>
+      <c r="G18">
+        <v>0.01</v>
+      </c>
+      <c r="H18">
+        <v>0.001722469267344271</v>
+      </c>
+      <c r="I18">
+        <v>0.01827753073265573</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19">
+        <v>500</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>493</v>
+      </c>
+      <c r="G19">
+        <v>0.014</v>
+      </c>
+      <c r="H19">
+        <v>0.00369119620560452</v>
+      </c>
+      <c r="I19">
+        <v>0.02430880379439548</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
+        <v>500</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>500</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21">
+        <v>500</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>500</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>500</v>
+      </c>
+      <c r="D22">
+        <v>7</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>489</v>
+      </c>
+      <c r="G22">
+        <v>0.018</v>
+      </c>
+      <c r="H22">
+        <v>0.007014409000001933</v>
+      </c>
+      <c r="I22">
+        <v>0.02898559099999806</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23">
+        <v>500</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>500</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24">
+        <v>500</v>
+      </c>
+      <c r="D24">
+        <v>249</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>251</v>
+      </c>
+      <c r="G24">
+        <v>0.498</v>
+      </c>
+      <c r="H24">
+        <v>0.4541295258264922</v>
+      </c>
+      <c r="I24">
+        <v>0.5418704741735079</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25">
+        <v>500</v>
+      </c>
+      <c r="D25">
+        <v>250</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>250</v>
+      </c>
+      <c r="G25">
+        <v>0.5</v>
+      </c>
+      <c r="H25">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I25">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26">
+        <v>500</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>498</v>
+      </c>
+      <c r="G26">
+        <v>0.004</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0.009538159551912971</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27">
+        <v>500</v>
+      </c>
+      <c r="D27">
+        <v>7</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>493</v>
+      </c>
+      <c r="G27">
+        <v>0.014</v>
+      </c>
+      <c r="H27">
+        <v>0.003691196205604519</v>
+      </c>
+      <c r="I27">
+        <v>0.02430880379439548</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>500</v>
+      </c>
+      <c r="D28">
+        <v>9</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>491</v>
+      </c>
+      <c r="G28">
+        <v>0.018</v>
+      </c>
+      <c r="H28">
+        <v>0.006334649426270291</v>
+      </c>
+      <c r="I28">
+        <v>0.02966535057372971</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29">
+        <v>500</v>
+      </c>
+      <c r="D29">
+        <v>11</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>489</v>
+      </c>
+      <c r="G29">
+        <v>0.022</v>
+      </c>
+      <c r="H29">
+        <v>0.009129762347397428</v>
+      </c>
+      <c r="I29">
+        <v>0.03487023765260257</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30">
+        <v>500</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>499</v>
+      </c>
+      <c r="G30">
+        <v>0.002</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0.00592</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31">
+        <v>500</v>
+      </c>
+      <c r="D31">
+        <v>7</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>493</v>
+      </c>
+      <c r="G31">
+        <v>0.014</v>
+      </c>
+      <c r="H31">
+        <v>0.00369119620560452</v>
+      </c>
+      <c r="I31">
+        <v>0.02430880379439548</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32">
+        <v>500</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>497</v>
+      </c>
+      <c r="G32">
+        <v>0.005</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0.01086951637231636</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33">
+        <v>500</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>496</v>
+      </c>
+      <c r="G33">
+        <v>0.008</v>
+      </c>
+      <c r="H33">
+        <v>0.0001836026626924024</v>
+      </c>
+      <c r="I33">
+        <v>0.0158163973373076</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34">
+        <v>500</v>
+      </c>
+      <c r="D34">
+        <v>249</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>251</v>
+      </c>
+      <c r="G34">
+        <v>0.498</v>
+      </c>
+      <c r="H34">
+        <v>0.4541295258264922</v>
+      </c>
+      <c r="I34">
+        <v>0.5418704741735079</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35">
+        <v>500</v>
+      </c>
+      <c r="D35">
+        <v>249</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>251</v>
+      </c>
+      <c r="G35">
+        <v>0.498</v>
+      </c>
+      <c r="H35">
+        <v>0.4541295258264922</v>
+      </c>
+      <c r="I35">
+        <v>0.5418704741735079</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36">
+        <v>500</v>
+      </c>
+      <c r="D36">
+        <v>247</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36">
+        <v>250</v>
+      </c>
+      <c r="G36">
+        <v>0.497</v>
+      </c>
+      <c r="H36">
+        <v>0.4532617774088743</v>
+      </c>
+      <c r="I36">
+        <v>0.5407382225911257</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37">
+        <v>500</v>
+      </c>
+      <c r="D37">
+        <v>248</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37">
+        <v>250</v>
+      </c>
+      <c r="G37">
+        <v>0.498</v>
+      </c>
+      <c r="H37">
+        <v>0.4542173560984032</v>
+      </c>
+      <c r="I37">
+        <v>0.5417826439015967</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38">
+        <v>500</v>
+      </c>
+      <c r="D38">
+        <v>11</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>489</v>
+      </c>
+      <c r="G38">
+        <v>0.022</v>
+      </c>
+      <c r="H38">
+        <v>0.009129762347397428</v>
+      </c>
+      <c r="I38">
+        <v>0.03487023765260257</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39">
+        <v>500</v>
+      </c>
+      <c r="D39">
+        <v>250</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>250</v>
+      </c>
+      <c r="G39">
+        <v>0.5</v>
+      </c>
+      <c r="H39">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I39">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40">
+        <v>500</v>
+      </c>
+      <c r="D40">
+        <v>248</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
         <v>252</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>248</v>
-      </c>
-      <c r="G4">
-        <v>0.504</v>
-      </c>
-      <c r="H4">
-        <v>0.4601305787473543</v>
-      </c>
-      <c r="I4">
-        <v>0.5478694212526457</v>
-      </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="G40">
+        <v>0.496</v>
+      </c>
+      <c r="H40">
+        <v>0.4521305787473543</v>
+      </c>
+      <c r="I40">
+        <v>0.5398694212526457</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
         <v>15</v>
       </c>
-      <c r="L4" t="s">
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41">
+        <v>500</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>495</v>
+      </c>
+      <c r="G41">
+        <v>0.01</v>
+      </c>
+      <c r="H41">
+        <v>0.001269816025738698</v>
+      </c>
+      <c r="I41">
+        <v>0.0187301839742613</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="s">
+        <v>25</v>
+      </c>
+      <c r="L41" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42">
+        <v>500</v>
+      </c>
+      <c r="D42">
+        <v>249</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>251</v>
+      </c>
+      <c r="G42">
+        <v>0.498</v>
+      </c>
+      <c r="H42">
+        <v>0.4541295258264922</v>
+      </c>
+      <c r="I42">
+        <v>0.5418704741735079</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="s">
+        <v>25</v>
+      </c>
+      <c r="L42" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
         <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43">
+        <v>500</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>496</v>
+      </c>
+      <c r="G43">
+        <v>0.008</v>
+      </c>
+      <c r="H43">
+        <v>0.0001836026626924024</v>
+      </c>
+      <c r="I43">
+        <v>0.0158163973373076</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="s">
+        <v>25</v>
+      </c>
+      <c r="L43" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44">
+        <v>500</v>
+      </c>
+      <c r="D44">
+        <v>6</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44">
+        <v>492</v>
+      </c>
+      <c r="G44">
+        <v>0.014</v>
+      </c>
+      <c r="H44">
+        <v>0.004071614508040399</v>
+      </c>
+      <c r="I44">
+        <v>0.0239283854919596</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="s">
+        <v>25</v>
+      </c>
+      <c r="L44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45">
+        <v>500</v>
+      </c>
+      <c r="D45">
+        <v>250</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>250</v>
+      </c>
+      <c r="G45">
+        <v>0.5</v>
+      </c>
+      <c r="H45">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I45">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="s">
+        <v>25</v>
+      </c>
+      <c r="L45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46">
+        <v>500</v>
+      </c>
+      <c r="D46">
+        <v>249</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>251</v>
+      </c>
+      <c r="G46">
+        <v>0.498</v>
+      </c>
+      <c r="H46">
+        <v>0.4541295258264922</v>
+      </c>
+      <c r="I46">
+        <v>0.5418704741735079</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47">
+        <v>500</v>
+      </c>
+      <c r="D47">
+        <v>247</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>253</v>
+      </c>
+      <c r="G47">
+        <v>0.494</v>
+      </c>
+      <c r="H47">
+        <v>0.4501323336716188</v>
+      </c>
+      <c r="I47">
+        <v>0.5378676663283812</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="s">
+        <v>25</v>
+      </c>
+      <c r="L47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48">
+        <v>500</v>
+      </c>
+      <c r="D48">
+        <v>249</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>251</v>
+      </c>
+      <c r="G48">
+        <v>0.498</v>
+      </c>
+      <c r="H48">
+        <v>0.4541295258264922</v>
+      </c>
+      <c r="I48">
+        <v>0.5418704741735079</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="s">
+        <v>25</v>
+      </c>
+      <c r="L48" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49">
+        <v>500</v>
+      </c>
+      <c r="D49">
+        <v>494</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>6</v>
+      </c>
+      <c r="G49">
+        <v>0.988</v>
+      </c>
+      <c r="H49">
+        <v>0.9784462275337606</v>
+      </c>
+      <c r="I49">
+        <v>0.9975537724662393</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50">
+        <v>500</v>
+      </c>
+      <c r="D50">
+        <v>246</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>254</v>
+      </c>
+      <c r="G50">
+        <v>0.492</v>
+      </c>
+      <c r="H50">
+        <v>0.4481347906835411</v>
+      </c>
+      <c r="I50">
+        <v>0.5358652093164589</v>
+      </c>
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+      <c r="K50" t="s">
+        <v>25</v>
+      </c>
+      <c r="L50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51">
+        <v>500</v>
+      </c>
+      <c r="D51">
+        <v>250</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>250</v>
+      </c>
+      <c r="G51">
+        <v>0.5</v>
+      </c>
+      <c r="H51">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I51">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51" t="s">
+        <v>25</v>
+      </c>
+      <c r="L51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52">
+        <v>500</v>
+      </c>
+      <c r="D52">
+        <v>11</v>
+      </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
+      <c r="F52">
+        <v>484</v>
+      </c>
+      <c r="G52">
+        <v>0.027</v>
+      </c>
+      <c r="H52">
+        <v>0.01347212677809939</v>
+      </c>
+      <c r="I52">
+        <v>0.04052787322190061</v>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
+      </c>
+      <c r="K52" t="s">
+        <v>25</v>
+      </c>
+      <c r="L52" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53">
+        <v>500</v>
+      </c>
+      <c r="D53">
+        <v>250</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>250</v>
+      </c>
+      <c r="G53">
+        <v>0.5</v>
+      </c>
+      <c r="H53">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I53">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J53" t="b">
+        <v>1</v>
+      </c>
+      <c r="K53" t="s">
+        <v>25</v>
+      </c>
+      <c r="L53" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54">
+        <v>500</v>
+      </c>
+      <c r="D54">
+        <v>5</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>495</v>
+      </c>
+      <c r="G54">
+        <v>0.01</v>
+      </c>
+      <c r="H54">
+        <v>0.001269816025738698</v>
+      </c>
+      <c r="I54">
+        <v>0.0187301839742613</v>
+      </c>
+      <c r="J54" t="b">
+        <v>1</v>
+      </c>
+      <c r="K54" t="s">
+        <v>25</v>
+      </c>
+      <c r="L54" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55">
+        <v>500</v>
+      </c>
+      <c r="D55">
+        <v>247</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>252</v>
+      </c>
+      <c r="G55">
+        <v>0.495</v>
+      </c>
+      <c r="H55">
+        <v>0.4511752634341045</v>
+      </c>
+      <c r="I55">
+        <v>0.5388247365658955</v>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55" t="s">
+        <v>25</v>
+      </c>
+      <c r="L55" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56">
+        <v>500</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>498</v>
+      </c>
+      <c r="G56">
+        <v>0.004</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0.009538159551912971</v>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
+      </c>
+      <c r="K56" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57">
+        <v>500</v>
+      </c>
+      <c r="D57">
+        <v>6</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>494</v>
+      </c>
+      <c r="G57">
+        <v>0.012</v>
+      </c>
+      <c r="H57">
+        <v>0.002446227533760635</v>
+      </c>
+      <c r="I57">
+        <v>0.02155377246623937</v>
+      </c>
+      <c r="J57" t="b">
+        <v>1</v>
+      </c>
+      <c r="K57" t="s">
+        <v>25</v>
+      </c>
+      <c r="L57" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58">
+        <v>500</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>498</v>
+      </c>
+      <c r="G58">
+        <v>0.003</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0.007379178645730549</v>
+      </c>
+      <c r="J58" t="b">
+        <v>1</v>
+      </c>
+      <c r="K58" t="s">
+        <v>25</v>
+      </c>
+      <c r="L58" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59">
+        <v>500</v>
+      </c>
+      <c r="D59">
+        <v>250</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>250</v>
+      </c>
+      <c r="G59">
+        <v>0.5</v>
+      </c>
+      <c r="H59">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I59">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J59" t="b">
+        <v>1</v>
+      </c>
+      <c r="K59" t="s">
+        <v>25</v>
+      </c>
+      <c r="L59" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60">
+        <v>500</v>
+      </c>
+      <c r="D60">
+        <v>9</v>
+      </c>
+      <c r="E60">
+        <v>244</v>
+      </c>
+      <c r="F60">
+        <v>247</v>
+      </c>
+      <c r="G60">
+        <v>0.262</v>
+      </c>
+      <c r="H60">
+        <v>0.2385619731759944</v>
+      </c>
+      <c r="I60">
+        <v>0.2854380268240056</v>
+      </c>
+      <c r="J60" t="b">
+        <v>1</v>
+      </c>
+      <c r="K60" t="s">
+        <v>25</v>
+      </c>
+      <c r="L60" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61">
+        <v>500</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61">
+        <v>247</v>
+      </c>
+      <c r="F61">
+        <v>249</v>
+      </c>
+      <c r="G61">
+        <v>0.255</v>
+      </c>
+      <c r="H61">
+        <v>0.2323777930232925</v>
+      </c>
+      <c r="I61">
+        <v>0.2776222069767075</v>
+      </c>
+      <c r="J61" t="b">
+        <v>1</v>
+      </c>
+      <c r="K61" t="s">
+        <v>25</v>
+      </c>
+      <c r="L61" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62">
+        <v>500</v>
+      </c>
+      <c r="D62">
+        <v>245</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>255</v>
+      </c>
+      <c r="G62">
+        <v>0.49</v>
+      </c>
+      <c r="H62">
+        <v>0.4461379499011075</v>
+      </c>
+      <c r="I62">
+        <v>0.5338620500988925</v>
+      </c>
+      <c r="J62" t="b">
+        <v>1</v>
+      </c>
+      <c r="K62" t="s">
+        <v>25</v>
+      </c>
+      <c r="L62" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63">
+        <v>500</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>245</v>
+      </c>
+      <c r="F63">
+        <v>255</v>
+      </c>
+      <c r="G63">
+        <v>0.245</v>
+      </c>
+      <c r="H63">
+        <v>0.2230689749505538</v>
+      </c>
+      <c r="I63">
+        <v>0.2669310250494463</v>
+      </c>
+      <c r="J63" t="b">
+        <v>1</v>
+      </c>
+      <c r="K63" t="s">
+        <v>25</v>
+      </c>
+      <c r="L63" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64">
+        <v>500</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>495</v>
+      </c>
+      <c r="G64">
+        <v>0.01</v>
+      </c>
+      <c r="H64">
+        <v>0.001269816025738698</v>
+      </c>
+      <c r="I64">
+        <v>0.0187301839742613</v>
+      </c>
+      <c r="J64" t="b">
+        <v>1</v>
+      </c>
+      <c r="K64" t="s">
+        <v>25</v>
+      </c>
+      <c r="L64" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65">
+        <v>500</v>
+      </c>
+      <c r="D65">
+        <v>7</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>493</v>
+      </c>
+      <c r="G65">
+        <v>0.014</v>
+      </c>
+      <c r="H65">
+        <v>0.00369119620560452</v>
+      </c>
+      <c r="I65">
+        <v>0.02430880379439548</v>
+      </c>
+      <c r="J65" t="b">
+        <v>1</v>
+      </c>
+      <c r="K65" t="s">
+        <v>25</v>
+      </c>
+      <c r="L65" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66">
+        <v>500</v>
+      </c>
+      <c r="D66">
+        <v>250</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>250</v>
+      </c>
+      <c r="G66">
+        <v>0.5</v>
+      </c>
+      <c r="H66">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I66">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J66" t="b">
+        <v>1</v>
+      </c>
+      <c r="K66" t="s">
+        <v>25</v>
+      </c>
+      <c r="L66" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67">
+        <v>500</v>
+      </c>
+      <c r="D67">
+        <v>251</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>249</v>
+      </c>
+      <c r="G67">
+        <v>0.502</v>
+      </c>
+      <c r="H67">
+        <v>0.4581295258264922</v>
+      </c>
+      <c r="I67">
+        <v>0.5458704741735079</v>
+      </c>
+      <c r="J67" t="b">
+        <v>1</v>
+      </c>
+      <c r="K67" t="s">
+        <v>25</v>
+      </c>
+      <c r="L67" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68">
+        <v>500</v>
+      </c>
+      <c r="D68">
+        <v>8</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>492</v>
+      </c>
+      <c r="G68">
+        <v>0.016</v>
+      </c>
+      <c r="H68">
+        <v>0.004990607908314968</v>
+      </c>
+      <c r="I68">
+        <v>0.02700939209168503</v>
+      </c>
+      <c r="J68" t="b">
+        <v>1</v>
+      </c>
+      <c r="K68" t="s">
+        <v>25</v>
+      </c>
+      <c r="L68" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69">
+        <v>500</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="F69">
+        <v>494</v>
+      </c>
+      <c r="G69">
+        <v>0.01</v>
+      </c>
+      <c r="H69">
+        <v>0.001722469267344271</v>
+      </c>
+      <c r="I69">
+        <v>0.01827753073265573</v>
+      </c>
+      <c r="J69" t="b">
+        <v>1</v>
+      </c>
+      <c r="K69" t="s">
+        <v>25</v>
+      </c>
+      <c r="L69" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70">
+        <v>500</v>
+      </c>
+      <c r="D70">
+        <v>250</v>
+      </c>
+      <c r="E70">
+        <v>247</v>
+      </c>
+      <c r="F70">
+        <v>3</v>
+      </c>
+      <c r="G70">
+        <v>0.747</v>
+      </c>
+      <c r="H70">
+        <v>0.7245458505202776</v>
+      </c>
+      <c r="I70">
+        <v>0.7694541494797223</v>
+      </c>
+      <c r="J70" t="b">
+        <v>1</v>
+      </c>
+      <c r="K70" t="s">
+        <v>25</v>
+      </c>
+      <c r="L70" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" t="s">
+        <v>20</v>
+      </c>
+      <c r="B71" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71">
+        <v>500</v>
+      </c>
+      <c r="D71">
+        <v>498</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>0.997</v>
+      </c>
+      <c r="H71">
+        <v>0.9926208213542694</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="J71" t="b">
+        <v>1</v>
+      </c>
+      <c r="K71" t="s">
+        <v>25</v>
+      </c>
+      <c r="L71" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" t="s">
+        <v>20</v>
+      </c>
+      <c r="B72" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72">
+        <v>500</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>500</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72" t="b">
+        <v>1</v>
+      </c>
+      <c r="K72" t="s">
+        <v>25</v>
+      </c>
+      <c r="L72" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" t="s">
+        <v>20</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73">
+        <v>500</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>498</v>
+      </c>
+      <c r="G73">
+        <v>0.004</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0.009538159551912971</v>
+      </c>
+      <c r="J73" t="b">
+        <v>1</v>
+      </c>
+      <c r="K73" t="s">
+        <v>25</v>
+      </c>
+      <c r="L73" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B74" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74">
+        <v>500</v>
+      </c>
+      <c r="D74">
+        <v>249</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>251</v>
+      </c>
+      <c r="G74">
+        <v>0.498</v>
+      </c>
+      <c r="H74">
+        <v>0.4541295258264922</v>
+      </c>
+      <c r="I74">
+        <v>0.5418704741735079</v>
+      </c>
+      <c r="J74" t="b">
+        <v>1</v>
+      </c>
+      <c r="K74" t="s">
+        <v>25</v>
+      </c>
+      <c r="L74" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" t="s">
+        <v>21</v>
+      </c>
+      <c r="B75" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75">
+        <v>500</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+      <c r="E75">
+        <v>243</v>
+      </c>
+      <c r="F75">
+        <v>254</v>
+      </c>
+      <c r="G75">
+        <v>0.249</v>
+      </c>
+      <c r="H75">
+        <v>0.2265444791279456</v>
+      </c>
+      <c r="I75">
+        <v>0.2714555208720544</v>
+      </c>
+      <c r="J75" t="b">
+        <v>1</v>
+      </c>
+      <c r="K75" t="s">
+        <v>25</v>
+      </c>
+      <c r="L75" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" t="s">
+        <v>21</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76">
+        <v>500</v>
+      </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>497</v>
+      </c>
+      <c r="G76">
+        <v>0.006</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0.0127760190132064</v>
+      </c>
+      <c r="J76" t="b">
+        <v>1</v>
+      </c>
+      <c r="K76" t="s">
+        <v>25</v>
+      </c>
+      <c r="L76" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77">
+        <v>500</v>
+      </c>
+      <c r="D77">
+        <v>8</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>492</v>
+      </c>
+      <c r="G77">
+        <v>0.016</v>
+      </c>
+      <c r="H77">
+        <v>0.004990607908314968</v>
+      </c>
+      <c r="I77">
+        <v>0.02700939209168503</v>
+      </c>
+      <c r="J77" t="b">
+        <v>1</v>
+      </c>
+      <c r="K77" t="s">
+        <v>25</v>
+      </c>
+      <c r="L77" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" t="s">
+        <v>22</v>
+      </c>
+      <c r="B78" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78">
+        <v>500</v>
+      </c>
+      <c r="D78">
+        <v>3</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>497</v>
+      </c>
+      <c r="G78">
+        <v>0.006</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0.0127760190132064</v>
+      </c>
+      <c r="J78" t="b">
+        <v>1</v>
+      </c>
+      <c r="K78" t="s">
+        <v>25</v>
+      </c>
+      <c r="L78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" t="s">
+        <v>23</v>
+      </c>
+      <c r="B79" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79">
+        <v>500</v>
+      </c>
+      <c r="D79">
+        <v>499</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>0.998</v>
+      </c>
+      <c r="H79">
+        <v>0.99408</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79" t="b">
+        <v>1</v>
+      </c>
+      <c r="K79" t="s">
+        <v>25</v>
+      </c>
+      <c r="L79" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="30">
   <si>
     <t>A</t>
   </si>
@@ -55,9 +55,6 @@
     <t>PPO_812</t>
   </si>
   <si>
-    <t>PPO_817</t>
-  </si>
-  <si>
     <t>PPO_820</t>
   </si>
   <si>
@@ -67,28 +64,40 @@
     <t>PPO_832</t>
   </si>
   <si>
-    <t>PPO_834</t>
-  </si>
-  <si>
-    <t>PPO_836</t>
-  </si>
-  <si>
-    <t>PPO_838</t>
-  </si>
-  <si>
     <t>PPO_842</t>
   </si>
   <si>
-    <t>PPO_845</t>
+    <t>PPO_849</t>
   </si>
   <si>
-    <t>PPO_846</t>
+    <t>PPO_850</t>
+  </si>
+  <si>
+    <t>PPO_851</t>
+  </si>
+  <si>
+    <t>PPO_852X</t>
   </si>
   <si>
     <t>PPO_909</t>
   </si>
   <si>
     <t>PPO_914</t>
+  </si>
+  <si>
+    <t>PPO_915</t>
+  </si>
+  <si>
+    <t>PPO_918</t>
+  </si>
+  <si>
+    <t>PPO_919</t>
+  </si>
+  <si>
+    <t>SOUP_9</t>
+  </si>
+  <si>
+    <t>X_1</t>
   </si>
   <si>
     <t>center</t>
@@ -452,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -498,37 +507,37 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>500</v>
       </c>
       <c r="D2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>0.988</v>
+        <v>0.996</v>
       </c>
       <c r="H2">
-        <v>0.9784462275337606</v>
+        <v>0.990461840448087</v>
       </c>
       <c r="I2">
-        <v>0.9975537724662393</v>
+        <v>1</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -536,37 +545,37 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>500</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="G3">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.004516800347703961</v>
       </c>
       <c r="I3">
-        <v>0.01404724417776211</v>
+        <v>0.02548319965229604</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -574,37 +583,37 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>500</v>
       </c>
       <c r="D4">
-        <v>249</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>250</v>
+        <v>488</v>
       </c>
       <c r="G4">
-        <v>0.499</v>
+        <v>0.021</v>
       </c>
       <c r="H4">
-        <v>0.4551731554706159</v>
+        <v>0.008886884631612904</v>
       </c>
       <c r="I4">
-        <v>0.5428268445293841</v>
+        <v>0.0331131153683871</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -618,31 +627,31 @@
         <v>500</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>498</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>490</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>0.019</v>
+        <v>0.996</v>
       </c>
       <c r="H5">
-        <v>0.007182857599697888</v>
+        <v>0.990461840448087</v>
       </c>
       <c r="I5">
-        <v>0.03081714240030211</v>
+        <v>1</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -659,28 +668,28 @@
         <v>4</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="G6">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="H6">
-        <v>0.002502639051671845</v>
+        <v>0.0001836026626924024</v>
       </c>
       <c r="I6">
-        <v>0.01949736094832815</v>
+        <v>0.0158163973373076</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -694,31 +703,31 @@
         <v>500</v>
       </c>
       <c r="D7">
+        <v>249</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>251</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>249</v>
-      </c>
       <c r="G7">
-        <v>0.502</v>
+        <v>0.498</v>
       </c>
       <c r="H7">
-        <v>0.4581295258264922</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I7">
-        <v>0.5458704741735079</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -732,31 +741,31 @@
         <v>500</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G8">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.001269816025738698</v>
       </c>
       <c r="I8">
-        <v>0.0127760190132064</v>
+        <v>0.0187301839742613</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -770,39 +779,39 @@
         <v>500</v>
       </c>
       <c r="D9">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G9">
-        <v>0.498</v>
+        <v>0.49</v>
       </c>
       <c r="H9">
-        <v>0.4541295258264922</v>
+        <v>0.4461379499011075</v>
       </c>
       <c r="I9">
-        <v>0.5418704741735079</v>
+        <v>0.5338620500988925</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>500</v>
@@ -829,86 +838,86 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>500</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="G11">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="H11">
-        <v>0.004516800347703959</v>
+        <v>0.001269816025738694</v>
       </c>
       <c r="I11">
-        <v>0.02548319965229604</v>
+        <v>0.01873018397426131</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>500</v>
       </c>
       <c r="D12">
-        <v>495</v>
+        <v>251</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>249</v>
       </c>
       <c r="G12">
-        <v>0.99</v>
+        <v>0.502</v>
       </c>
       <c r="H12">
-        <v>0.9812698160257387</v>
+        <v>0.4581295258264922</v>
       </c>
       <c r="I12">
-        <v>0.9987301839742613</v>
+        <v>0.5458704741735079</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -916,37 +925,37 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>500</v>
       </c>
       <c r="D13">
-        <v>251</v>
+        <v>7</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>249</v>
+        <v>489</v>
       </c>
       <c r="G13">
-        <v>0.502</v>
+        <v>0.018</v>
       </c>
       <c r="H13">
-        <v>0.4581295258264922</v>
+        <v>0.007014409000001933</v>
       </c>
       <c r="I13">
-        <v>0.5458704741735079</v>
+        <v>0.02898559099999806</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -954,37 +963,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C14">
         <v>500</v>
       </c>
       <c r="D14">
-        <v>253</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>247</v>
+        <v>499</v>
       </c>
       <c r="G14">
-        <v>0.506</v>
+        <v>0.002</v>
       </c>
       <c r="H14">
-        <v>0.4621323336716188</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0.5498676663283812</v>
+        <v>0.00592</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -992,37 +1001,37 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C15">
         <v>500</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>496</v>
+        <v>250</v>
       </c>
       <c r="G15">
-        <v>0.007</v>
+        <v>0.5</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I15">
-        <v>0.01404724417776211</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1030,37 +1039,37 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16">
         <v>500</v>
       </c>
       <c r="D16">
-        <v>249</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>250</v>
+        <v>488</v>
       </c>
       <c r="G16">
-        <v>0.499</v>
+        <v>0.024</v>
       </c>
       <c r="H16">
-        <v>0.4551731554706159</v>
+        <v>0.01057122713419567</v>
       </c>
       <c r="I16">
-        <v>0.5428268445293841</v>
+        <v>0.03742877286580433</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1068,37 +1077,37 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17">
         <v>500</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G17">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="H17">
-        <v>0.001269816025738698</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0.0187301839742613</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L17" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1106,37 +1115,37 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C18">
         <v>500</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>250</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>494</v>
+        <v>250</v>
       </c>
       <c r="G18">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="H18">
-        <v>0.001722469267344271</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I18">
-        <v>0.01827753073265573</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1144,37 +1153,37 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19">
         <v>500</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>252</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>493</v>
+        <v>248</v>
       </c>
       <c r="G19">
-        <v>0.014</v>
+        <v>0.504</v>
       </c>
       <c r="H19">
-        <v>0.00369119620560452</v>
+        <v>0.4601305787473543</v>
       </c>
       <c r="I19">
-        <v>0.02430880379439548</v>
+        <v>0.5478694212526457</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1182,37 +1191,37 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20">
         <v>500</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L20" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1220,7 +1229,7 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21">
         <v>500</v>
@@ -1229,218 +1238,218 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>0.00296</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C22">
         <v>500</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="G22">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="H22">
-        <v>0.007014409000001933</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>0.02898559099999806</v>
+        <v>0.01086951637231636</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C23">
         <v>500</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>500</v>
+        <v>255</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>0.4461379499011075</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>0.5338620500988925</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C24">
         <v>500</v>
       </c>
       <c r="D24">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G24">
-        <v>0.498</v>
+        <v>0.494</v>
       </c>
       <c r="H24">
-        <v>0.4541295258264922</v>
+        <v>0.4501323336716188</v>
       </c>
       <c r="I24">
-        <v>0.5418704741735079</v>
+        <v>0.5378676663283812</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L24" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C25">
         <v>500</v>
       </c>
       <c r="D25">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>250</v>
+        <v>498</v>
       </c>
       <c r="G25">
-        <v>0.5</v>
+        <v>0.004</v>
       </c>
       <c r="H25">
-        <v>0.4561291748584872</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>0.5438708251415129</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C26">
         <v>500</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="G26">
-        <v>0.004</v>
+        <v>0.016</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>0.004990607908314968</v>
       </c>
       <c r="I26">
-        <v>0.009538159551912971</v>
+        <v>0.02700939209168503</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L26" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1448,37 +1457,37 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C27">
         <v>500</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="G27">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="H27">
-        <v>0.003691196205604519</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>0.02430880379439548</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1486,37 +1495,37 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>500</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>250</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>491</v>
+        <v>250</v>
       </c>
       <c r="G28">
-        <v>0.018</v>
+        <v>0.5</v>
       </c>
       <c r="H28">
-        <v>0.006334649426270291</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I28">
-        <v>0.02966535057372971</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L28" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1524,37 +1533,37 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>500</v>
       </c>
       <c r="D29">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G29">
-        <v>0.022</v>
+        <v>0.016</v>
       </c>
       <c r="H29">
-        <v>0.009129762347397428</v>
+        <v>0.004990607908314968</v>
       </c>
       <c r="I29">
-        <v>0.03487023765260257</v>
+        <v>0.02700939209168503</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L29" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1562,37 +1571,37 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C30">
         <v>500</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>499</v>
+        <v>251</v>
       </c>
       <c r="G30">
-        <v>0.002</v>
+        <v>0.497</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>0.4531738581138466</v>
       </c>
       <c r="I30">
-        <v>0.00592</v>
+        <v>0.5408261418861534</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1600,37 +1609,37 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C31">
         <v>500</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>250</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>493</v>
+        <v>250</v>
       </c>
       <c r="G31">
-        <v>0.014</v>
+        <v>0.5</v>
       </c>
       <c r="H31">
-        <v>0.00369119620560452</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I31">
-        <v>0.02430880379439548</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1638,197 +1647,197 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C32">
         <v>500</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="G32">
-        <v>0.005</v>
+        <v>0.016</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>0.004990607908314968</v>
       </c>
       <c r="I32">
-        <v>0.01086951637231636</v>
+        <v>0.02700939209168503</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C33">
         <v>500</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="G33">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="H33">
-        <v>0.0001836026626924024</v>
+        <v>0.00369119620560452</v>
       </c>
       <c r="I33">
-        <v>0.0158163973373076</v>
+        <v>0.02430880379439548</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C34">
         <v>500</v>
       </c>
       <c r="D34">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G34">
-        <v>0.498</v>
+        <v>0.494</v>
       </c>
       <c r="H34">
-        <v>0.4541295258264922</v>
+        <v>0.4501323336716188</v>
       </c>
       <c r="I34">
-        <v>0.5418704741735079</v>
+        <v>0.5378676663283812</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C35">
         <v>500</v>
       </c>
       <c r="D35">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G35">
-        <v>0.498</v>
+        <v>0.5</v>
       </c>
       <c r="H35">
-        <v>0.4541295258264922</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I35">
-        <v>0.5418704741735079</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L35" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C36">
         <v>500</v>
       </c>
       <c r="D36">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G36">
-        <v>0.497</v>
+        <v>0.496</v>
       </c>
       <c r="H36">
-        <v>0.4532617774088743</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I36">
-        <v>0.5407382225911257</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B37" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C37">
         <v>500</v>
@@ -1837,104 +1846,104 @@
         <v>248</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G37">
-        <v>0.498</v>
+        <v>0.496</v>
       </c>
       <c r="H37">
-        <v>0.4542173560984032</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I37">
-        <v>0.5417826439015967</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L37" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C38">
         <v>500</v>
       </c>
       <c r="D38">
-        <v>11</v>
+        <v>249</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>489</v>
+        <v>250</v>
       </c>
       <c r="G38">
-        <v>0.022</v>
+        <v>0.499</v>
       </c>
       <c r="H38">
-        <v>0.009129762347397428</v>
+        <v>0.4551731554706159</v>
       </c>
       <c r="I38">
-        <v>0.03487023765260257</v>
+        <v>0.5428268445293841</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C39">
         <v>500</v>
       </c>
       <c r="D39">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>250</v>
+        <v>494</v>
       </c>
       <c r="G39">
-        <v>0.5</v>
+        <v>0.012</v>
       </c>
       <c r="H39">
-        <v>0.4561291748584872</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I39">
-        <v>0.5438708251415129</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L39" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -1942,37 +1951,37 @@
         <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C40">
         <v>500</v>
       </c>
       <c r="D40">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G40">
-        <v>0.496</v>
+        <v>0.493</v>
       </c>
       <c r="H40">
-        <v>0.4521305787473543</v>
+        <v>0.4491773714989907</v>
       </c>
       <c r="I40">
-        <v>0.5398694212526457</v>
+        <v>0.5368226285010094</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L40" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -1980,37 +1989,37 @@
         <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C41">
         <v>500</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>244</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41">
-        <v>495</v>
+        <v>254</v>
       </c>
       <c r="G41">
-        <v>0.01</v>
+        <v>0.49</v>
       </c>
       <c r="H41">
-        <v>0.001269816025738698</v>
+        <v>0.4462257970754079</v>
       </c>
       <c r="I41">
-        <v>0.0187301839742613</v>
+        <v>0.5337742029245921</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L41" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2018,303 +2027,303 @@
         <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C42">
         <v>500</v>
       </c>
       <c r="D42">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G42">
-        <v>0.498</v>
+        <v>0.5</v>
       </c>
       <c r="H42">
-        <v>0.4541295258264922</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I42">
-        <v>0.5418704741735079</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L42" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C43">
         <v>500</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>248</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>496</v>
+        <v>252</v>
       </c>
       <c r="G43">
-        <v>0.008</v>
+        <v>0.496</v>
       </c>
       <c r="H43">
-        <v>0.0001836026626924024</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I43">
-        <v>0.0158163973373076</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L43" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C44">
         <v>500</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>249</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>492</v>
+        <v>251</v>
       </c>
       <c r="G44">
-        <v>0.014</v>
+        <v>0.498</v>
       </c>
       <c r="H44">
-        <v>0.004071614508040399</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I44">
-        <v>0.0239283854919596</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L44" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C45">
         <v>500</v>
       </c>
       <c r="D45">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45">
-        <v>250</v>
+        <v>499</v>
       </c>
       <c r="G45">
-        <v>0.5</v>
+        <v>0.002</v>
       </c>
       <c r="H45">
-        <v>0.4561291748584872</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>0.5438708251415129</v>
+        <v>0.00592</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L45" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C46">
         <v>500</v>
       </c>
       <c r="D46">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G46">
-        <v>0.498</v>
+        <v>0.494</v>
       </c>
       <c r="H46">
-        <v>0.4541295258264922</v>
+        <v>0.4501323336716188</v>
       </c>
       <c r="I46">
-        <v>0.5418704741735079</v>
+        <v>0.5378676663283812</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C47">
         <v>500</v>
       </c>
       <c r="D47">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G47">
-        <v>0.494</v>
+        <v>0.498</v>
       </c>
       <c r="H47">
-        <v>0.4501323336716188</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I47">
-        <v>0.5378676663283812</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L47" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C48">
         <v>500</v>
       </c>
       <c r="D48">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G48">
-        <v>0.498</v>
+        <v>0.494</v>
       </c>
       <c r="H48">
-        <v>0.4541295258264922</v>
+        <v>0.4501323336716188</v>
       </c>
       <c r="I48">
-        <v>0.5418704741735079</v>
+        <v>0.5378676663283812</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L48" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B49" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C49">
         <v>500</v>
       </c>
       <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
         <v>494</v>
       </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>6</v>
-      </c>
       <c r="G49">
-        <v>0.988</v>
+        <v>0.011</v>
       </c>
       <c r="H49">
-        <v>0.9784462275337606</v>
+        <v>0.002061110791571409</v>
       </c>
       <c r="I49">
-        <v>0.9975537724662393</v>
+        <v>0.01993888920842859</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L49" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2322,37 +2331,37 @@
         <v>16</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C50">
         <v>500</v>
       </c>
       <c r="D50">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="F50">
-        <v>254</v>
+        <v>9</v>
       </c>
       <c r="G50">
-        <v>0.492</v>
+        <v>0.739</v>
       </c>
       <c r="H50">
-        <v>0.4481347906835411</v>
+        <v>0.7155581961202155</v>
       </c>
       <c r="I50">
-        <v>0.5358652093164589</v>
+        <v>0.7624418038797844</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2360,121 +2369,121 @@
         <v>16</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C51">
         <v>500</v>
       </c>
       <c r="D51">
-        <v>250</v>
+        <v>495</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="G51">
-        <v>0.5</v>
+        <v>0.99</v>
       </c>
       <c r="H51">
-        <v>0.4561291748584872</v>
+        <v>0.9812698160257387</v>
       </c>
       <c r="I51">
-        <v>0.5438708251415129</v>
+        <v>0.9987301839742613</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C52">
         <v>500</v>
       </c>
       <c r="D52">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E52">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="G52">
-        <v>0.027</v>
+        <v>0.008</v>
       </c>
       <c r="H52">
-        <v>0.01347212677809939</v>
+        <v>0.0001836026626924024</v>
       </c>
       <c r="I52">
-        <v>0.04052787322190061</v>
+        <v>0.0158163973373076</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L52" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B53" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C53">
         <v>500</v>
       </c>
       <c r="D53">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F53">
-        <v>250</v>
+        <v>490</v>
       </c>
       <c r="G53">
-        <v>0.5</v>
+        <v>0.016</v>
       </c>
       <c r="H53">
-        <v>0.4561291748584872</v>
+        <v>0.00571362455285248</v>
       </c>
       <c r="I53">
-        <v>0.5438708251415129</v>
+        <v>0.02628637544714752</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L53" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B54" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C54">
         <v>500</v>
@@ -2501,18 +2510,18 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L54" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B55" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C55">
         <v>500</v>
@@ -2521,720 +2530,720 @@
         <v>247</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G55">
-        <v>0.495</v>
+        <v>0.494</v>
       </c>
       <c r="H55">
-        <v>0.4511752634341045</v>
+        <v>0.4501323336716188</v>
       </c>
       <c r="I55">
-        <v>0.5388247365658955</v>
+        <v>0.5378676663283812</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L55" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C56">
         <v>500</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>493</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>498</v>
+        <v>7</v>
       </c>
       <c r="G56">
-        <v>0.004</v>
+        <v>0.986</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>0.9756911962056045</v>
       </c>
       <c r="I56">
-        <v>0.009538159551912971</v>
+        <v>0.9963088037943955</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L56" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C57">
         <v>500</v>
       </c>
       <c r="D57">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
       <c r="F57">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G57">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="H57">
-        <v>0.002446227533760635</v>
+        <v>0.004990607908314968</v>
       </c>
       <c r="I57">
-        <v>0.02155377246623937</v>
+        <v>0.02700939209168503</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L57" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C58">
         <v>500</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>496</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>498</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>0.003</v>
+        <v>0.992</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>0.9841836026626924</v>
       </c>
       <c r="I58">
-        <v>0.007379178645730549</v>
+        <v>0.9998163973373075</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L58" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C59">
         <v>500</v>
       </c>
       <c r="D59">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E59">
         <v>0</v>
       </c>
       <c r="F59">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G59">
-        <v>0.5</v>
+        <v>0.496</v>
       </c>
       <c r="H59">
-        <v>0.4561291748584872</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I59">
-        <v>0.5438708251415129</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L59" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C60">
         <v>500</v>
       </c>
       <c r="D60">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E60">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>247</v>
+        <v>494</v>
       </c>
       <c r="G60">
-        <v>0.262</v>
+        <v>0.012</v>
       </c>
       <c r="H60">
-        <v>0.2385619731759944</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I60">
-        <v>0.2854380268240056</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C61">
         <v>500</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>249</v>
       </c>
       <c r="E61">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G61">
-        <v>0.255</v>
+        <v>0.498</v>
       </c>
       <c r="H61">
-        <v>0.2323777930232925</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I61">
-        <v>0.2776222069767075</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L61" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C62">
         <v>500</v>
       </c>
       <c r="D62">
-        <v>245</v>
+        <v>492</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>255</v>
+        <v>6</v>
       </c>
       <c r="G62">
-        <v>0.49</v>
+        <v>0.986</v>
       </c>
       <c r="H62">
-        <v>0.4461379499011075</v>
+        <v>0.9760716145080404</v>
       </c>
       <c r="I62">
-        <v>0.5338620500988925</v>
+        <v>0.9959283854919596</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L62" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C63">
         <v>500</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>255</v>
+        <v>497</v>
       </c>
       <c r="G63">
-        <v>0.245</v>
+        <v>0.006</v>
       </c>
       <c r="H63">
-        <v>0.2230689749505538</v>
+        <v>0</v>
       </c>
       <c r="I63">
-        <v>0.2669310250494463</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
+        <v>17</v>
+      </c>
+      <c r="B64" t="s">
         <v>18</v>
       </c>
-      <c r="B64" t="s">
-        <v>24</v>
-      </c>
       <c r="C64">
         <v>500</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>252</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="F64">
-        <v>495</v>
+        <v>248</v>
       </c>
       <c r="G64">
-        <v>0.01</v>
+        <v>0.504</v>
       </c>
       <c r="H64">
-        <v>0.001269816025738698</v>
+        <v>0.4601305787473543</v>
       </c>
       <c r="I64">
-        <v>0.0187301839742613</v>
+        <v>0.5478694212526457</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
+        <v>17</v>
+      </c>
+      <c r="B65" t="s">
         <v>19</v>
       </c>
-      <c r="B65" t="s">
-        <v>20</v>
-      </c>
       <c r="C65">
         <v>500</v>
       </c>
       <c r="D65">
-        <v>7</v>
+        <v>496</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>493</v>
+        <v>4</v>
       </c>
       <c r="G65">
-        <v>0.014</v>
+        <v>0.992</v>
       </c>
       <c r="H65">
-        <v>0.00369119620560452</v>
+        <v>0.9841836026626924</v>
       </c>
       <c r="I65">
-        <v>0.02430880379439548</v>
+        <v>0.9998163973373075</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L65" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C66">
         <v>500</v>
       </c>
       <c r="D66">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E66">
         <v>0</v>
       </c>
       <c r="F66">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G66">
-        <v>0.5</v>
+        <v>0.504</v>
       </c>
       <c r="H66">
-        <v>0.4561291748584872</v>
+        <v>0.4601305787473543</v>
       </c>
       <c r="I66">
-        <v>0.5438708251415129</v>
+        <v>0.5478694212526457</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L66" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C67">
         <v>500</v>
       </c>
       <c r="D67">
-        <v>251</v>
+        <v>7</v>
       </c>
       <c r="E67">
         <v>0</v>
       </c>
       <c r="F67">
-        <v>249</v>
+        <v>493</v>
       </c>
       <c r="G67">
-        <v>0.502</v>
+        <v>0.014</v>
       </c>
       <c r="H67">
-        <v>0.4581295258264922</v>
+        <v>0.00369119620560452</v>
       </c>
       <c r="I67">
-        <v>0.5458704741735079</v>
+        <v>0.02430880379439548</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L67" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C68">
         <v>500</v>
       </c>
       <c r="D68">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E68">
         <v>0</v>
       </c>
       <c r="F68">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G68">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="H68">
-        <v>0.004990607908314968</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I68">
-        <v>0.02700939209168503</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L68" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C69">
         <v>500</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>248</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69">
-        <v>494</v>
+        <v>252</v>
       </c>
       <c r="G69">
-        <v>0.01</v>
+        <v>0.496</v>
       </c>
       <c r="H69">
-        <v>0.001722469267344271</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I69">
-        <v>0.01827753073265573</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L69" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C70">
         <v>500</v>
       </c>
       <c r="D70">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E70">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="G70">
-        <v>0.747</v>
+        <v>0.496</v>
       </c>
       <c r="H70">
-        <v>0.7245458505202776</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I70">
-        <v>0.7694541494797223</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L70" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C71">
         <v>500</v>
       </c>
       <c r="D71">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G71">
-        <v>0.997</v>
+        <v>0.992</v>
       </c>
       <c r="H71">
-        <v>0.9926208213542694</v>
+        <v>0.9841836026626924</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>0.9998163973373075</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L71" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C72">
         <v>500</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>0.003256725293618782</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>0.02274327470638122</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L72" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C73">
         <v>500</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>252</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
-        <v>498</v>
+        <v>248</v>
       </c>
       <c r="G73">
-        <v>0.004</v>
+        <v>0.504</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>0.4601305787473543</v>
       </c>
       <c r="I73">
-        <v>0.009538159551912971</v>
+        <v>0.5478694212526457</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L73" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C74">
         <v>500</v>
@@ -3243,74 +3252,74 @@
         <v>249</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="F74">
-        <v>251</v>
+        <v>5</v>
       </c>
       <c r="G74">
-        <v>0.498</v>
+        <v>0.744</v>
       </c>
       <c r="H74">
-        <v>0.4541295258264922</v>
+        <v>0.721210130296067</v>
       </c>
       <c r="I74">
-        <v>0.5418704741735079</v>
+        <v>0.766789869703933</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L74" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
+        <v>18</v>
+      </c>
+      <c r="B75" t="s">
         <v>21</v>
       </c>
-      <c r="B75" t="s">
-        <v>23</v>
-      </c>
       <c r="C75">
         <v>500</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F75">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G75">
-        <v>0.249</v>
+        <v>0.248</v>
       </c>
       <c r="H75">
-        <v>0.2265444791279456</v>
+        <v>0.2258904968971505</v>
       </c>
       <c r="I75">
-        <v>0.2714555208720544</v>
+        <v>0.2701095031028495</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L75" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C76">
         <v>500</v>
@@ -3337,15 +3346,15 @@
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L76" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B77" t="s">
         <v>23</v>
@@ -3354,36 +3363,36 @@
         <v>500</v>
       </c>
       <c r="D77">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="F77">
-        <v>492</v>
+        <v>253</v>
       </c>
       <c r="G77">
-        <v>0.016</v>
+        <v>0.25</v>
       </c>
       <c r="H77">
-        <v>0.004990607908314968</v>
+        <v>0.2275443077097929</v>
       </c>
       <c r="I77">
-        <v>0.02700939209168503</v>
+        <v>0.2724556922902071</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L77" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B78" t="s">
         <v>24</v>
@@ -3392,69 +3401,1665 @@
         <v>500</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>497</v>
+        <v>250</v>
       </c>
       <c r="G78">
-        <v>0.006</v>
+        <v>0.5</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I78">
-        <v>0.0127760190132064</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L78" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
+        <v>18</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79">
+        <v>500</v>
+      </c>
+      <c r="D79">
+        <v>249</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>251</v>
+      </c>
+      <c r="G79">
+        <v>0.498</v>
+      </c>
+      <c r="H79">
+        <v>0.4541295258264922</v>
+      </c>
+      <c r="I79">
+        <v>0.5418704741735079</v>
+      </c>
+      <c r="J79" t="b">
+        <v>1</v>
+      </c>
+      <c r="K79" t="s">
+        <v>28</v>
+      </c>
+      <c r="L79" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" t="s">
+        <v>18</v>
+      </c>
+      <c r="B80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80">
+        <v>500</v>
+      </c>
+      <c r="D80">
+        <v>3</v>
+      </c>
+      <c r="E80">
+        <v>244</v>
+      </c>
+      <c r="F80">
+        <v>253</v>
+      </c>
+      <c r="G80">
+        <v>0.25</v>
+      </c>
+      <c r="H80">
+        <v>0.2275443077097929</v>
+      </c>
+      <c r="I80">
+        <v>0.2724556922902071</v>
+      </c>
+      <c r="J80" t="b">
+        <v>1</v>
+      </c>
+      <c r="K80" t="s">
+        <v>28</v>
+      </c>
+      <c r="L80" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" t="s">
+        <v>18</v>
+      </c>
+      <c r="B81" t="s">
+        <v>27</v>
+      </c>
+      <c r="C81">
+        <v>500</v>
+      </c>
+      <c r="D81">
+        <v>499</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>0.998</v>
+      </c>
+      <c r="H81">
+        <v>0.99408</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81" t="b">
+        <v>1</v>
+      </c>
+      <c r="K81" t="s">
+        <v>28</v>
+      </c>
+      <c r="L81" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82">
+        <v>500</v>
+      </c>
+      <c r="D82">
+        <v>5</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+      <c r="F82">
+        <v>493</v>
+      </c>
+      <c r="G82">
+        <v>0.012</v>
+      </c>
+      <c r="H82">
+        <v>0.002858010547901262</v>
+      </c>
+      <c r="I82">
+        <v>0.02114198945209874</v>
+      </c>
+      <c r="J82" t="b">
+        <v>1</v>
+      </c>
+      <c r="K82" t="s">
+        <v>28</v>
+      </c>
+      <c r="L82" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83">
+        <v>500</v>
+      </c>
+      <c r="D83">
+        <v>251</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>249</v>
+      </c>
+      <c r="G83">
+        <v>0.502</v>
+      </c>
+      <c r="H83">
+        <v>0.4581295258264922</v>
+      </c>
+      <c r="I83">
+        <v>0.5458704741735079</v>
+      </c>
+      <c r="J83" t="b">
+        <v>1</v>
+      </c>
+      <c r="K83" t="s">
+        <v>28</v>
+      </c>
+      <c r="L83" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" t="s">
+        <v>19</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84">
+        <v>500</v>
+      </c>
+      <c r="D84">
+        <v>250</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>250</v>
+      </c>
+      <c r="G84">
+        <v>0.5</v>
+      </c>
+      <c r="H84">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I84">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J84" t="b">
+        <v>1</v>
+      </c>
+      <c r="K84" t="s">
+        <v>28</v>
+      </c>
+      <c r="L84" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85">
+        <v>500</v>
+      </c>
+      <c r="D85">
+        <v>250</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>249</v>
+      </c>
+      <c r="G85">
+        <v>0.501</v>
+      </c>
+      <c r="H85">
+        <v>0.4571731554706159</v>
+      </c>
+      <c r="I85">
+        <v>0.5448268445293841</v>
+      </c>
+      <c r="J85" t="b">
+        <v>1</v>
+      </c>
+      <c r="K85" t="s">
+        <v>28</v>
+      </c>
+      <c r="L85" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86">
+        <v>500</v>
+      </c>
+      <c r="D86">
+        <v>494</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>6</v>
+      </c>
+      <c r="G86">
+        <v>0.988</v>
+      </c>
+      <c r="H86">
+        <v>0.9784462275337606</v>
+      </c>
+      <c r="I86">
+        <v>0.9975537724662393</v>
+      </c>
+      <c r="J86" t="b">
+        <v>1</v>
+      </c>
+      <c r="K86" t="s">
+        <v>28</v>
+      </c>
+      <c r="L86" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" t="s">
+        <v>21</v>
+      </c>
+      <c r="C87">
+        <v>500</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>499</v>
+      </c>
+      <c r="G87">
+        <v>0.002</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0.00592</v>
+      </c>
+      <c r="J87" t="b">
+        <v>1</v>
+      </c>
+      <c r="K87" t="s">
+        <v>28</v>
+      </c>
+      <c r="L87" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88" t="s">
+        <v>22</v>
+      </c>
+      <c r="C88">
+        <v>500</v>
+      </c>
+      <c r="D88">
+        <v>248</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>252</v>
+      </c>
+      <c r="G88">
+        <v>0.496</v>
+      </c>
+      <c r="H88">
+        <v>0.4521305787473543</v>
+      </c>
+      <c r="I88">
+        <v>0.5398694212526457</v>
+      </c>
+      <c r="J88" t="b">
+        <v>1</v>
+      </c>
+      <c r="K88" t="s">
+        <v>28</v>
+      </c>
+      <c r="L88" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" t="s">
+        <v>19</v>
+      </c>
+      <c r="B89" t="s">
         <v>23</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C89">
+        <v>500</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>498</v>
+      </c>
+      <c r="G89">
+        <v>0.003</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0.007379178645730549</v>
+      </c>
+      <c r="J89" t="b">
+        <v>1</v>
+      </c>
+      <c r="K89" t="s">
+        <v>28</v>
+      </c>
+      <c r="L89" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" t="s">
+        <v>19</v>
+      </c>
+      <c r="B90" t="s">
         <v>24</v>
       </c>
-      <c r="C79">
-        <v>500</v>
-      </c>
-      <c r="D79">
+      <c r="C90">
+        <v>500</v>
+      </c>
+      <c r="D90">
+        <v>3</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>497</v>
+      </c>
+      <c r="G90">
+        <v>0.006</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0.0127760190132064</v>
+      </c>
+      <c r="J90" t="b">
+        <v>1</v>
+      </c>
+      <c r="K90" t="s">
+        <v>28</v>
+      </c>
+      <c r="L90" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" t="s">
+        <v>19</v>
+      </c>
+      <c r="B91" t="s">
+        <v>25</v>
+      </c>
+      <c r="C91">
+        <v>500</v>
+      </c>
+      <c r="D91">
+        <v>245</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>255</v>
+      </c>
+      <c r="G91">
+        <v>0.49</v>
+      </c>
+      <c r="H91">
+        <v>0.4461379499011075</v>
+      </c>
+      <c r="I91">
+        <v>0.5338620500988925</v>
+      </c>
+      <c r="J91" t="b">
+        <v>1</v>
+      </c>
+      <c r="K91" t="s">
+        <v>28</v>
+      </c>
+      <c r="L91" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" t="s">
+        <v>19</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92">
+        <v>500</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
         <v>499</v>
       </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-      <c r="F79">
-        <v>1</v>
-      </c>
-      <c r="G79">
-        <v>0.998</v>
-      </c>
-      <c r="H79">
-        <v>0.99408</v>
-      </c>
-      <c r="I79">
-        <v>1</v>
-      </c>
-      <c r="J79" t="b">
-        <v>1</v>
-      </c>
-      <c r="K79" t="s">
+      <c r="G92">
+        <v>0.002</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0.00592</v>
+      </c>
+      <c r="J92" t="b">
+        <v>1</v>
+      </c>
+      <c r="K92" t="s">
+        <v>28</v>
+      </c>
+      <c r="L92" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" t="s">
+        <v>19</v>
+      </c>
+      <c r="B93" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93">
+        <v>500</v>
+      </c>
+      <c r="D93">
+        <v>3</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93">
+        <v>496</v>
+      </c>
+      <c r="G93">
+        <v>0.007</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0.01404724417776211</v>
+      </c>
+      <c r="J93" t="b">
+        <v>1</v>
+      </c>
+      <c r="K93" t="s">
+        <v>28</v>
+      </c>
+      <c r="L93" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" t="s">
+        <v>20</v>
+      </c>
+      <c r="B94" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94">
+        <v>500</v>
+      </c>
+      <c r="D94">
+        <v>7</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>493</v>
+      </c>
+      <c r="G94">
+        <v>0.014</v>
+      </c>
+      <c r="H94">
+        <v>0.00369119620560452</v>
+      </c>
+      <c r="I94">
+        <v>0.02430880379439548</v>
+      </c>
+      <c r="J94" t="b">
+        <v>1</v>
+      </c>
+      <c r="K94" t="s">
+        <v>28</v>
+      </c>
+      <c r="L94" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" t="s">
+        <v>20</v>
+      </c>
+      <c r="B95" t="s">
+        <v>22</v>
+      </c>
+      <c r="C95">
+        <v>500</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <v>498</v>
+      </c>
+      <c r="G95">
+        <v>0.003</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0.007379178645730549</v>
+      </c>
+      <c r="J95" t="b">
+        <v>1</v>
+      </c>
+      <c r="K95" t="s">
+        <v>28</v>
+      </c>
+      <c r="L95" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" t="s">
+        <v>20</v>
+      </c>
+      <c r="B96" t="s">
+        <v>23</v>
+      </c>
+      <c r="C96">
+        <v>500</v>
+      </c>
+      <c r="D96">
+        <v>4</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>496</v>
+      </c>
+      <c r="G96">
+        <v>0.008</v>
+      </c>
+      <c r="H96">
+        <v>0.0001836026626924024</v>
+      </c>
+      <c r="I96">
+        <v>0.0158163973373076</v>
+      </c>
+      <c r="J96" t="b">
+        <v>1</v>
+      </c>
+      <c r="K96" t="s">
+        <v>28</v>
+      </c>
+      <c r="L96" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" t="s">
+        <v>20</v>
+      </c>
+      <c r="B97" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97">
+        <v>500</v>
+      </c>
+      <c r="D97">
+        <v>246</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>254</v>
+      </c>
+      <c r="G97">
+        <v>0.492</v>
+      </c>
+      <c r="H97">
+        <v>0.4481347906835411</v>
+      </c>
+      <c r="I97">
+        <v>0.5358652093164589</v>
+      </c>
+      <c r="J97" t="b">
+        <v>1</v>
+      </c>
+      <c r="K97" t="s">
+        <v>28</v>
+      </c>
+      <c r="L97" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" t="s">
+        <v>20</v>
+      </c>
+      <c r="B98" t="s">
         <v>25</v>
       </c>
-      <c r="L79" t="s">
+      <c r="C98">
+        <v>500</v>
+      </c>
+      <c r="D98">
+        <v>247</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>253</v>
+      </c>
+      <c r="G98">
+        <v>0.494</v>
+      </c>
+      <c r="H98">
+        <v>0.4501323336716188</v>
+      </c>
+      <c r="I98">
+        <v>0.5378676663283812</v>
+      </c>
+      <c r="J98" t="b">
+        <v>1</v>
+      </c>
+      <c r="K98" t="s">
+        <v>28</v>
+      </c>
+      <c r="L98" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" t="s">
+        <v>20</v>
+      </c>
+      <c r="B99" t="s">
         <v>26</v>
+      </c>
+      <c r="C99">
+        <v>500</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="F99">
+        <v>497</v>
+      </c>
+      <c r="G99">
+        <v>0.005</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0.01086951637231636</v>
+      </c>
+      <c r="J99" t="b">
+        <v>1</v>
+      </c>
+      <c r="K99" t="s">
+        <v>28</v>
+      </c>
+      <c r="L99" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" t="s">
+        <v>20</v>
+      </c>
+      <c r="B100" t="s">
+        <v>27</v>
+      </c>
+      <c r="C100">
+        <v>500</v>
+      </c>
+      <c r="D100">
+        <v>491</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>9</v>
+      </c>
+      <c r="G100">
+        <v>0.982</v>
+      </c>
+      <c r="H100">
+        <v>0.9703346494262702</v>
+      </c>
+      <c r="I100">
+        <v>0.9936653505737297</v>
+      </c>
+      <c r="J100" t="b">
+        <v>1</v>
+      </c>
+      <c r="K100" t="s">
+        <v>28</v>
+      </c>
+      <c r="L100" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" t="s">
+        <v>21</v>
+      </c>
+      <c r="B101" t="s">
+        <v>22</v>
+      </c>
+      <c r="C101">
+        <v>500</v>
+      </c>
+      <c r="D101">
+        <v>492</v>
+      </c>
+      <c r="E101">
+        <v>2</v>
+      </c>
+      <c r="F101">
+        <v>6</v>
+      </c>
+      <c r="G101">
+        <v>0.986</v>
+      </c>
+      <c r="H101">
+        <v>0.9760716145080404</v>
+      </c>
+      <c r="I101">
+        <v>0.9959283854919596</v>
+      </c>
+      <c r="J101" t="b">
+        <v>1</v>
+      </c>
+      <c r="K101" t="s">
+        <v>28</v>
+      </c>
+      <c r="L101" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" t="s">
+        <v>21</v>
+      </c>
+      <c r="B102" t="s">
+        <v>23</v>
+      </c>
+      <c r="C102">
+        <v>500</v>
+      </c>
+      <c r="D102">
+        <v>248</v>
+      </c>
+      <c r="E102">
+        <v>3</v>
+      </c>
+      <c r="F102">
+        <v>249</v>
+      </c>
+      <c r="G102">
+        <v>0.499</v>
+      </c>
+      <c r="H102">
+        <v>0.4552610733532655</v>
+      </c>
+      <c r="I102">
+        <v>0.5427389266467344</v>
+      </c>
+      <c r="J102" t="b">
+        <v>1</v>
+      </c>
+      <c r="K102" t="s">
+        <v>28</v>
+      </c>
+      <c r="L102" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" t="s">
+        <v>21</v>
+      </c>
+      <c r="B103" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103">
+        <v>500</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>498</v>
+      </c>
+      <c r="G103">
+        <v>0.004</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0.009538159551912971</v>
+      </c>
+      <c r="J103" t="b">
+        <v>1</v>
+      </c>
+      <c r="K103" t="s">
+        <v>28</v>
+      </c>
+      <c r="L103" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" t="s">
+        <v>21</v>
+      </c>
+      <c r="B104" t="s">
+        <v>25</v>
+      </c>
+      <c r="C104">
+        <v>500</v>
+      </c>
+      <c r="D104">
+        <v>247</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+      <c r="F104">
+        <v>251</v>
+      </c>
+      <c r="G104">
+        <v>0.496</v>
+      </c>
+      <c r="H104">
+        <v>0.4522184111315305</v>
+      </c>
+      <c r="I104">
+        <v>0.5397815888684695</v>
+      </c>
+      <c r="J104" t="b">
+        <v>1</v>
+      </c>
+      <c r="K104" t="s">
+        <v>28</v>
+      </c>
+      <c r="L104" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" t="s">
+        <v>21</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105">
+        <v>500</v>
+      </c>
+      <c r="D105">
+        <v>497</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>3</v>
+      </c>
+      <c r="G105">
+        <v>0.994</v>
+      </c>
+      <c r="H105">
+        <v>0.9872239809867935</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105" t="b">
+        <v>1</v>
+      </c>
+      <c r="K105" t="s">
+        <v>28</v>
+      </c>
+      <c r="L105" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" t="s">
+        <v>21</v>
+      </c>
+      <c r="B106" t="s">
+        <v>27</v>
+      </c>
+      <c r="C106">
+        <v>500</v>
+      </c>
+      <c r="D106">
+        <v>498</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>2</v>
+      </c>
+      <c r="G106">
+        <v>0.996</v>
+      </c>
+      <c r="H106">
+        <v>0.990461840448087</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106" t="b">
+        <v>1</v>
+      </c>
+      <c r="K106" t="s">
+        <v>28</v>
+      </c>
+      <c r="L106" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" t="s">
+        <v>22</v>
+      </c>
+      <c r="B107" t="s">
+        <v>23</v>
+      </c>
+      <c r="C107">
+        <v>500</v>
+      </c>
+      <c r="D107">
+        <v>3</v>
+      </c>
+      <c r="E107">
+        <v>5</v>
+      </c>
+      <c r="F107">
+        <v>492</v>
+      </c>
+      <c r="G107">
+        <v>0.011</v>
+      </c>
+      <c r="H107">
+        <v>0.002968403278812887</v>
+      </c>
+      <c r="I107">
+        <v>0.01903159672118711</v>
+      </c>
+      <c r="J107" t="b">
+        <v>1</v>
+      </c>
+      <c r="K107" t="s">
+        <v>28</v>
+      </c>
+      <c r="L107" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" t="s">
+        <v>22</v>
+      </c>
+      <c r="B108" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108">
+        <v>500</v>
+      </c>
+      <c r="D108">
+        <v>249</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>251</v>
+      </c>
+      <c r="G108">
+        <v>0.498</v>
+      </c>
+      <c r="H108">
+        <v>0.4541295258264922</v>
+      </c>
+      <c r="I108">
+        <v>0.5418704741735079</v>
+      </c>
+      <c r="J108" t="b">
+        <v>1</v>
+      </c>
+      <c r="K108" t="s">
+        <v>28</v>
+      </c>
+      <c r="L108" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" t="s">
+        <v>22</v>
+      </c>
+      <c r="B109" t="s">
+        <v>25</v>
+      </c>
+      <c r="C109">
+        <v>500</v>
+      </c>
+      <c r="D109">
+        <v>250</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>250</v>
+      </c>
+      <c r="G109">
+        <v>0.5</v>
+      </c>
+      <c r="H109">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I109">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J109" t="b">
+        <v>1</v>
+      </c>
+      <c r="K109" t="s">
+        <v>28</v>
+      </c>
+      <c r="L109" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110" t="s">
+        <v>22</v>
+      </c>
+      <c r="B110" t="s">
+        <v>26</v>
+      </c>
+      <c r="C110">
+        <v>500</v>
+      </c>
+      <c r="D110">
+        <v>247</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>253</v>
+      </c>
+      <c r="G110">
+        <v>0.494</v>
+      </c>
+      <c r="H110">
+        <v>0.4501323336716188</v>
+      </c>
+      <c r="I110">
+        <v>0.5378676663283812</v>
+      </c>
+      <c r="J110" t="b">
+        <v>1</v>
+      </c>
+      <c r="K110" t="s">
+        <v>28</v>
+      </c>
+      <c r="L110" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="A111" t="s">
+        <v>22</v>
+      </c>
+      <c r="B111" t="s">
+        <v>27</v>
+      </c>
+      <c r="C111">
+        <v>500</v>
+      </c>
+      <c r="D111">
+        <v>489</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>11</v>
+      </c>
+      <c r="G111">
+        <v>0.978</v>
+      </c>
+      <c r="H111">
+        <v>0.9651297623473974</v>
+      </c>
+      <c r="I111">
+        <v>0.9908702376526025</v>
+      </c>
+      <c r="J111" t="b">
+        <v>1</v>
+      </c>
+      <c r="K111" t="s">
+        <v>28</v>
+      </c>
+      <c r="L111" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="A112" t="s">
+        <v>23</v>
+      </c>
+      <c r="B112" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112">
+        <v>500</v>
+      </c>
+      <c r="D112">
+        <v>251</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>249</v>
+      </c>
+      <c r="G112">
+        <v>0.502</v>
+      </c>
+      <c r="H112">
+        <v>0.4581295258264922</v>
+      </c>
+      <c r="I112">
+        <v>0.5458704741735079</v>
+      </c>
+      <c r="J112" t="b">
+        <v>1</v>
+      </c>
+      <c r="K112" t="s">
+        <v>28</v>
+      </c>
+      <c r="L112" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
+      <c r="A113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B113" t="s">
+        <v>25</v>
+      </c>
+      <c r="C113">
+        <v>500</v>
+      </c>
+      <c r="D113">
+        <v>245</v>
+      </c>
+      <c r="E113">
+        <v>2</v>
+      </c>
+      <c r="F113">
+        <v>253</v>
+      </c>
+      <c r="G113">
+        <v>0.492</v>
+      </c>
+      <c r="H113">
+        <v>0.448222631518302</v>
+      </c>
+      <c r="I113">
+        <v>0.535777368481698</v>
+      </c>
+      <c r="J113" t="b">
+        <v>1</v>
+      </c>
+      <c r="K113" t="s">
+        <v>28</v>
+      </c>
+      <c r="L113" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
+      <c r="A114" t="s">
+        <v>23</v>
+      </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114">
+        <v>500</v>
+      </c>
+      <c r="D114">
+        <v>248</v>
+      </c>
+      <c r="E114">
+        <v>6</v>
+      </c>
+      <c r="F114">
+        <v>246</v>
+      </c>
+      <c r="G114">
+        <v>0.502</v>
+      </c>
+      <c r="H114">
+        <v>0.4583935473510485</v>
+      </c>
+      <c r="I114">
+        <v>0.5456064526489515</v>
+      </c>
+      <c r="J114" t="b">
+        <v>1</v>
+      </c>
+      <c r="K114" t="s">
+        <v>28</v>
+      </c>
+      <c r="L114" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
+      <c r="A115" t="s">
+        <v>23</v>
+      </c>
+      <c r="B115" t="s">
+        <v>27</v>
+      </c>
+      <c r="C115">
+        <v>500</v>
+      </c>
+      <c r="D115">
+        <v>497</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>3</v>
+      </c>
+      <c r="G115">
+        <v>0.994</v>
+      </c>
+      <c r="H115">
+        <v>0.9872239809867935</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115" t="b">
+        <v>1</v>
+      </c>
+      <c r="K115" t="s">
+        <v>28</v>
+      </c>
+      <c r="L115" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
+      <c r="A116" t="s">
+        <v>24</v>
+      </c>
+      <c r="B116" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116">
+        <v>500</v>
+      </c>
+      <c r="D116">
+        <v>12</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>488</v>
+      </c>
+      <c r="G116">
+        <v>0.024</v>
+      </c>
+      <c r="H116">
+        <v>0.01057122713419567</v>
+      </c>
+      <c r="I116">
+        <v>0.03742877286580433</v>
+      </c>
+      <c r="J116" t="b">
+        <v>1</v>
+      </c>
+      <c r="K116" t="s">
+        <v>28</v>
+      </c>
+      <c r="L116" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12">
+      <c r="A117" t="s">
+        <v>24</v>
+      </c>
+      <c r="B117" t="s">
+        <v>26</v>
+      </c>
+      <c r="C117">
+        <v>500</v>
+      </c>
+      <c r="D117">
+        <v>494</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>6</v>
+      </c>
+      <c r="G117">
+        <v>0.988</v>
+      </c>
+      <c r="H117">
+        <v>0.9784462275337606</v>
+      </c>
+      <c r="I117">
+        <v>0.9975537724662393</v>
+      </c>
+      <c r="J117" t="b">
+        <v>1</v>
+      </c>
+      <c r="K117" t="s">
+        <v>28</v>
+      </c>
+      <c r="L117" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="A118" t="s">
+        <v>24</v>
+      </c>
+      <c r="B118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C118">
+        <v>500</v>
+      </c>
+      <c r="D118">
+        <v>253</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+      <c r="F118">
+        <v>246</v>
+      </c>
+      <c r="G118">
+        <v>0.507</v>
+      </c>
+      <c r="H118">
+        <v>0.4631773714989907</v>
+      </c>
+      <c r="I118">
+        <v>0.5508226285010094</v>
+      </c>
+      <c r="J118" t="b">
+        <v>1</v>
+      </c>
+      <c r="K118" t="s">
+        <v>28</v>
+      </c>
+      <c r="L118" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119" t="s">
+        <v>25</v>
+      </c>
+      <c r="B119" t="s">
+        <v>26</v>
+      </c>
+      <c r="C119">
+        <v>500</v>
+      </c>
+      <c r="D119">
+        <v>250</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>250</v>
+      </c>
+      <c r="G119">
+        <v>0.5</v>
+      </c>
+      <c r="H119">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I119">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J119" t="b">
+        <v>1</v>
+      </c>
+      <c r="K119" t="s">
+        <v>28</v>
+      </c>
+      <c r="L119" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120" t="s">
+        <v>25</v>
+      </c>
+      <c r="B120" t="s">
+        <v>27</v>
+      </c>
+      <c r="C120">
+        <v>500</v>
+      </c>
+      <c r="D120">
+        <v>253</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>247</v>
+      </c>
+      <c r="G120">
+        <v>0.506</v>
+      </c>
+      <c r="H120">
+        <v>0.4621323336716188</v>
+      </c>
+      <c r="I120">
+        <v>0.5498676663283812</v>
+      </c>
+      <c r="J120" t="b">
+        <v>1</v>
+      </c>
+      <c r="K120" t="s">
+        <v>28</v>
+      </c>
+      <c r="L120" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="A121" t="s">
+        <v>26</v>
+      </c>
+      <c r="B121" t="s">
+        <v>27</v>
+      </c>
+      <c r="C121">
+        <v>500</v>
+      </c>
+      <c r="D121">
+        <v>493</v>
+      </c>
+      <c r="E121">
+        <v>2</v>
+      </c>
+      <c r="F121">
+        <v>5</v>
+      </c>
+      <c r="G121">
+        <v>0.988</v>
+      </c>
+      <c r="H121">
+        <v>0.9788580105479012</v>
+      </c>
+      <c r="I121">
+        <v>0.9971419894520988</v>
+      </c>
+      <c r="J121" t="b">
+        <v>1</v>
+      </c>
+      <c r="K121" t="s">
+        <v>28</v>
+      </c>
+      <c r="L121" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="28">
   <si>
     <t>A</t>
   </si>
@@ -73,10 +73,7 @@
     <t>PPO_850</t>
   </si>
   <si>
-    <t>PPO_851</t>
-  </si>
-  <si>
-    <t>PPO_852X</t>
+    <t>PPO_853</t>
   </si>
   <si>
     <t>PPO_909</t>
@@ -94,10 +91,7 @@
     <t>PPO_919</t>
   </si>
   <si>
-    <t>SOUP_9</t>
-  </si>
-  <si>
-    <t>X_1</t>
+    <t>PPO_920</t>
   </si>
   <si>
     <t>center</t>
@@ -461,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -513,19 +507,19 @@
         <v>500</v>
       </c>
       <c r="D2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>0.996</v>
+        <v>0.994</v>
       </c>
       <c r="H2">
-        <v>0.990461840448087</v>
+        <v>0.9872239809867935</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -534,10 +528,10 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -551,31 +545,31 @@
         <v>500</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="G3">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="H3">
-        <v>0.004516800347703961</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.02548319965229604</v>
+        <v>0.008792975487946511</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -589,31 +583,31 @@
         <v>500</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="G4">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="H4">
-        <v>0.008886884631612904</v>
+        <v>0.002858010547901262</v>
       </c>
       <c r="I4">
-        <v>0.0331131153683871</v>
+        <v>0.02114198945209874</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -627,31 +621,31 @@
         <v>500</v>
       </c>
       <c r="D5">
-        <v>498</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>497</v>
       </c>
       <c r="G5">
-        <v>0.996</v>
+        <v>0.006</v>
       </c>
       <c r="H5">
-        <v>0.990461840448087</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -665,31 +659,31 @@
         <v>500</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>249</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>496</v>
+        <v>251</v>
       </c>
       <c r="G6">
-        <v>0.008</v>
+        <v>0.498</v>
       </c>
       <c r="H6">
-        <v>0.0001836026626924024</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I6">
-        <v>0.0158163973373076</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -703,31 +697,31 @@
         <v>500</v>
       </c>
       <c r="D7">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>251</v>
+        <v>497</v>
       </c>
       <c r="G7">
-        <v>0.498</v>
+        <v>0.006</v>
       </c>
       <c r="H7">
-        <v>0.4541295258264922</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.5418704741735079</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -741,31 +735,31 @@
         <v>500</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>246</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>495</v>
+        <v>254</v>
       </c>
       <c r="G8">
-        <v>0.01</v>
+        <v>0.492</v>
       </c>
       <c r="H8">
-        <v>0.001269816025738698</v>
+        <v>0.4481347906835411</v>
       </c>
       <c r="I8">
-        <v>0.0187301839742613</v>
+        <v>0.5358652093164589</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -779,31 +773,31 @@
         <v>500</v>
       </c>
       <c r="D9">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G9">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>0.4461379499011075</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I9">
-        <v>0.5338620500988925</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -817,107 +811,107 @@
         <v>500</v>
       </c>
       <c r="D10">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>250</v>
+        <v>498</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>0.004</v>
       </c>
       <c r="H10">
-        <v>0.4561291748584872</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.5438708251415129</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
       <c r="C11">
         <v>500</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G11">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="H11">
-        <v>0.001269816025738694</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0.01873018397426131</v>
+        <v>0.008792975487946511</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>500</v>
       </c>
       <c r="D12">
-        <v>251</v>
+        <v>7</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>249</v>
+        <v>491</v>
       </c>
       <c r="G12">
-        <v>0.502</v>
+        <v>0.016</v>
       </c>
       <c r="H12">
-        <v>0.4581295258264922</v>
+        <v>0.005345981179194954</v>
       </c>
       <c r="I12">
-        <v>0.5458704741735079</v>
+        <v>0.02665401882080505</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -925,37 +919,37 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>500</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>250</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>489</v>
+        <v>250</v>
       </c>
       <c r="G13">
-        <v>0.018</v>
+        <v>0.5</v>
       </c>
       <c r="H13">
-        <v>0.007014409000001933</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I13">
-        <v>0.02898559099999806</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -963,37 +957,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>500</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="G14">
-        <v>0.002</v>
+        <v>0.022</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.009129762347397428</v>
       </c>
       <c r="I14">
-        <v>0.00592</v>
+        <v>0.03487023765260257</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1001,37 +995,37 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C15">
         <v>500</v>
       </c>
       <c r="D15">
-        <v>250</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>250</v>
+        <v>492</v>
       </c>
       <c r="G15">
-        <v>0.5</v>
+        <v>0.016</v>
       </c>
       <c r="H15">
-        <v>0.4561291748584872</v>
+        <v>0.004990607908314969</v>
       </c>
       <c r="I15">
-        <v>0.5438708251415129</v>
+        <v>0.02700939209168503</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1039,37 +1033,37 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C16">
         <v>500</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>254</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>488</v>
+        <v>246</v>
       </c>
       <c r="G16">
-        <v>0.024</v>
+        <v>0.508</v>
       </c>
       <c r="H16">
-        <v>0.01057122713419567</v>
+        <v>0.4641347906835411</v>
       </c>
       <c r="I16">
-        <v>0.03742877286580433</v>
+        <v>0.5518652093164589</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1077,37 +1071,37 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17">
         <v>500</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="G17">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.001269816025738696</v>
       </c>
       <c r="I17">
-        <v>0.009538159551912971</v>
+        <v>0.0187301839742613</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1115,37 +1109,37 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C18">
         <v>500</v>
       </c>
       <c r="D18">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>250</v>
+        <v>498</v>
       </c>
       <c r="G18">
-        <v>0.5</v>
+        <v>0.004</v>
       </c>
       <c r="H18">
-        <v>0.4561291748584872</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>0.5438708251415129</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1153,37 +1147,37 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19">
         <v>500</v>
       </c>
       <c r="D19">
-        <v>252</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>248</v>
+        <v>495</v>
       </c>
       <c r="G19">
-        <v>0.504</v>
+        <v>0.01</v>
       </c>
       <c r="H19">
-        <v>0.4601305787473543</v>
+        <v>0.001269816025738698</v>
       </c>
       <c r="I19">
-        <v>0.5478694212526457</v>
+        <v>0.0187301839742613</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1191,37 +1185,37 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C20">
         <v>500</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>497</v>
+        <v>254</v>
       </c>
       <c r="G20">
-        <v>0.006</v>
+        <v>0.492</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>0.4481347906835411</v>
       </c>
       <c r="I20">
-        <v>0.0127760190132064</v>
+        <v>0.5358652093164589</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1229,37 +1223,37 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21">
         <v>500</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>499</v>
+        <v>254</v>
       </c>
       <c r="G21">
-        <v>0.001</v>
+        <v>0.492</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>0.4481347906835411</v>
       </c>
       <c r="I21">
-        <v>0.00296</v>
+        <v>0.5358652093164589</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1267,189 +1261,189 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22">
         <v>500</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G22">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0.01086951637231636</v>
+        <v>0.01404724417776211</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C23">
         <v>500</v>
       </c>
       <c r="D23">
-        <v>245</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>255</v>
+        <v>493</v>
       </c>
       <c r="G23">
-        <v>0.49</v>
+        <v>0.014</v>
       </c>
       <c r="H23">
-        <v>0.4461379499011075</v>
+        <v>0.00369119620560452</v>
       </c>
       <c r="I23">
-        <v>0.5338620500988925</v>
+        <v>0.02430880379439548</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C24">
         <v>500</v>
       </c>
       <c r="D24">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G24">
-        <v>0.494</v>
+        <v>0.5</v>
       </c>
       <c r="H24">
-        <v>0.4501323336716188</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I24">
-        <v>0.5378676663283812</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C25">
         <v>500</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="G25">
-        <v>0.004</v>
+        <v>0.022</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>0.009129762347397428</v>
       </c>
       <c r="I25">
-        <v>0.009538159551912971</v>
+        <v>0.03487023765260257</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C26">
         <v>500</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>492</v>
+        <v>250</v>
       </c>
       <c r="G26">
-        <v>0.016</v>
+        <v>0.5</v>
       </c>
       <c r="H26">
-        <v>0.004990607908314968</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I26">
-        <v>0.02700939209168503</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1457,37 +1451,37 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <v>500</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="G27">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>0.002858010547901262</v>
       </c>
       <c r="I27">
-        <v>0.0127760190132064</v>
+        <v>0.02114198945209874</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1495,37 +1489,37 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C28">
         <v>500</v>
       </c>
       <c r="D28">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>250</v>
+        <v>496</v>
       </c>
       <c r="G28">
-        <v>0.5</v>
+        <v>0.007</v>
       </c>
       <c r="H28">
-        <v>0.4561291748584872</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>0.5438708251415129</v>
+        <v>0.01404724417776211</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1533,37 +1527,37 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C29">
         <v>500</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29">
-        <v>492</v>
+        <v>250</v>
       </c>
       <c r="G29">
-        <v>0.016</v>
+        <v>0.5</v>
       </c>
       <c r="H29">
-        <v>0.004990607908314968</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I29">
-        <v>0.02700939209168503</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1571,37 +1565,37 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C30">
         <v>500</v>
       </c>
       <c r="D30">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G30">
-        <v>0.497</v>
+        <v>0.502</v>
       </c>
       <c r="H30">
-        <v>0.4531738581138466</v>
+        <v>0.4581295258264922</v>
       </c>
       <c r="I30">
-        <v>0.5408261418861534</v>
+        <v>0.5458704741735079</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1609,37 +1603,37 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C31">
         <v>500</v>
       </c>
       <c r="D31">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="G31">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H31">
-        <v>0.4561291748584872</v>
+        <v>0.4461379499011075</v>
       </c>
       <c r="I31">
-        <v>0.5438708251415129</v>
+        <v>0.5338620500988925</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1647,37 +1641,37 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C32">
         <v>500</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>249</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>492</v>
+        <v>251</v>
       </c>
       <c r="G32">
-        <v>0.016</v>
+        <v>0.498</v>
       </c>
       <c r="H32">
-        <v>0.004990607908314968</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I32">
-        <v>0.02700939209168503</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1685,45 +1679,45 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C33">
         <v>500</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>249</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>493</v>
+        <v>250</v>
       </c>
       <c r="G33">
-        <v>0.014</v>
+        <v>0.499</v>
       </c>
       <c r="H33">
-        <v>0.00369119620560452</v>
+        <v>0.4551731554706159</v>
       </c>
       <c r="I33">
-        <v>0.02430880379439548</v>
+        <v>0.5428268445293841</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C34">
         <v>500</v>
@@ -1750,56 +1744,56 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L34" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C35">
         <v>500</v>
       </c>
       <c r="D35">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G35">
-        <v>0.5</v>
+        <v>0.495</v>
       </c>
       <c r="H35">
-        <v>0.4561291748584872</v>
+        <v>0.4511752634341045</v>
       </c>
       <c r="I35">
-        <v>0.5438708251415129</v>
+        <v>0.5388247365658955</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L35" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C36">
         <v>500</v>
@@ -1826,124 +1820,124 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C37">
         <v>500</v>
       </c>
       <c r="D37">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G37">
-        <v>0.496</v>
+        <v>0.492</v>
       </c>
       <c r="H37">
-        <v>0.4521305787473543</v>
+        <v>0.4481347906835411</v>
       </c>
       <c r="I37">
-        <v>0.5398694212526457</v>
+        <v>0.5358652093164589</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C38">
         <v>500</v>
       </c>
       <c r="D38">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>250</v>
+        <v>497</v>
       </c>
       <c r="G38">
-        <v>0.499</v>
+        <v>0.006</v>
       </c>
       <c r="H38">
-        <v>0.4551731554706159</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>0.5428268445293841</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C39">
         <v>500</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>242</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>494</v>
+        <v>258</v>
       </c>
       <c r="G39">
-        <v>0.012</v>
+        <v>0.484</v>
       </c>
       <c r="H39">
-        <v>0.002446227533760637</v>
+        <v>0.4401516424741424</v>
       </c>
       <c r="I39">
-        <v>0.02155377246623937</v>
+        <v>0.5278483575258576</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -1951,37 +1945,37 @@
         <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C40">
         <v>500</v>
       </c>
       <c r="D40">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G40">
-        <v>0.493</v>
+        <v>0.49</v>
       </c>
       <c r="H40">
-        <v>0.4491773714989907</v>
+        <v>0.4461379499011075</v>
       </c>
       <c r="I40">
-        <v>0.5368226285010094</v>
+        <v>0.5338620500988925</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L40" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -1989,683 +1983,683 @@
         <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C41">
         <v>500</v>
       </c>
       <c r="D41">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G41">
-        <v>0.49</v>
+        <v>0.496</v>
       </c>
       <c r="H41">
-        <v>0.4462257970754079</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I41">
-        <v>0.5337742029245921</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L41" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C42">
         <v>500</v>
       </c>
       <c r="D42">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="F42">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="G42">
-        <v>0.5</v>
+        <v>0.743</v>
       </c>
       <c r="H42">
-        <v>0.4561291748584872</v>
+        <v>0.7200440274317749</v>
       </c>
       <c r="I42">
-        <v>0.5438708251415129</v>
+        <v>0.7659559725682251</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L42" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C43">
         <v>500</v>
       </c>
       <c r="D43">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>252</v>
+        <v>499</v>
       </c>
       <c r="G43">
-        <v>0.496</v>
+        <v>0.002</v>
       </c>
       <c r="H43">
-        <v>0.4521305787473543</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>0.5398694212526457</v>
+        <v>0.00592</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L43" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C44">
         <v>500</v>
       </c>
       <c r="D44">
-        <v>249</v>
+        <v>7</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>251</v>
+        <v>493</v>
       </c>
       <c r="G44">
-        <v>0.498</v>
+        <v>0.014</v>
       </c>
       <c r="H44">
-        <v>0.4541295258264922</v>
+        <v>0.00369119620560452</v>
       </c>
       <c r="I44">
-        <v>0.5418704741735079</v>
+        <v>0.02430880379439548</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L44" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C45">
         <v>500</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="G45">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>0.007182857599697888</v>
       </c>
       <c r="I45">
-        <v>0.00592</v>
+        <v>0.03081714240030211</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L45" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C46">
         <v>500</v>
       </c>
       <c r="D46">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G46">
-        <v>0.494</v>
+        <v>0.502</v>
       </c>
       <c r="H46">
-        <v>0.4501323336716188</v>
+        <v>0.4581295258264922</v>
       </c>
       <c r="I46">
-        <v>0.5378676663283812</v>
+        <v>0.5458704741735079</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L46" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C47">
         <v>500</v>
       </c>
       <c r="D47">
-        <v>249</v>
+        <v>496</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>251</v>
+        <v>4</v>
       </c>
       <c r="G47">
-        <v>0.498</v>
+        <v>0.992</v>
       </c>
       <c r="H47">
-        <v>0.4541295258264922</v>
+        <v>0.9841836026626924</v>
       </c>
       <c r="I47">
-        <v>0.5418704741735079</v>
+        <v>0.9998163973373075</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L47" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C48">
         <v>500</v>
       </c>
       <c r="D48">
-        <v>247</v>
+        <v>4</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>253</v>
+        <v>496</v>
       </c>
       <c r="G48">
-        <v>0.494</v>
+        <v>0.008</v>
       </c>
       <c r="H48">
-        <v>0.4501323336716188</v>
+        <v>0.0001836026626924024</v>
       </c>
       <c r="I48">
-        <v>0.5378676663283812</v>
+        <v>0.0158163973373076</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L48" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C49">
         <v>500</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>248</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>494</v>
+        <v>252</v>
       </c>
       <c r="G49">
-        <v>0.011</v>
+        <v>0.496</v>
       </c>
       <c r="H49">
-        <v>0.002061110791571409</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I49">
-        <v>0.01993888920842859</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C50">
         <v>500</v>
       </c>
       <c r="D50">
-        <v>248</v>
+        <v>6</v>
       </c>
       <c r="E50">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>9</v>
+        <v>494</v>
       </c>
       <c r="G50">
-        <v>0.739</v>
+        <v>0.012</v>
       </c>
       <c r="H50">
-        <v>0.7155581961202155</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I50">
-        <v>0.7624418038797844</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L50" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C51">
         <v>500</v>
       </c>
       <c r="D51">
-        <v>495</v>
+        <v>249</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="G51">
-        <v>0.99</v>
+        <v>0.498</v>
       </c>
       <c r="H51">
-        <v>0.9812698160257387</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I51">
-        <v>0.9987301839742613</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L51" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C52">
         <v>500</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>492</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>496</v>
+        <v>6</v>
       </c>
       <c r="G52">
-        <v>0.008</v>
+        <v>0.986</v>
       </c>
       <c r="H52">
-        <v>0.0001836026626924024</v>
+        <v>0.9760716145080404</v>
       </c>
       <c r="I52">
-        <v>0.0158163973373076</v>
+        <v>0.9959283854919596</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L52" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" t="s">
         <v>16</v>
       </c>
-      <c r="B53" t="s">
-        <v>22</v>
-      </c>
       <c r="C53">
         <v>500</v>
       </c>
       <c r="D53">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="G53">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="H53">
-        <v>0.00571362455285248</v>
+        <v>0</v>
       </c>
       <c r="I53">
-        <v>0.02628637544714752</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L53" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C54">
         <v>500</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>252</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>495</v>
+        <v>248</v>
       </c>
       <c r="G54">
-        <v>0.01</v>
+        <v>0.504</v>
       </c>
       <c r="H54">
-        <v>0.001269816025738698</v>
+        <v>0.4601305787473543</v>
       </c>
       <c r="I54">
-        <v>0.0187301839742613</v>
+        <v>0.5478694212526457</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L54" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C55">
         <v>500</v>
       </c>
       <c r="D55">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G55">
-        <v>0.494</v>
+        <v>0.502</v>
       </c>
       <c r="H55">
-        <v>0.4501323336716188</v>
+        <v>0.4581295258264922</v>
       </c>
       <c r="I55">
-        <v>0.5378676663283812</v>
+        <v>0.5458704741735079</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L55" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C56">
         <v>500</v>
       </c>
       <c r="D56">
-        <v>493</v>
+        <v>6</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>7</v>
+        <v>494</v>
       </c>
       <c r="G56">
-        <v>0.986</v>
+        <v>0.012</v>
       </c>
       <c r="H56">
-        <v>0.9756911962056045</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I56">
-        <v>0.9963088037943955</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L56" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C57">
         <v>500</v>
       </c>
       <c r="D57">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G57">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="H57">
-        <v>0.004990607908314968</v>
+        <v>0.003256725293618782</v>
       </c>
       <c r="I57">
-        <v>0.02700939209168503</v>
+        <v>0.02274327470638122</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L57" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C58">
         <v>500</v>
       </c>
       <c r="D58">
-        <v>496</v>
+        <v>250</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>249</v>
       </c>
       <c r="G58">
-        <v>0.992</v>
+        <v>0.501</v>
       </c>
       <c r="H58">
-        <v>0.9841836026626924</v>
+        <v>0.4571731554706159</v>
       </c>
       <c r="I58">
-        <v>0.9998163973373075</v>
+        <v>0.5448268445293841</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L58" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -2673,7 +2667,7 @@
         <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C59">
         <v>500</v>
@@ -2700,10 +2694,10 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L59" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -2711,37 +2705,37 @@
         <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C60">
         <v>500</v>
       </c>
       <c r="D60">
-        <v>6</v>
+        <v>497</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60">
-        <v>494</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <v>0.012</v>
+        <v>0.994</v>
       </c>
       <c r="H60">
-        <v>0.002446227533760637</v>
+        <v>0.9872239809867935</v>
       </c>
       <c r="I60">
-        <v>0.02155377246623937</v>
+        <v>1</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L60" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -2749,1106 +2743,1106 @@
         <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C61">
         <v>500</v>
       </c>
       <c r="D61">
-        <v>249</v>
+        <v>2</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61">
-        <v>251</v>
+        <v>498</v>
       </c>
       <c r="G61">
-        <v>0.498</v>
+        <v>0.004</v>
       </c>
       <c r="H61">
-        <v>0.4541295258264922</v>
+        <v>0</v>
       </c>
       <c r="I61">
-        <v>0.5418704741735079</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L61" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C62">
         <v>500</v>
       </c>
       <c r="D62">
-        <v>492</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>249</v>
       </c>
       <c r="F62">
-        <v>6</v>
+        <v>251</v>
       </c>
       <c r="G62">
-        <v>0.986</v>
+        <v>0.249</v>
       </c>
       <c r="H62">
-        <v>0.9760716145080404</v>
+        <v>0.2270647629132461</v>
       </c>
       <c r="I62">
-        <v>0.9959283854919596</v>
+        <v>0.2709352370867539</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L62" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C63">
         <v>500</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63">
         <v>0</v>
       </c>
       <c r="F63">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G63">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H63">
         <v>0</v>
       </c>
       <c r="I63">
-        <v>0.0127760190132064</v>
+        <v>0.00592</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L63" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C64">
         <v>500</v>
       </c>
       <c r="D64">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="F64">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G64">
-        <v>0.504</v>
+        <v>0.249</v>
       </c>
       <c r="H64">
-        <v>0.4601305787473543</v>
+        <v>0.2270647629132461</v>
       </c>
       <c r="I64">
-        <v>0.5478694212526457</v>
+        <v>0.2709352370867539</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L64" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B65" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C65">
         <v>500</v>
       </c>
       <c r="D65">
-        <v>496</v>
+        <v>245</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>255</v>
       </c>
       <c r="G65">
-        <v>0.992</v>
+        <v>0.49</v>
       </c>
       <c r="H65">
-        <v>0.9841836026626924</v>
+        <v>0.4461379499011075</v>
       </c>
       <c r="I65">
-        <v>0.9998163973373075</v>
+        <v>0.5338620500988924</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L65" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C66">
         <v>500</v>
       </c>
       <c r="D66">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E66">
         <v>0</v>
       </c>
       <c r="F66">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G66">
-        <v>0.504</v>
+        <v>0.498</v>
       </c>
       <c r="H66">
-        <v>0.4601305787473543</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I66">
-        <v>0.5478694212526457</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L66" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B67" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C67">
         <v>500</v>
       </c>
       <c r="D67">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E67">
         <v>0</v>
       </c>
       <c r="F67">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="G67">
-        <v>0.014</v>
+        <v>0.008</v>
       </c>
       <c r="H67">
-        <v>0.00369119620560452</v>
+        <v>0.0001836026626924024</v>
       </c>
       <c r="I67">
-        <v>0.02430880379439548</v>
+        <v>0.0158163973373076</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L67" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B68" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C68">
         <v>500</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>248</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>494</v>
+        <v>251</v>
       </c>
       <c r="G68">
-        <v>0.012</v>
+        <v>0.497</v>
       </c>
       <c r="H68">
-        <v>0.002446227533760637</v>
+        <v>0.4531738581138466</v>
       </c>
       <c r="I68">
-        <v>0.02155377246623937</v>
+        <v>0.5408261418861534</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L68" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C69">
         <v>500</v>
       </c>
       <c r="D69">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G69">
-        <v>0.496</v>
+        <v>0.498</v>
       </c>
       <c r="H69">
-        <v>0.4521305787473543</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I69">
-        <v>0.5398694212526457</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L69" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C70">
         <v>500</v>
       </c>
       <c r="D70">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G70">
-        <v>0.496</v>
+        <v>0.498</v>
       </c>
       <c r="H70">
-        <v>0.4521305787473543</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I70">
-        <v>0.5398694212526457</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L70" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B71" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C71">
         <v>500</v>
       </c>
       <c r="D71">
-        <v>496</v>
+        <v>249</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71">
-        <v>4</v>
+        <v>251</v>
       </c>
       <c r="G71">
-        <v>0.992</v>
+        <v>0.498</v>
       </c>
       <c r="H71">
-        <v>0.9841836026626924</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I71">
-        <v>0.9998163973373075</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L71" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C72">
         <v>500</v>
       </c>
       <c r="D72">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="G72">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>0.003256725293618782</v>
+        <v>0</v>
       </c>
       <c r="I72">
-        <v>0.02274327470638122</v>
+        <v>0</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L72" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B73" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C73">
         <v>500</v>
       </c>
       <c r="D73">
-        <v>252</v>
+        <v>6</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
-        <v>248</v>
+        <v>494</v>
       </c>
       <c r="G73">
-        <v>0.504</v>
+        <v>0.012</v>
       </c>
       <c r="H73">
-        <v>0.4601305787473543</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I73">
-        <v>0.5478694212526457</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L73" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C74">
         <v>500</v>
       </c>
       <c r="D74">
-        <v>249</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>498</v>
       </c>
       <c r="G74">
-        <v>0.744</v>
+        <v>0.004</v>
       </c>
       <c r="H74">
-        <v>0.721210130296067</v>
+        <v>0</v>
       </c>
       <c r="I74">
-        <v>0.766789869703933</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L74" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C75">
         <v>500</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>246</v>
       </c>
       <c r="E75">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G75">
-        <v>0.248</v>
+        <v>0.492</v>
       </c>
       <c r="H75">
-        <v>0.2258904968971505</v>
+        <v>0.4481347906835411</v>
       </c>
       <c r="I75">
-        <v>0.2701095031028495</v>
+        <v>0.5358652093164589</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L75" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B76" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C76">
         <v>500</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>497</v>
+        <v>251</v>
       </c>
       <c r="G76">
-        <v>0.006</v>
+        <v>0.498</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I76">
-        <v>0.0127760190132064</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L76" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C77">
         <v>500</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="F77">
-        <v>253</v>
+        <v>498</v>
       </c>
       <c r="G77">
-        <v>0.25</v>
+        <v>0.004</v>
       </c>
       <c r="H77">
-        <v>0.2275443077097929</v>
+        <v>0</v>
       </c>
       <c r="I77">
-        <v>0.2724556922902071</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L77" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C78">
         <v>500</v>
       </c>
       <c r="D78">
-        <v>250</v>
+        <v>497</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="G78">
-        <v>0.5</v>
+        <v>0.994</v>
       </c>
       <c r="H78">
-        <v>0.4561291748584872</v>
+        <v>0.9872239809867935</v>
       </c>
       <c r="I78">
-        <v>0.5438708251415129</v>
+        <v>1</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L78" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B79" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C79">
         <v>500</v>
       </c>
       <c r="D79">
+        <v>250</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79">
         <v>249</v>
       </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-      <c r="F79">
-        <v>251</v>
-      </c>
       <c r="G79">
-        <v>0.498</v>
+        <v>0.501</v>
       </c>
       <c r="H79">
-        <v>0.4541295258264922</v>
+        <v>0.4571731554706159</v>
       </c>
       <c r="I79">
-        <v>0.5418704741735079</v>
+        <v>0.5448268445293841</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L79" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B80" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C80">
         <v>500</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E80">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="F80">
-        <v>253</v>
+        <v>492</v>
       </c>
       <c r="G80">
-        <v>0.25</v>
+        <v>0.016</v>
       </c>
       <c r="H80">
-        <v>0.2275443077097929</v>
+        <v>0.004990607908314968</v>
       </c>
       <c r="I80">
-        <v>0.2724556922902071</v>
+        <v>0.02700939209168503</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L80" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B81" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C81">
         <v>500</v>
       </c>
       <c r="D81">
-        <v>499</v>
+        <v>252</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>247</v>
       </c>
       <c r="G81">
-        <v>0.998</v>
+        <v>0.505</v>
       </c>
       <c r="H81">
-        <v>0.99408</v>
+        <v>0.4611752634341045</v>
       </c>
       <c r="I81">
-        <v>1</v>
+        <v>0.5488247365658955</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L81" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C82">
         <v>500</v>
       </c>
       <c r="D82">
+        <v>495</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
         <v>5</v>
       </c>
-      <c r="E82">
-        <v>2</v>
-      </c>
-      <c r="F82">
-        <v>493</v>
-      </c>
       <c r="G82">
-        <v>0.012</v>
+        <v>0.99</v>
       </c>
       <c r="H82">
-        <v>0.002858010547901262</v>
+        <v>0.9812698160257387</v>
       </c>
       <c r="I82">
-        <v>0.02114198945209874</v>
+        <v>0.9987301839742613</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L82" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C83">
         <v>500</v>
       </c>
       <c r="D83">
-        <v>251</v>
+        <v>3</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83">
-        <v>249</v>
+        <v>496</v>
       </c>
       <c r="G83">
-        <v>0.502</v>
+        <v>0.007</v>
       </c>
       <c r="H83">
-        <v>0.4581295258264922</v>
+        <v>0</v>
       </c>
       <c r="I83">
-        <v>0.5458704741735079</v>
+        <v>0.01404724417776211</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L83" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B84" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C84">
         <v>500</v>
       </c>
       <c r="D84">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F84">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G84">
-        <v>0.5</v>
+        <v>0.492</v>
       </c>
       <c r="H84">
-        <v>0.4561291748584872</v>
+        <v>0.448222631518302</v>
       </c>
       <c r="I84">
-        <v>0.5438708251415129</v>
+        <v>0.535777368481698</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L84" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B85" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C85">
         <v>500</v>
       </c>
       <c r="D85">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G85">
-        <v>0.501</v>
+        <v>0.504</v>
       </c>
       <c r="H85">
-        <v>0.4571731554706159</v>
+        <v>0.4601305787473543</v>
       </c>
       <c r="I85">
-        <v>0.5448268445293841</v>
+        <v>0.5478694212526457</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L85" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C86">
         <v>500</v>
       </c>
       <c r="D86">
-        <v>494</v>
+        <v>249</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86">
-        <v>6</v>
+        <v>250</v>
       </c>
       <c r="G86">
-        <v>0.988</v>
+        <v>0.499</v>
       </c>
       <c r="H86">
-        <v>0.9784462275337606</v>
+        <v>0.4551731554706159</v>
       </c>
       <c r="I86">
-        <v>0.9975537724662393</v>
+        <v>0.5428268445293841</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L86" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C87">
         <v>500</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87">
-        <v>499</v>
+        <v>249</v>
       </c>
       <c r="G87">
-        <v>0.002</v>
+        <v>0.501</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>0.4571731554706159</v>
       </c>
       <c r="I87">
-        <v>0.00592</v>
+        <v>0.5448268445293841</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L87" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B88" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C88">
         <v>500</v>
       </c>
       <c r="D88">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88">
         <v>252</v>
       </c>
       <c r="G88">
-        <v>0.496</v>
+        <v>0.495</v>
       </c>
       <c r="H88">
-        <v>0.4521305787473543</v>
+        <v>0.4511752634341045</v>
       </c>
       <c r="I88">
-        <v>0.5398694212526457</v>
+        <v>0.5388247365658955</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B89" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C89">
         <v>500</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>498</v>
+        <v>250</v>
       </c>
       <c r="G89">
-        <v>0.003</v>
+        <v>0.5</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I89">
-        <v>0.007379178645730549</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L89" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B90" t="s">
         <v>24</v>
@@ -3857,36 +3851,36 @@
         <v>500</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G90">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>0.0001836026626924024</v>
       </c>
       <c r="I90">
-        <v>0.0127760190132064</v>
+        <v>0.0158163973373076</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L90" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B91" t="s">
         <v>25</v>
@@ -3895,1171 +3889,69 @@
         <v>500</v>
       </c>
       <c r="D91">
-        <v>245</v>
+        <v>493</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F91">
-        <v>255</v>
+        <v>4</v>
       </c>
       <c r="G91">
-        <v>0.49</v>
+        <v>0.989</v>
       </c>
       <c r="H91">
-        <v>0.4461379499011075</v>
+        <v>0.9805026390516718</v>
       </c>
       <c r="I91">
-        <v>0.5338620500988925</v>
+        <v>0.9974973609483282</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L91" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C92">
         <v>500</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>249</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F92">
-        <v>499</v>
+        <v>249</v>
       </c>
       <c r="G92">
-        <v>0.002</v>
+        <v>0.5</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>0.4562170044263437</v>
       </c>
       <c r="I92">
-        <v>0.00592</v>
+        <v>0.5437829955736563</v>
       </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L92" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12">
-      <c r="A93" t="s">
-        <v>19</v>
-      </c>
-      <c r="B93" t="s">
-        <v>27</v>
-      </c>
-      <c r="C93">
-        <v>500</v>
-      </c>
-      <c r="D93">
-        <v>3</v>
-      </c>
-      <c r="E93">
-        <v>1</v>
-      </c>
-      <c r="F93">
-        <v>496</v>
-      </c>
-      <c r="G93">
-        <v>0.007</v>
-      </c>
-      <c r="H93">
-        <v>0</v>
-      </c>
-      <c r="I93">
-        <v>0.01404724417776211</v>
-      </c>
-      <c r="J93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K93" t="s">
-        <v>28</v>
-      </c>
-      <c r="L93" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12">
-      <c r="A94" t="s">
-        <v>20</v>
-      </c>
-      <c r="B94" t="s">
-        <v>21</v>
-      </c>
-      <c r="C94">
-        <v>500</v>
-      </c>
-      <c r="D94">
-        <v>7</v>
-      </c>
-      <c r="E94">
-        <v>0</v>
-      </c>
-      <c r="F94">
-        <v>493</v>
-      </c>
-      <c r="G94">
-        <v>0.014</v>
-      </c>
-      <c r="H94">
-        <v>0.00369119620560452</v>
-      </c>
-      <c r="I94">
-        <v>0.02430880379439548</v>
-      </c>
-      <c r="J94" t="b">
-        <v>1</v>
-      </c>
-      <c r="K94" t="s">
-        <v>28</v>
-      </c>
-      <c r="L94" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12">
-      <c r="A95" t="s">
-        <v>20</v>
-      </c>
-      <c r="B95" t="s">
-        <v>22</v>
-      </c>
-      <c r="C95">
-        <v>500</v>
-      </c>
-      <c r="D95">
-        <v>1</v>
-      </c>
-      <c r="E95">
-        <v>1</v>
-      </c>
-      <c r="F95">
-        <v>498</v>
-      </c>
-      <c r="G95">
-        <v>0.003</v>
-      </c>
-      <c r="H95">
-        <v>0</v>
-      </c>
-      <c r="I95">
-        <v>0.007379178645730549</v>
-      </c>
-      <c r="J95" t="b">
-        <v>1</v>
-      </c>
-      <c r="K95" t="s">
-        <v>28</v>
-      </c>
-      <c r="L95" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12">
-      <c r="A96" t="s">
-        <v>20</v>
-      </c>
-      <c r="B96" t="s">
-        <v>23</v>
-      </c>
-      <c r="C96">
-        <v>500</v>
-      </c>
-      <c r="D96">
-        <v>4</v>
-      </c>
-      <c r="E96">
-        <v>0</v>
-      </c>
-      <c r="F96">
-        <v>496</v>
-      </c>
-      <c r="G96">
-        <v>0.008</v>
-      </c>
-      <c r="H96">
-        <v>0.0001836026626924024</v>
-      </c>
-      <c r="I96">
-        <v>0.0158163973373076</v>
-      </c>
-      <c r="J96" t="b">
-        <v>1</v>
-      </c>
-      <c r="K96" t="s">
-        <v>28</v>
-      </c>
-      <c r="L96" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12">
-      <c r="A97" t="s">
-        <v>20</v>
-      </c>
-      <c r="B97" t="s">
-        <v>24</v>
-      </c>
-      <c r="C97">
-        <v>500</v>
-      </c>
-      <c r="D97">
-        <v>246</v>
-      </c>
-      <c r="E97">
-        <v>0</v>
-      </c>
-      <c r="F97">
-        <v>254</v>
-      </c>
-      <c r="G97">
-        <v>0.492</v>
-      </c>
-      <c r="H97">
-        <v>0.4481347906835411</v>
-      </c>
-      <c r="I97">
-        <v>0.5358652093164589</v>
-      </c>
-      <c r="J97" t="b">
-        <v>1</v>
-      </c>
-      <c r="K97" t="s">
-        <v>28</v>
-      </c>
-      <c r="L97" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12">
-      <c r="A98" t="s">
-        <v>20</v>
-      </c>
-      <c r="B98" t="s">
-        <v>25</v>
-      </c>
-      <c r="C98">
-        <v>500</v>
-      </c>
-      <c r="D98">
-        <v>247</v>
-      </c>
-      <c r="E98">
-        <v>0</v>
-      </c>
-      <c r="F98">
-        <v>253</v>
-      </c>
-      <c r="G98">
-        <v>0.494</v>
-      </c>
-      <c r="H98">
-        <v>0.4501323336716188</v>
-      </c>
-      <c r="I98">
-        <v>0.5378676663283812</v>
-      </c>
-      <c r="J98" t="b">
-        <v>1</v>
-      </c>
-      <c r="K98" t="s">
-        <v>28</v>
-      </c>
-      <c r="L98" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12">
-      <c r="A99" t="s">
-        <v>20</v>
-      </c>
-      <c r="B99" t="s">
-        <v>26</v>
-      </c>
-      <c r="C99">
-        <v>500</v>
-      </c>
-      <c r="D99">
-        <v>2</v>
-      </c>
-      <c r="E99">
-        <v>1</v>
-      </c>
-      <c r="F99">
-        <v>497</v>
-      </c>
-      <c r="G99">
-        <v>0.005</v>
-      </c>
-      <c r="H99">
-        <v>0</v>
-      </c>
-      <c r="I99">
-        <v>0.01086951637231636</v>
-      </c>
-      <c r="J99" t="b">
-        <v>1</v>
-      </c>
-      <c r="K99" t="s">
-        <v>28</v>
-      </c>
-      <c r="L99" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12">
-      <c r="A100" t="s">
-        <v>20</v>
-      </c>
-      <c r="B100" t="s">
-        <v>27</v>
-      </c>
-      <c r="C100">
-        <v>500</v>
-      </c>
-      <c r="D100">
-        <v>491</v>
-      </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
-      <c r="F100">
-        <v>9</v>
-      </c>
-      <c r="G100">
-        <v>0.982</v>
-      </c>
-      <c r="H100">
-        <v>0.9703346494262702</v>
-      </c>
-      <c r="I100">
-        <v>0.9936653505737297</v>
-      </c>
-      <c r="J100" t="b">
-        <v>1</v>
-      </c>
-      <c r="K100" t="s">
-        <v>28</v>
-      </c>
-      <c r="L100" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12">
-      <c r="A101" t="s">
-        <v>21</v>
-      </c>
-      <c r="B101" t="s">
-        <v>22</v>
-      </c>
-      <c r="C101">
-        <v>500</v>
-      </c>
-      <c r="D101">
-        <v>492</v>
-      </c>
-      <c r="E101">
-        <v>2</v>
-      </c>
-      <c r="F101">
-        <v>6</v>
-      </c>
-      <c r="G101">
-        <v>0.986</v>
-      </c>
-      <c r="H101">
-        <v>0.9760716145080404</v>
-      </c>
-      <c r="I101">
-        <v>0.9959283854919596</v>
-      </c>
-      <c r="J101" t="b">
-        <v>1</v>
-      </c>
-      <c r="K101" t="s">
-        <v>28</v>
-      </c>
-      <c r="L101" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12">
-      <c r="A102" t="s">
-        <v>21</v>
-      </c>
-      <c r="B102" t="s">
-        <v>23</v>
-      </c>
-      <c r="C102">
-        <v>500</v>
-      </c>
-      <c r="D102">
-        <v>248</v>
-      </c>
-      <c r="E102">
-        <v>3</v>
-      </c>
-      <c r="F102">
-        <v>249</v>
-      </c>
-      <c r="G102">
-        <v>0.499</v>
-      </c>
-      <c r="H102">
-        <v>0.4552610733532655</v>
-      </c>
-      <c r="I102">
-        <v>0.5427389266467344</v>
-      </c>
-      <c r="J102" t="b">
-        <v>1</v>
-      </c>
-      <c r="K102" t="s">
-        <v>28</v>
-      </c>
-      <c r="L102" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12">
-      <c r="A103" t="s">
-        <v>21</v>
-      </c>
-      <c r="B103" t="s">
-        <v>24</v>
-      </c>
-      <c r="C103">
-        <v>500</v>
-      </c>
-      <c r="D103">
-        <v>2</v>
-      </c>
-      <c r="E103">
-        <v>0</v>
-      </c>
-      <c r="F103">
-        <v>498</v>
-      </c>
-      <c r="G103">
-        <v>0.004</v>
-      </c>
-      <c r="H103">
-        <v>0</v>
-      </c>
-      <c r="I103">
-        <v>0.009538159551912971</v>
-      </c>
-      <c r="J103" t="b">
-        <v>1</v>
-      </c>
-      <c r="K103" t="s">
-        <v>28</v>
-      </c>
-      <c r="L103" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12">
-      <c r="A104" t="s">
-        <v>21</v>
-      </c>
-      <c r="B104" t="s">
-        <v>25</v>
-      </c>
-      <c r="C104">
-        <v>500</v>
-      </c>
-      <c r="D104">
-        <v>247</v>
-      </c>
-      <c r="E104">
-        <v>2</v>
-      </c>
-      <c r="F104">
-        <v>251</v>
-      </c>
-      <c r="G104">
-        <v>0.496</v>
-      </c>
-      <c r="H104">
-        <v>0.4522184111315305</v>
-      </c>
-      <c r="I104">
-        <v>0.5397815888684695</v>
-      </c>
-      <c r="J104" t="b">
-        <v>1</v>
-      </c>
-      <c r="K104" t="s">
-        <v>28</v>
-      </c>
-      <c r="L104" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12">
-      <c r="A105" t="s">
-        <v>21</v>
-      </c>
-      <c r="B105" t="s">
-        <v>26</v>
-      </c>
-      <c r="C105">
-        <v>500</v>
-      </c>
-      <c r="D105">
-        <v>497</v>
-      </c>
-      <c r="E105">
-        <v>0</v>
-      </c>
-      <c r="F105">
-        <v>3</v>
-      </c>
-      <c r="G105">
-        <v>0.994</v>
-      </c>
-      <c r="H105">
-        <v>0.9872239809867935</v>
-      </c>
-      <c r="I105">
-        <v>1</v>
-      </c>
-      <c r="J105" t="b">
-        <v>1</v>
-      </c>
-      <c r="K105" t="s">
-        <v>28</v>
-      </c>
-      <c r="L105" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12">
-      <c r="A106" t="s">
-        <v>21</v>
-      </c>
-      <c r="B106" t="s">
-        <v>27</v>
-      </c>
-      <c r="C106">
-        <v>500</v>
-      </c>
-      <c r="D106">
-        <v>498</v>
-      </c>
-      <c r="E106">
-        <v>0</v>
-      </c>
-      <c r="F106">
-        <v>2</v>
-      </c>
-      <c r="G106">
-        <v>0.996</v>
-      </c>
-      <c r="H106">
-        <v>0.990461840448087</v>
-      </c>
-      <c r="I106">
-        <v>1</v>
-      </c>
-      <c r="J106" t="b">
-        <v>1</v>
-      </c>
-      <c r="K106" t="s">
-        <v>28</v>
-      </c>
-      <c r="L106" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12">
-      <c r="A107" t="s">
-        <v>22</v>
-      </c>
-      <c r="B107" t="s">
-        <v>23</v>
-      </c>
-      <c r="C107">
-        <v>500</v>
-      </c>
-      <c r="D107">
-        <v>3</v>
-      </c>
-      <c r="E107">
-        <v>5</v>
-      </c>
-      <c r="F107">
-        <v>492</v>
-      </c>
-      <c r="G107">
-        <v>0.011</v>
-      </c>
-      <c r="H107">
-        <v>0.002968403278812887</v>
-      </c>
-      <c r="I107">
-        <v>0.01903159672118711</v>
-      </c>
-      <c r="J107" t="b">
-        <v>1</v>
-      </c>
-      <c r="K107" t="s">
-        <v>28</v>
-      </c>
-      <c r="L107" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12">
-      <c r="A108" t="s">
-        <v>22</v>
-      </c>
-      <c r="B108" t="s">
-        <v>24</v>
-      </c>
-      <c r="C108">
-        <v>500</v>
-      </c>
-      <c r="D108">
-        <v>249</v>
-      </c>
-      <c r="E108">
-        <v>0</v>
-      </c>
-      <c r="F108">
-        <v>251</v>
-      </c>
-      <c r="G108">
-        <v>0.498</v>
-      </c>
-      <c r="H108">
-        <v>0.4541295258264922</v>
-      </c>
-      <c r="I108">
-        <v>0.5418704741735079</v>
-      </c>
-      <c r="J108" t="b">
-        <v>1</v>
-      </c>
-      <c r="K108" t="s">
-        <v>28</v>
-      </c>
-      <c r="L108" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12">
-      <c r="A109" t="s">
-        <v>22</v>
-      </c>
-      <c r="B109" t="s">
-        <v>25</v>
-      </c>
-      <c r="C109">
-        <v>500</v>
-      </c>
-      <c r="D109">
-        <v>250</v>
-      </c>
-      <c r="E109">
-        <v>0</v>
-      </c>
-      <c r="F109">
-        <v>250</v>
-      </c>
-      <c r="G109">
-        <v>0.5</v>
-      </c>
-      <c r="H109">
-        <v>0.4561291748584872</v>
-      </c>
-      <c r="I109">
-        <v>0.5438708251415129</v>
-      </c>
-      <c r="J109" t="b">
-        <v>1</v>
-      </c>
-      <c r="K109" t="s">
-        <v>28</v>
-      </c>
-      <c r="L109" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12">
-      <c r="A110" t="s">
-        <v>22</v>
-      </c>
-      <c r="B110" t="s">
-        <v>26</v>
-      </c>
-      <c r="C110">
-        <v>500</v>
-      </c>
-      <c r="D110">
-        <v>247</v>
-      </c>
-      <c r="E110">
-        <v>0</v>
-      </c>
-      <c r="F110">
-        <v>253</v>
-      </c>
-      <c r="G110">
-        <v>0.494</v>
-      </c>
-      <c r="H110">
-        <v>0.4501323336716188</v>
-      </c>
-      <c r="I110">
-        <v>0.5378676663283812</v>
-      </c>
-      <c r="J110" t="b">
-        <v>1</v>
-      </c>
-      <c r="K110" t="s">
-        <v>28</v>
-      </c>
-      <c r="L110" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12">
-      <c r="A111" t="s">
-        <v>22</v>
-      </c>
-      <c r="B111" t="s">
-        <v>27</v>
-      </c>
-      <c r="C111">
-        <v>500</v>
-      </c>
-      <c r="D111">
-        <v>489</v>
-      </c>
-      <c r="E111">
-        <v>0</v>
-      </c>
-      <c r="F111">
-        <v>11</v>
-      </c>
-      <c r="G111">
-        <v>0.978</v>
-      </c>
-      <c r="H111">
-        <v>0.9651297623473974</v>
-      </c>
-      <c r="I111">
-        <v>0.9908702376526025</v>
-      </c>
-      <c r="J111" t="b">
-        <v>1</v>
-      </c>
-      <c r="K111" t="s">
-        <v>28</v>
-      </c>
-      <c r="L111" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12">
-      <c r="A112" t="s">
-        <v>23</v>
-      </c>
-      <c r="B112" t="s">
-        <v>24</v>
-      </c>
-      <c r="C112">
-        <v>500</v>
-      </c>
-      <c r="D112">
-        <v>251</v>
-      </c>
-      <c r="E112">
-        <v>0</v>
-      </c>
-      <c r="F112">
-        <v>249</v>
-      </c>
-      <c r="G112">
-        <v>0.502</v>
-      </c>
-      <c r="H112">
-        <v>0.4581295258264922</v>
-      </c>
-      <c r="I112">
-        <v>0.5458704741735079</v>
-      </c>
-      <c r="J112" t="b">
-        <v>1</v>
-      </c>
-      <c r="K112" t="s">
-        <v>28</v>
-      </c>
-      <c r="L112" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12">
-      <c r="A113" t="s">
-        <v>23</v>
-      </c>
-      <c r="B113" t="s">
-        <v>25</v>
-      </c>
-      <c r="C113">
-        <v>500</v>
-      </c>
-      <c r="D113">
-        <v>245</v>
-      </c>
-      <c r="E113">
-        <v>2</v>
-      </c>
-      <c r="F113">
-        <v>253</v>
-      </c>
-      <c r="G113">
-        <v>0.492</v>
-      </c>
-      <c r="H113">
-        <v>0.448222631518302</v>
-      </c>
-      <c r="I113">
-        <v>0.535777368481698</v>
-      </c>
-      <c r="J113" t="b">
-        <v>1</v>
-      </c>
-      <c r="K113" t="s">
-        <v>28</v>
-      </c>
-      <c r="L113" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12">
-      <c r="A114" t="s">
-        <v>23</v>
-      </c>
-      <c r="B114" t="s">
-        <v>26</v>
-      </c>
-      <c r="C114">
-        <v>500</v>
-      </c>
-      <c r="D114">
-        <v>248</v>
-      </c>
-      <c r="E114">
-        <v>6</v>
-      </c>
-      <c r="F114">
-        <v>246</v>
-      </c>
-      <c r="G114">
-        <v>0.502</v>
-      </c>
-      <c r="H114">
-        <v>0.4583935473510485</v>
-      </c>
-      <c r="I114">
-        <v>0.5456064526489515</v>
-      </c>
-      <c r="J114" t="b">
-        <v>1</v>
-      </c>
-      <c r="K114" t="s">
-        <v>28</v>
-      </c>
-      <c r="L114" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12">
-      <c r="A115" t="s">
-        <v>23</v>
-      </c>
-      <c r="B115" t="s">
-        <v>27</v>
-      </c>
-      <c r="C115">
-        <v>500</v>
-      </c>
-      <c r="D115">
-        <v>497</v>
-      </c>
-      <c r="E115">
-        <v>0</v>
-      </c>
-      <c r="F115">
-        <v>3</v>
-      </c>
-      <c r="G115">
-        <v>0.994</v>
-      </c>
-      <c r="H115">
-        <v>0.9872239809867935</v>
-      </c>
-      <c r="I115">
-        <v>1</v>
-      </c>
-      <c r="J115" t="b">
-        <v>1</v>
-      </c>
-      <c r="K115" t="s">
-        <v>28</v>
-      </c>
-      <c r="L115" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12">
-      <c r="A116" t="s">
-        <v>24</v>
-      </c>
-      <c r="B116" t="s">
-        <v>25</v>
-      </c>
-      <c r="C116">
-        <v>500</v>
-      </c>
-      <c r="D116">
-        <v>12</v>
-      </c>
-      <c r="E116">
-        <v>0</v>
-      </c>
-      <c r="F116">
-        <v>488</v>
-      </c>
-      <c r="G116">
-        <v>0.024</v>
-      </c>
-      <c r="H116">
-        <v>0.01057122713419567</v>
-      </c>
-      <c r="I116">
-        <v>0.03742877286580433</v>
-      </c>
-      <c r="J116" t="b">
-        <v>1</v>
-      </c>
-      <c r="K116" t="s">
-        <v>28</v>
-      </c>
-      <c r="L116" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12">
-      <c r="A117" t="s">
-        <v>24</v>
-      </c>
-      <c r="B117" t="s">
-        <v>26</v>
-      </c>
-      <c r="C117">
-        <v>500</v>
-      </c>
-      <c r="D117">
-        <v>494</v>
-      </c>
-      <c r="E117">
-        <v>0</v>
-      </c>
-      <c r="F117">
-        <v>6</v>
-      </c>
-      <c r="G117">
-        <v>0.988</v>
-      </c>
-      <c r="H117">
-        <v>0.9784462275337606</v>
-      </c>
-      <c r="I117">
-        <v>0.9975537724662393</v>
-      </c>
-      <c r="J117" t="b">
-        <v>1</v>
-      </c>
-      <c r="K117" t="s">
-        <v>28</v>
-      </c>
-      <c r="L117" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12">
-      <c r="A118" t="s">
-        <v>24</v>
-      </c>
-      <c r="B118" t="s">
-        <v>27</v>
-      </c>
-      <c r="C118">
-        <v>500</v>
-      </c>
-      <c r="D118">
-        <v>253</v>
-      </c>
-      <c r="E118">
-        <v>1</v>
-      </c>
-      <c r="F118">
-        <v>246</v>
-      </c>
-      <c r="G118">
-        <v>0.507</v>
-      </c>
-      <c r="H118">
-        <v>0.4631773714989907</v>
-      </c>
-      <c r="I118">
-        <v>0.5508226285010094</v>
-      </c>
-      <c r="J118" t="b">
-        <v>1</v>
-      </c>
-      <c r="K118" t="s">
-        <v>28</v>
-      </c>
-      <c r="L118" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12">
-      <c r="A119" t="s">
-        <v>25</v>
-      </c>
-      <c r="B119" t="s">
-        <v>26</v>
-      </c>
-      <c r="C119">
-        <v>500</v>
-      </c>
-      <c r="D119">
-        <v>250</v>
-      </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
-      <c r="F119">
-        <v>250</v>
-      </c>
-      <c r="G119">
-        <v>0.5</v>
-      </c>
-      <c r="H119">
-        <v>0.4561291748584872</v>
-      </c>
-      <c r="I119">
-        <v>0.5438708251415129</v>
-      </c>
-      <c r="J119" t="b">
-        <v>1</v>
-      </c>
-      <c r="K119" t="s">
-        <v>28</v>
-      </c>
-      <c r="L119" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12">
-      <c r="A120" t="s">
-        <v>25</v>
-      </c>
-      <c r="B120" t="s">
-        <v>27</v>
-      </c>
-      <c r="C120">
-        <v>500</v>
-      </c>
-      <c r="D120">
-        <v>253</v>
-      </c>
-      <c r="E120">
-        <v>0</v>
-      </c>
-      <c r="F120">
-        <v>247</v>
-      </c>
-      <c r="G120">
-        <v>0.506</v>
-      </c>
-      <c r="H120">
-        <v>0.4621323336716188</v>
-      </c>
-      <c r="I120">
-        <v>0.5498676663283812</v>
-      </c>
-      <c r="J120" t="b">
-        <v>1</v>
-      </c>
-      <c r="K120" t="s">
-        <v>28</v>
-      </c>
-      <c r="L120" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12">
-      <c r="A121" t="s">
-        <v>26</v>
-      </c>
-      <c r="B121" t="s">
-        <v>27</v>
-      </c>
-      <c r="C121">
-        <v>500</v>
-      </c>
-      <c r="D121">
-        <v>493</v>
-      </c>
-      <c r="E121">
-        <v>2</v>
-      </c>
-      <c r="F121">
-        <v>5</v>
-      </c>
-      <c r="G121">
-        <v>0.988</v>
-      </c>
-      <c r="H121">
-        <v>0.9788580105479012</v>
-      </c>
-      <c r="I121">
-        <v>0.9971419894520988</v>
-      </c>
-      <c r="J121" t="b">
-        <v>1</v>
-      </c>
-      <c r="K121" t="s">
-        <v>28</v>
-      </c>
-      <c r="L121" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="29">
   <si>
     <t>A</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>PPO_920</t>
+  </si>
+  <si>
+    <t>PPO_921</t>
   </si>
   <si>
     <t>center</t>
@@ -455,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -507,31 +510,31 @@
         <v>500</v>
       </c>
       <c r="D2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>0.994</v>
+        <v>0.992</v>
       </c>
       <c r="H2">
-        <v>0.9872239809867935</v>
+        <v>0.9841836026626924</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0.9998163973373075</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -545,31 +548,31 @@
         <v>500</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="G3">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.004516800347703959</v>
       </c>
       <c r="I3">
-        <v>0.008792975487946511</v>
+        <v>0.02548319965229604</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -583,31 +586,31 @@
         <v>500</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G4">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="H4">
-        <v>0.002858010547901262</v>
+        <v>0.005345981179194954</v>
       </c>
       <c r="I4">
-        <v>0.02114198945209874</v>
+        <v>0.02665401882080505</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -642,10 +645,10 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -680,10 +683,10 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -697,31 +700,31 @@
         <v>500</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="G7">
-        <v>0.006</v>
+        <v>0.022</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.009129762347397428</v>
       </c>
       <c r="I7">
-        <v>0.0127760190132064</v>
+        <v>0.03487023765260257</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -735,31 +738,31 @@
         <v>500</v>
       </c>
       <c r="D8">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G8">
-        <v>0.492</v>
+        <v>0.49</v>
       </c>
       <c r="H8">
-        <v>0.4481347906835411</v>
+        <v>0.4461379499011075</v>
       </c>
       <c r="I8">
-        <v>0.5358652093164589</v>
+        <v>0.5338620500988925</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -794,10 +797,10 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -811,69 +814,69 @@
         <v>500</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G10">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0.009538159551912971</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>500</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="G11">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>0.00369119620560452</v>
       </c>
       <c r="I11">
-        <v>0.008792975487946511</v>
+        <v>0.02430880379439548</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -881,37 +884,37 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>500</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="G12">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="H12">
-        <v>0.005345981179194954</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>0.02665401882080505</v>
+        <v>0.00592</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -919,37 +922,37 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>500</v>
       </c>
       <c r="D13">
-        <v>250</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>250</v>
+        <v>488</v>
       </c>
       <c r="G13">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="H13">
-        <v>0.4561291748584872</v>
+        <v>0.00835975470098493</v>
       </c>
       <c r="I13">
-        <v>0.5438708251415129</v>
+        <v>0.03164024529901507</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -957,37 +960,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>500</v>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>250</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>489</v>
+        <v>250</v>
       </c>
       <c r="G14">
-        <v>0.022</v>
+        <v>0.5</v>
       </c>
       <c r="H14">
-        <v>0.009129762347397428</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I14">
-        <v>0.03487023765260257</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -995,37 +998,37 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>500</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G15">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="H15">
-        <v>0.004990607908314969</v>
+        <v>0.006334649426270291</v>
       </c>
       <c r="I15">
-        <v>0.02700939209168503</v>
+        <v>0.02966535057372971</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1033,37 +1036,37 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>500</v>
       </c>
       <c r="D16">
-        <v>254</v>
+        <v>11</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>246</v>
+        <v>489</v>
       </c>
       <c r="G16">
-        <v>0.508</v>
+        <v>0.022</v>
       </c>
       <c r="H16">
-        <v>0.4641347906835411</v>
+        <v>0.009129762347397428</v>
       </c>
       <c r="I16">
-        <v>0.5518652093164589</v>
+        <v>0.03487023765260257</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1071,37 +1074,37 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>500</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>247</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>495</v>
+        <v>251</v>
       </c>
       <c r="G17">
-        <v>0.01</v>
+        <v>0.496</v>
       </c>
       <c r="H17">
-        <v>0.001269816025738696</v>
+        <v>0.4522184111315305</v>
       </c>
       <c r="I17">
-        <v>0.0187301839742613</v>
+        <v>0.5397815888684695</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1109,7 +1112,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>500</v>
@@ -1136,10 +1139,10 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1147,37 +1150,37 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>500</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G19">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="H19">
-        <v>0.001269816025738698</v>
+        <v>0.003256725293618782</v>
       </c>
       <c r="I19">
-        <v>0.0187301839742613</v>
+        <v>0.02274327470638122</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1185,37 +1188,37 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>500</v>
       </c>
       <c r="D20">
-        <v>246</v>
+        <v>4</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>254</v>
+        <v>496</v>
       </c>
       <c r="G20">
-        <v>0.492</v>
+        <v>0.008</v>
       </c>
       <c r="H20">
-        <v>0.4481347906835411</v>
+        <v>0.0001836026626924024</v>
       </c>
       <c r="I20">
-        <v>0.5358652093164589</v>
+        <v>0.0158163973373076</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1223,7 +1226,7 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>500</v>
@@ -1250,10 +1253,10 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1261,113 +1264,113 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>500</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>248</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>496</v>
+        <v>252</v>
       </c>
       <c r="G22">
-        <v>0.007</v>
+        <v>0.496</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I22">
-        <v>0.01404724417776211</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>500</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="G23">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="H23">
-        <v>0.00369119620560452</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>0.02430880379439548</v>
+        <v>0.00592</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>500</v>
       </c>
       <c r="D24">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>250</v>
+        <v>497</v>
       </c>
       <c r="G24">
-        <v>0.5</v>
+        <v>0.006</v>
       </c>
       <c r="H24">
-        <v>0.4561291748584872</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>0.5438708251415129</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1375,37 +1378,37 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>500</v>
       </c>
       <c r="D25">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G25">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="H25">
-        <v>0.009129762347397428</v>
+        <v>0.001269816025738698</v>
       </c>
       <c r="I25">
-        <v>0.03487023765260257</v>
+        <v>0.0187301839742613</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1413,7 +1416,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C26">
         <v>500</v>
@@ -1440,10 +1443,10 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1451,7 +1454,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C27">
         <v>500</v>
@@ -1460,28 +1463,28 @@
         <v>5</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G27">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="H27">
-        <v>0.002858010547901262</v>
+        <v>0.001269816025738698</v>
       </c>
       <c r="I27">
-        <v>0.02114198945209874</v>
+        <v>0.0187301839742613</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1489,37 +1492,37 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C28">
         <v>500</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>496</v>
+        <v>250</v>
       </c>
       <c r="G28">
-        <v>0.007</v>
+        <v>0.5</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I28">
-        <v>0.01404724417776211</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1527,37 +1530,37 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C29">
         <v>500</v>
       </c>
       <c r="D29">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>250</v>
+        <v>493</v>
       </c>
       <c r="G29">
-        <v>0.5</v>
+        <v>0.013</v>
       </c>
       <c r="H29">
-        <v>0.4561291748584872</v>
+        <v>0.003256725293618782</v>
       </c>
       <c r="I29">
-        <v>0.5438708251415129</v>
+        <v>0.02274327470638122</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1565,37 +1568,37 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C30">
         <v>500</v>
       </c>
       <c r="D30">
-        <v>251</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>249</v>
+        <v>494</v>
       </c>
       <c r="G30">
-        <v>0.502</v>
+        <v>0.011</v>
       </c>
       <c r="H30">
-        <v>0.4581295258264922</v>
+        <v>0.002061110791571407</v>
       </c>
       <c r="I30">
-        <v>0.5458704741735079</v>
+        <v>0.01993888920842859</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1603,37 +1606,37 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C31">
         <v>500</v>
       </c>
       <c r="D31">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G31">
-        <v>0.49</v>
+        <v>0.494</v>
       </c>
       <c r="H31">
-        <v>0.4461379499011075</v>
+        <v>0.4501323336716188</v>
       </c>
       <c r="I31">
-        <v>0.5338620500988925</v>
+        <v>0.5378676663283812</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1641,37 +1644,37 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32">
         <v>500</v>
       </c>
       <c r="D32">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G32">
-        <v>0.498</v>
+        <v>0.504</v>
       </c>
       <c r="H32">
-        <v>0.4541295258264922</v>
+        <v>0.4601305787473543</v>
       </c>
       <c r="I32">
-        <v>0.5418704741735079</v>
+        <v>0.5478694212526457</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1679,45 +1682,45 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C33">
         <v>500</v>
       </c>
       <c r="D33">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G33">
-        <v>0.499</v>
+        <v>0.494</v>
       </c>
       <c r="H33">
-        <v>0.4551731554706159</v>
+        <v>0.4501323336716188</v>
       </c>
       <c r="I33">
-        <v>0.5428268445293841</v>
+        <v>0.5378676663283812</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C34">
         <v>500</v>
@@ -1744,86 +1747,86 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C35">
         <v>500</v>
       </c>
       <c r="D35">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G35">
-        <v>0.495</v>
+        <v>0.5</v>
       </c>
       <c r="H35">
-        <v>0.4511752634341045</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I35">
-        <v>0.5388247365658955</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C36">
         <v>500</v>
       </c>
       <c r="D36">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G36">
-        <v>0.496</v>
+        <v>0.502</v>
       </c>
       <c r="H36">
-        <v>0.4521305787473543</v>
+        <v>0.4581295258264922</v>
       </c>
       <c r="I36">
-        <v>0.5398694212526457</v>
+        <v>0.5458704741735079</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1831,37 +1834,37 @@
         <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C37">
         <v>500</v>
       </c>
       <c r="D37">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G37">
-        <v>0.492</v>
+        <v>0.49</v>
       </c>
       <c r="H37">
-        <v>0.4481347906835411</v>
+        <v>0.4461379499011075</v>
       </c>
       <c r="I37">
-        <v>0.5358652093164589</v>
+        <v>0.5338620500988925</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -1869,37 +1872,37 @@
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C38">
         <v>500</v>
       </c>
       <c r="D38">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>497</v>
+        <v>253</v>
       </c>
       <c r="G38">
-        <v>0.006</v>
+        <v>0.493</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>0.4491773714989907</v>
       </c>
       <c r="I38">
-        <v>0.0127760190132064</v>
+        <v>0.5368226285010094</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -1907,37 +1910,37 @@
         <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C39">
         <v>500</v>
       </c>
       <c r="D39">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="G39">
-        <v>0.484</v>
+        <v>0.496</v>
       </c>
       <c r="H39">
-        <v>0.4401516424741424</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I39">
-        <v>0.5278483575258576</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -1945,37 +1948,37 @@
         <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C40">
         <v>500</v>
       </c>
       <c r="D40">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G40">
-        <v>0.49</v>
+        <v>0.496</v>
       </c>
       <c r="H40">
-        <v>0.4461379499011075</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I40">
-        <v>0.5338620500988925</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -1983,189 +1986,189 @@
         <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C41">
         <v>500</v>
       </c>
       <c r="D41">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41">
-        <v>252</v>
+        <v>500</v>
       </c>
       <c r="G41">
-        <v>0.496</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>0.4521305787473543</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>0.5398694212526457</v>
+        <v>0</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C42">
         <v>500</v>
       </c>
       <c r="D42">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E42">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>257</v>
       </c>
       <c r="G42">
-        <v>0.743</v>
+        <v>0.486</v>
       </c>
       <c r="H42">
-        <v>0.7200440274317749</v>
+        <v>0.4421463755939478</v>
       </c>
       <c r="I42">
-        <v>0.7659559725682251</v>
+        <v>0.5298536244060521</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C43">
         <v>500</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>499</v>
+        <v>260</v>
       </c>
       <c r="G43">
-        <v>0.002</v>
+        <v>0.48</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>0.4361642855685066</v>
       </c>
       <c r="I43">
-        <v>0.00592</v>
+        <v>0.5238357144314933</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C44">
         <v>500</v>
       </c>
       <c r="D44">
-        <v>7</v>
+        <v>246</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>493</v>
+        <v>254</v>
       </c>
       <c r="G44">
-        <v>0.014</v>
+        <v>0.492</v>
       </c>
       <c r="H44">
-        <v>0.00369119620560452</v>
+        <v>0.4481347906835411</v>
       </c>
       <c r="I44">
-        <v>0.02430880379439548</v>
+        <v>0.5358652093164589</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C45">
         <v>500</v>
       </c>
       <c r="D45">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="G45">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="H45">
-        <v>0.007182857599697888</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>0.03081714240030211</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2173,37 +2176,37 @@
         <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C46">
         <v>500</v>
       </c>
       <c r="D46">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="F46">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="G46">
-        <v>0.502</v>
+        <v>0.744</v>
       </c>
       <c r="H46">
-        <v>0.4581295258264922</v>
+        <v>0.721210130296067</v>
       </c>
       <c r="I46">
-        <v>0.5458704741735079</v>
+        <v>0.766789869703933</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2211,37 +2214,37 @@
         <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C47">
         <v>500</v>
       </c>
       <c r="D47">
-        <v>496</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>500</v>
       </c>
       <c r="G47">
-        <v>0.992</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>0.9841836026626924</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>0.9998163973373075</v>
+        <v>0</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2249,227 +2252,227 @@
         <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C48">
         <v>500</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G48">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="H48">
-        <v>0.0001836026626924024</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>0.0158163973373076</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C49">
         <v>500</v>
       </c>
       <c r="D49">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>252</v>
+        <v>499</v>
       </c>
       <c r="G49">
-        <v>0.496</v>
+        <v>0.002</v>
       </c>
       <c r="H49">
-        <v>0.4521305787473543</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>0.5398694212526457</v>
+        <v>0.00592</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C50">
         <v>500</v>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>245</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>494</v>
+        <v>255</v>
       </c>
       <c r="G50">
-        <v>0.012</v>
+        <v>0.49</v>
       </c>
       <c r="H50">
-        <v>0.002446227533760637</v>
+        <v>0.4461379499011075</v>
       </c>
       <c r="I50">
-        <v>0.02155377246623937</v>
+        <v>0.5338620500988924</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C51">
         <v>500</v>
       </c>
       <c r="D51">
-        <v>249</v>
+        <v>494</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>251</v>
+        <v>6</v>
       </c>
       <c r="G51">
-        <v>0.498</v>
+        <v>0.988</v>
       </c>
       <c r="H51">
-        <v>0.4541295258264922</v>
+        <v>0.9784462275337606</v>
       </c>
       <c r="I51">
-        <v>0.5418704741735079</v>
+        <v>0.9975537724662393</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C52">
         <v>500</v>
       </c>
       <c r="D52">
-        <v>492</v>
+        <v>6</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>6</v>
+        <v>494</v>
       </c>
       <c r="G52">
-        <v>0.986</v>
+        <v>0.012</v>
       </c>
       <c r="H52">
-        <v>0.9760716145080404</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I52">
-        <v>0.9959283854919596</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C53">
         <v>500</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G53">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>0.001269816025738698</v>
       </c>
       <c r="I53">
-        <v>0.0127760190132064</v>
+        <v>0.0187301839742613</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2477,37 +2480,37 @@
         <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C54">
         <v>500</v>
       </c>
       <c r="D54">
+        <v>248</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
         <v>252</v>
       </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <v>248</v>
-      </c>
       <c r="G54">
-        <v>0.504</v>
+        <v>0.496</v>
       </c>
       <c r="H54">
-        <v>0.4601305787473543</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I54">
-        <v>0.5478694212526457</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -2515,37 +2518,37 @@
         <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C55">
         <v>500</v>
       </c>
       <c r="D55">
-        <v>251</v>
+        <v>6</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>249</v>
+        <v>494</v>
       </c>
       <c r="G55">
-        <v>0.502</v>
+        <v>0.012</v>
       </c>
       <c r="H55">
-        <v>0.4581295258264922</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I55">
-        <v>0.5458704741735079</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -2553,37 +2556,37 @@
         <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C56">
         <v>500</v>
       </c>
       <c r="D56">
-        <v>6</v>
+        <v>249</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>494</v>
+        <v>251</v>
       </c>
       <c r="G56">
-        <v>0.012</v>
+        <v>0.498</v>
       </c>
       <c r="H56">
-        <v>0.002446227533760637</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I56">
-        <v>0.02155377246623937</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -2591,37 +2594,37 @@
         <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C57">
         <v>500</v>
       </c>
       <c r="D57">
+        <v>492</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="F57">
         <v>6</v>
       </c>
-      <c r="E57">
-        <v>1</v>
-      </c>
-      <c r="F57">
-        <v>493</v>
-      </c>
       <c r="G57">
-        <v>0.013</v>
+        <v>0.986</v>
       </c>
       <c r="H57">
-        <v>0.003256725293618782</v>
+        <v>0.9760716145080404</v>
       </c>
       <c r="I57">
-        <v>0.02274327470638122</v>
+        <v>0.9959283854919596</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -2629,37 +2632,37 @@
         <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C58">
         <v>500</v>
       </c>
       <c r="D58">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>249</v>
+        <v>497</v>
       </c>
       <c r="G58">
-        <v>0.501</v>
+        <v>0.006</v>
       </c>
       <c r="H58">
-        <v>0.4571731554706159</v>
+        <v>0</v>
       </c>
       <c r="I58">
-        <v>0.5448268445293841</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -2667,37 +2670,37 @@
         <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C59">
         <v>500</v>
       </c>
       <c r="D59">
+        <v>252</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
         <v>248</v>
       </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>252</v>
-      </c>
       <c r="G59">
-        <v>0.496</v>
+        <v>0.504</v>
       </c>
       <c r="H59">
-        <v>0.4521305787473543</v>
+        <v>0.4601305787473543</v>
       </c>
       <c r="I59">
-        <v>0.5398694212526457</v>
+        <v>0.5478694212526457</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -2705,37 +2708,37 @@
         <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C60">
         <v>500</v>
       </c>
       <c r="D60">
-        <v>497</v>
+        <v>251</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="G60">
-        <v>0.994</v>
+        <v>0.502</v>
       </c>
       <c r="H60">
-        <v>0.9872239809867935</v>
+        <v>0.4581295258264922</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>0.5458704741735079</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -2743,531 +2746,531 @@
         <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C61">
         <v>500</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G61">
-        <v>0.004</v>
+        <v>0.012</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I61">
-        <v>0.009538159551912971</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C62">
         <v>500</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E62">
-        <v>249</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>251</v>
+        <v>493</v>
       </c>
       <c r="G62">
-        <v>0.249</v>
+        <v>0.013</v>
       </c>
       <c r="H62">
-        <v>0.2270647629132461</v>
+        <v>0.003256725293618782</v>
       </c>
       <c r="I62">
-        <v>0.2709352370867539</v>
+        <v>0.02274327470638122</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C63">
         <v>500</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>499</v>
+        <v>249</v>
       </c>
       <c r="G63">
-        <v>0.002</v>
+        <v>0.501</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>0.4571731554706159</v>
       </c>
       <c r="I63">
-        <v>0.00592</v>
+        <v>0.5448268445293841</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C64">
         <v>500</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="E64">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="F64">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G64">
-        <v>0.249</v>
+        <v>0.496</v>
       </c>
       <c r="H64">
-        <v>0.2270647629132461</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I64">
-        <v>0.2709352370867539</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C65">
         <v>500</v>
       </c>
       <c r="D65">
-        <v>245</v>
+        <v>497</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>255</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>0.49</v>
+        <v>0.994</v>
       </c>
       <c r="H65">
-        <v>0.4461379499011075</v>
+        <v>0.9872239809867935</v>
       </c>
       <c r="I65">
-        <v>0.5338620500988924</v>
+        <v>1</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C66">
         <v>500</v>
       </c>
       <c r="D66">
-        <v>249</v>
+        <v>2</v>
       </c>
       <c r="E66">
         <v>0</v>
       </c>
       <c r="F66">
-        <v>251</v>
+        <v>498</v>
       </c>
       <c r="G66">
-        <v>0.498</v>
+        <v>0.004</v>
       </c>
       <c r="H66">
-        <v>0.4541295258264922</v>
+        <v>0</v>
       </c>
       <c r="I66">
-        <v>0.5418704741735079</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C67">
         <v>500</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="G67">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="H67">
-        <v>0.0001836026626924024</v>
+        <v>0.004516800347703961</v>
       </c>
       <c r="I67">
-        <v>0.0158163973373076</v>
+        <v>0.02548319965229604</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C68">
         <v>500</v>
       </c>
       <c r="D68">
-        <v>248</v>
+        <v>5</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>245</v>
       </c>
       <c r="F68">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G68">
-        <v>0.497</v>
+        <v>0.255</v>
       </c>
       <c r="H68">
-        <v>0.4531738581138466</v>
+        <v>0.2322082724285459</v>
       </c>
       <c r="I68">
-        <v>0.5408261418861534</v>
+        <v>0.2777917275714542</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B69" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C69">
         <v>500</v>
       </c>
       <c r="D69">
-        <v>249</v>
+        <v>7</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69">
-        <v>251</v>
+        <v>493</v>
       </c>
       <c r="G69">
-        <v>0.498</v>
+        <v>0.014</v>
       </c>
       <c r="H69">
-        <v>0.4541295258264922</v>
+        <v>0.00369119620560452</v>
       </c>
       <c r="I69">
-        <v>0.5418704741735079</v>
+        <v>0.02430880379439548</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C70">
         <v>500</v>
       </c>
       <c r="D70">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="F70">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G70">
-        <v>0.498</v>
+        <v>0.248</v>
       </c>
       <c r="H70">
-        <v>0.4541295258264922</v>
+        <v>0.2255449933902551</v>
       </c>
       <c r="I70">
-        <v>0.5418704741735079</v>
+        <v>0.2704550066097449</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C71">
         <v>500</v>
       </c>
       <c r="D71">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G71">
-        <v>0.498</v>
+        <v>0.494</v>
       </c>
       <c r="H71">
-        <v>0.4541295258264922</v>
+        <v>0.4501323336716188</v>
       </c>
       <c r="I71">
-        <v>0.5418704741735079</v>
+        <v>0.5378676663283812</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B72" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C72">
         <v>500</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>500</v>
+        <v>252</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>0.496</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C73">
         <v>500</v>
       </c>
       <c r="D73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73">
         <v>494</v>
       </c>
       <c r="G73">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="H73">
-        <v>0.002446227533760637</v>
+        <v>0.002061110791571407</v>
       </c>
       <c r="I73">
-        <v>0.02155377246623937</v>
+        <v>0.01993888920842859</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C74">
         <v>500</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>249</v>
       </c>
       <c r="E74">
         <v>0</v>
       </c>
       <c r="F74">
-        <v>498</v>
+        <v>251</v>
       </c>
       <c r="G74">
-        <v>0.004</v>
+        <v>0.498</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I74">
-        <v>0.009538159551912971</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L74" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3275,37 +3278,37 @@
         <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C75">
         <v>500</v>
       </c>
       <c r="D75">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G75">
-        <v>0.492</v>
+        <v>0.498</v>
       </c>
       <c r="H75">
-        <v>0.4481347906835411</v>
+        <v>0.4542173560984032</v>
       </c>
       <c r="I75">
-        <v>0.5358652093164589</v>
+        <v>0.5417826439015968</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3313,7 +3316,7 @@
         <v>19</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C76">
         <v>500</v>
@@ -3340,10 +3343,10 @@
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L76" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3351,607 +3354,1139 @@
         <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C77">
         <v>500</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77">
-        <v>498</v>
+        <v>249</v>
       </c>
       <c r="G77">
-        <v>0.004</v>
+        <v>0.501</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>0.4571731554706159</v>
       </c>
       <c r="I77">
-        <v>0.009538159551912971</v>
+        <v>0.5448268445293841</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L77" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B78" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C78">
         <v>500</v>
       </c>
       <c r="D78">
-        <v>497</v>
+        <v>251</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="G78">
-        <v>0.994</v>
+        <v>0.502</v>
       </c>
       <c r="H78">
-        <v>0.9872239809867935</v>
+        <v>0.4581295258264922</v>
       </c>
       <c r="I78">
-        <v>1</v>
+        <v>0.5458704741735079</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" t="s">
         <v>20</v>
       </c>
-      <c r="B79" t="s">
-        <v>22</v>
-      </c>
       <c r="C79">
         <v>500</v>
       </c>
       <c r="D79">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79">
-        <v>249</v>
+        <v>500</v>
       </c>
       <c r="G79">
-        <v>0.501</v>
+        <v>0</v>
       </c>
       <c r="H79">
-        <v>0.4571731554706159</v>
+        <v>0</v>
       </c>
       <c r="I79">
-        <v>0.5448268445293841</v>
+        <v>0</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L79" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C80">
         <v>500</v>
       </c>
       <c r="D80">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E80">
         <v>0</v>
       </c>
       <c r="F80">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="G80">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="H80">
-        <v>0.004990607908314968</v>
+        <v>0</v>
       </c>
       <c r="I80">
-        <v>0.02700939209168503</v>
+        <v>0.00592</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C81">
         <v>500</v>
       </c>
       <c r="D81">
-        <v>252</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81">
-        <v>247</v>
+        <v>499</v>
       </c>
       <c r="G81">
-        <v>0.505</v>
+        <v>0.002</v>
       </c>
       <c r="H81">
-        <v>0.4611752634341045</v>
+        <v>0</v>
       </c>
       <c r="I81">
-        <v>0.5488247365658955</v>
+        <v>0.00592</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L81" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B82" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C82">
         <v>500</v>
       </c>
       <c r="D82">
-        <v>495</v>
+        <v>244</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>5</v>
+        <v>256</v>
       </c>
       <c r="G82">
-        <v>0.99</v>
+        <v>0.488</v>
       </c>
       <c r="H82">
-        <v>0.9812698160257387</v>
+        <v>0.444141811476063</v>
       </c>
       <c r="I82">
-        <v>0.9987301839742613</v>
+        <v>0.5318581885239371</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L82" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C83">
         <v>500</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>248</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83">
-        <v>496</v>
+        <v>252</v>
       </c>
       <c r="G83">
-        <v>0.007</v>
+        <v>0.496</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I83">
-        <v>0.01404724417776211</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L83" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B84" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C84">
         <v>500</v>
       </c>
       <c r="D84">
-        <v>245</v>
+        <v>3</v>
       </c>
       <c r="E84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F84">
-        <v>253</v>
+        <v>497</v>
       </c>
       <c r="G84">
-        <v>0.492</v>
+        <v>0.006</v>
       </c>
       <c r="H84">
-        <v>0.448222631518302</v>
+        <v>0</v>
       </c>
       <c r="I84">
-        <v>0.535777368481698</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L84" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C85">
         <v>500</v>
       </c>
       <c r="D85">
-        <v>252</v>
+        <v>2</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85">
-        <v>248</v>
+        <v>498</v>
       </c>
       <c r="G85">
-        <v>0.504</v>
+        <v>0.004</v>
       </c>
       <c r="H85">
-        <v>0.4601305787473543</v>
+        <v>0</v>
       </c>
       <c r="I85">
-        <v>0.5478694212526457</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L85" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
+        <v>20</v>
+      </c>
+      <c r="B86" t="s">
         <v>21</v>
       </c>
-      <c r="B86" t="s">
-        <v>25</v>
-      </c>
       <c r="C86">
         <v>500</v>
       </c>
       <c r="D86">
-        <v>249</v>
+        <v>497</v>
       </c>
       <c r="E86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="G86">
-        <v>0.499</v>
+        <v>0.994</v>
       </c>
       <c r="H86">
-        <v>0.4551731554706159</v>
+        <v>0.9872239809867935</v>
       </c>
       <c r="I86">
-        <v>0.5428268445293841</v>
+        <v>1</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L86" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
+        <v>20</v>
+      </c>
+      <c r="B87" t="s">
         <v>22</v>
       </c>
-      <c r="B87" t="s">
-        <v>23</v>
-      </c>
       <c r="C87">
         <v>500</v>
       </c>
       <c r="D87">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G87">
-        <v>0.501</v>
+        <v>0.498</v>
       </c>
       <c r="H87">
-        <v>0.4571731554706159</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I87">
-        <v>0.5448268445293841</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L87" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C88">
         <v>500</v>
       </c>
       <c r="D88">
-        <v>247</v>
+        <v>6</v>
       </c>
       <c r="E88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88">
-        <v>252</v>
+        <v>494</v>
       </c>
       <c r="G88">
-        <v>0.495</v>
+        <v>0.012</v>
       </c>
       <c r="H88">
-        <v>0.4511752634341045</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I88">
-        <v>0.5388247365658955</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L88" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C89">
         <v>500</v>
       </c>
       <c r="D89">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G89">
-        <v>0.5</v>
+        <v>0.497</v>
       </c>
       <c r="H89">
-        <v>0.4561291748584872</v>
+        <v>0.4531738581138466</v>
       </c>
       <c r="I89">
-        <v>0.5438708251415129</v>
+        <v>0.5408261418861534</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L89" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B90" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C90">
         <v>500</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>497</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90">
-        <v>496</v>
+        <v>3</v>
       </c>
       <c r="G90">
-        <v>0.008</v>
+        <v>0.994</v>
       </c>
       <c r="H90">
-        <v>0.0001836026626924024</v>
+        <v>0.9872239809867935</v>
       </c>
       <c r="I90">
-        <v>0.0158163973373076</v>
+        <v>1</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L90" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B91" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C91">
         <v>500</v>
       </c>
       <c r="D91">
-        <v>493</v>
+        <v>248</v>
       </c>
       <c r="E91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F91">
-        <v>4</v>
+        <v>248</v>
       </c>
       <c r="G91">
-        <v>0.989</v>
+        <v>0.5</v>
       </c>
       <c r="H91">
-        <v>0.9805026390516718</v>
+        <v>0.4563050105365796</v>
       </c>
       <c r="I91">
-        <v>0.9974973609483282</v>
+        <v>0.5436949894634203</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L91" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
+        <v>21</v>
+      </c>
+      <c r="B92" t="s">
+        <v>22</v>
+      </c>
+      <c r="C92">
+        <v>500</v>
+      </c>
+      <c r="D92">
+        <v>3</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92">
+        <v>496</v>
+      </c>
+      <c r="G92">
+        <v>0.007</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0.01404724417776211</v>
+      </c>
+      <c r="J92" t="b">
+        <v>1</v>
+      </c>
+      <c r="K92" t="s">
+        <v>27</v>
+      </c>
+      <c r="L92" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" t="s">
+        <v>21</v>
+      </c>
+      <c r="B93" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93">
+        <v>500</v>
+      </c>
+      <c r="D93">
+        <v>250</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>250</v>
+      </c>
+      <c r="G93">
+        <v>0.5</v>
+      </c>
+      <c r="H93">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I93">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J93" t="b">
+        <v>1</v>
+      </c>
+      <c r="K93" t="s">
+        <v>27</v>
+      </c>
+      <c r="L93" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" t="s">
+        <v>21</v>
+      </c>
+      <c r="B94" t="s">
         <v>24</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C94">
+        <v>500</v>
+      </c>
+      <c r="D94">
+        <v>251</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>249</v>
+      </c>
+      <c r="G94">
+        <v>0.502</v>
+      </c>
+      <c r="H94">
+        <v>0.4581295258264922</v>
+      </c>
+      <c r="I94">
+        <v>0.5458704741735079</v>
+      </c>
+      <c r="J94" t="b">
+        <v>1</v>
+      </c>
+      <c r="K94" t="s">
+        <v>27</v>
+      </c>
+      <c r="L94" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" t="s">
+        <v>21</v>
+      </c>
+      <c r="B95" t="s">
         <v>25</v>
       </c>
-      <c r="C92">
-        <v>500</v>
-      </c>
-      <c r="D92">
+      <c r="C95">
+        <v>500</v>
+      </c>
+      <c r="D95">
+        <v>250</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>250</v>
+      </c>
+      <c r="G95">
+        <v>0.5</v>
+      </c>
+      <c r="H95">
+        <v>0.4561291748584872</v>
+      </c>
+      <c r="I95">
+        <v>0.5438708251415129</v>
+      </c>
+      <c r="J95" t="b">
+        <v>1</v>
+      </c>
+      <c r="K95" t="s">
+        <v>27</v>
+      </c>
+      <c r="L95" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" t="s">
+        <v>21</v>
+      </c>
+      <c r="B96" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96">
+        <v>500</v>
+      </c>
+      <c r="D96">
+        <v>7</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96">
+        <v>492</v>
+      </c>
+      <c r="G96">
+        <v>0.015</v>
+      </c>
+      <c r="H96">
+        <v>0.004516800347703959</v>
+      </c>
+      <c r="I96">
+        <v>0.02548319965229604</v>
+      </c>
+      <c r="J96" t="b">
+        <v>1</v>
+      </c>
+      <c r="K96" t="s">
+        <v>27</v>
+      </c>
+      <c r="L96" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" t="s">
+        <v>23</v>
+      </c>
+      <c r="C97">
+        <v>500</v>
+      </c>
+      <c r="D97">
+        <v>251</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
         <v>249</v>
       </c>
-      <c r="E92">
+      <c r="G97">
+        <v>0.502</v>
+      </c>
+      <c r="H97">
+        <v>0.4581295258264922</v>
+      </c>
+      <c r="I97">
+        <v>0.5458704741735079</v>
+      </c>
+      <c r="J97" t="b">
+        <v>1</v>
+      </c>
+      <c r="K97" t="s">
+        <v>27</v>
+      </c>
+      <c r="L97" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98">
+        <v>500</v>
+      </c>
+      <c r="D98">
+        <v>249</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <v>250</v>
+      </c>
+      <c r="G98">
+        <v>0.499</v>
+      </c>
+      <c r="H98">
+        <v>0.4551731554706159</v>
+      </c>
+      <c r="I98">
+        <v>0.5428268445293841</v>
+      </c>
+      <c r="J98" t="b">
+        <v>1</v>
+      </c>
+      <c r="K98" t="s">
+        <v>27</v>
+      </c>
+      <c r="L98" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99">
+        <v>500</v>
+      </c>
+      <c r="D99">
+        <v>250</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="F99">
+        <v>249</v>
+      </c>
+      <c r="G99">
+        <v>0.501</v>
+      </c>
+      <c r="H99">
+        <v>0.4571731554706159</v>
+      </c>
+      <c r="I99">
+        <v>0.5448268445293841</v>
+      </c>
+      <c r="J99" t="b">
+        <v>1</v>
+      </c>
+      <c r="K99" t="s">
+        <v>27</v>
+      </c>
+      <c r="L99" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" t="s">
+        <v>22</v>
+      </c>
+      <c r="B100" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100">
+        <v>500</v>
+      </c>
+      <c r="D100">
+        <v>246</v>
+      </c>
+      <c r="E100">
+        <v>3</v>
+      </c>
+      <c r="F100">
+        <v>251</v>
+      </c>
+      <c r="G100">
+        <v>0.495</v>
+      </c>
+      <c r="H100">
+        <v>0.4512631855540924</v>
+      </c>
+      <c r="I100">
+        <v>0.5387368144459076</v>
+      </c>
+      <c r="J100" t="b">
+        <v>1</v>
+      </c>
+      <c r="K100" t="s">
+        <v>27</v>
+      </c>
+      <c r="L100" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101">
+        <v>500</v>
+      </c>
+      <c r="D101">
+        <v>6</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101">
+        <v>493</v>
+      </c>
+      <c r="G101">
+        <v>0.013</v>
+      </c>
+      <c r="H101">
+        <v>0.003256725293618782</v>
+      </c>
+      <c r="I101">
+        <v>0.02274327470638122</v>
+      </c>
+      <c r="J101" t="b">
+        <v>1</v>
+      </c>
+      <c r="K101" t="s">
+        <v>27</v>
+      </c>
+      <c r="L101" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" t="s">
+        <v>23</v>
+      </c>
+      <c r="B102" t="s">
+        <v>25</v>
+      </c>
+      <c r="C102">
+        <v>500</v>
+      </c>
+      <c r="D102">
+        <v>491</v>
+      </c>
+      <c r="E102">
         <v>2</v>
       </c>
-      <c r="F92">
+      <c r="F102">
+        <v>7</v>
+      </c>
+      <c r="G102">
+        <v>0.984</v>
+      </c>
+      <c r="H102">
+        <v>0.9733459811791949</v>
+      </c>
+      <c r="I102">
+        <v>0.9946540188208051</v>
+      </c>
+      <c r="J102" t="b">
+        <v>1</v>
+      </c>
+      <c r="K102" t="s">
+        <v>27</v>
+      </c>
+      <c r="L102" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" t="s">
+        <v>23</v>
+      </c>
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103">
+        <v>500</v>
+      </c>
+      <c r="D103">
+        <v>251</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+      <c r="F103">
+        <v>248</v>
+      </c>
+      <c r="G103">
+        <v>0.503</v>
+      </c>
+      <c r="H103">
+        <v>0.4591738581138466</v>
+      </c>
+      <c r="I103">
+        <v>0.5468261418861534</v>
+      </c>
+      <c r="J103" t="b">
+        <v>1</v>
+      </c>
+      <c r="K103" t="s">
+        <v>27</v>
+      </c>
+      <c r="L103" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" t="s">
+        <v>24</v>
+      </c>
+      <c r="B104" t="s">
+        <v>25</v>
+      </c>
+      <c r="C104">
+        <v>500</v>
+      </c>
+      <c r="D104">
+        <v>250</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="F104">
         <v>249</v>
       </c>
-      <c r="G92">
-        <v>0.5</v>
-      </c>
-      <c r="H92">
-        <v>0.4562170044263437</v>
-      </c>
-      <c r="I92">
-        <v>0.5437829955736563</v>
-      </c>
-      <c r="J92" t="b">
-        <v>1</v>
-      </c>
-      <c r="K92" t="s">
+      <c r="G104">
+        <v>0.501</v>
+      </c>
+      <c r="H104">
+        <v>0.4571731554706159</v>
+      </c>
+      <c r="I104">
+        <v>0.5448268445293841</v>
+      </c>
+      <c r="J104" t="b">
+        <v>1</v>
+      </c>
+      <c r="K104" t="s">
+        <v>27</v>
+      </c>
+      <c r="L104" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" t="s">
+        <v>24</v>
+      </c>
+      <c r="B105" t="s">
         <v>26</v>
       </c>
-      <c r="L92" t="s">
-        <v>27</v>
+      <c r="C105">
+        <v>500</v>
+      </c>
+      <c r="D105">
+        <v>249</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="F105">
+        <v>250</v>
+      </c>
+      <c r="G105">
+        <v>0.499</v>
+      </c>
+      <c r="H105">
+        <v>0.4551731554706159</v>
+      </c>
+      <c r="I105">
+        <v>0.5428268445293841</v>
+      </c>
+      <c r="J105" t="b">
+        <v>1</v>
+      </c>
+      <c r="K105" t="s">
+        <v>27</v>
+      </c>
+      <c r="L105" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106">
+        <v>500</v>
+      </c>
+      <c r="D106">
+        <v>250</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="F106">
+        <v>248</v>
+      </c>
+      <c r="G106">
+        <v>0.502</v>
+      </c>
+      <c r="H106">
+        <v>0.4582173560984033</v>
+      </c>
+      <c r="I106">
+        <v>0.5457826439015967</v>
+      </c>
+      <c r="J106" t="b">
+        <v>1</v>
+      </c>
+      <c r="K106" t="s">
+        <v>27</v>
+      </c>
+      <c r="L106" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="28">
   <si>
     <t>A</t>
   </si>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>PPO_915</t>
-  </si>
-  <si>
-    <t>PPO_918</t>
   </si>
   <si>
     <t>PPO_919</t>
@@ -458,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -510,31 +507,31 @@
         <v>500</v>
       </c>
       <c r="D2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>0.992</v>
+        <v>0.994</v>
       </c>
       <c r="H2">
-        <v>0.9841836026626924</v>
+        <v>0.9872239809867935</v>
       </c>
       <c r="I2">
-        <v>0.9998163973373075</v>
+        <v>1</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -548,31 +545,31 @@
         <v>500</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="G3">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="H3">
-        <v>0.004516800347703959</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.02548319965229604</v>
+        <v>0.008792975487946511</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -586,31 +583,31 @@
         <v>500</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="G4">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="H4">
-        <v>0.005345981179194954</v>
+        <v>0.002858010547901262</v>
       </c>
       <c r="I4">
-        <v>0.02665401882080505</v>
+        <v>0.02114198945209874</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -645,10 +642,10 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -683,10 +680,10 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -700,31 +697,31 @@
         <v>500</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="G7">
-        <v>0.022</v>
+        <v>0.006</v>
       </c>
       <c r="H7">
-        <v>0.009129762347397428</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.03487023765260257</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -738,31 +735,31 @@
         <v>500</v>
       </c>
       <c r="D8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G8">
-        <v>0.49</v>
+        <v>0.492</v>
       </c>
       <c r="H8">
-        <v>0.4461379499011075</v>
+        <v>0.4481347906835411</v>
       </c>
       <c r="I8">
-        <v>0.5338620500988925</v>
+        <v>0.5358652093164589</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -776,31 +773,31 @@
         <v>500</v>
       </c>
       <c r="D9">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>250</v>
+        <v>494</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.012</v>
       </c>
       <c r="H9">
-        <v>0.4561291748584872</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I9">
-        <v>0.5438708251415129</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -814,69 +811,69 @@
         <v>500</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G10">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0.0127760190132064</v>
+        <v>0.00592</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
       <c r="C11">
         <v>500</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="G11">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="H11">
-        <v>0.00369119620560452</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0.02430880379439548</v>
+        <v>0.008792975487946511</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -884,37 +881,37 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>500</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="G12">
-        <v>0.002</v>
+        <v>0.016</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>0.005345981179194954</v>
       </c>
       <c r="I12">
-        <v>0.00592</v>
+        <v>0.02665401882080505</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -922,37 +919,37 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>500</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>488</v>
+        <v>250</v>
       </c>
       <c r="G13">
-        <v>0.02</v>
+        <v>0.5</v>
       </c>
       <c r="H13">
-        <v>0.00835975470098493</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I13">
-        <v>0.03164024529901507</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -960,37 +957,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>500</v>
       </c>
       <c r="D14">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>250</v>
+        <v>489</v>
       </c>
       <c r="G14">
-        <v>0.5</v>
+        <v>0.022</v>
       </c>
       <c r="H14">
-        <v>0.4561291748584872</v>
+        <v>0.009129762347397428</v>
       </c>
       <c r="I14">
-        <v>0.5438708251415129</v>
+        <v>0.03487023765260257</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -998,37 +995,37 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15">
         <v>500</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G15">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="H15">
-        <v>0.006334649426270291</v>
+        <v>0.004990607908314969</v>
       </c>
       <c r="I15">
-        <v>0.02966535057372971</v>
+        <v>0.02700939209168503</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1036,37 +1033,37 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16">
         <v>500</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>254</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>489</v>
+        <v>246</v>
       </c>
       <c r="G16">
-        <v>0.022</v>
+        <v>0.508</v>
       </c>
       <c r="H16">
-        <v>0.009129762347397428</v>
+        <v>0.4641347906835411</v>
       </c>
       <c r="I16">
-        <v>0.03487023765260257</v>
+        <v>0.5518652093164589</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1074,37 +1071,37 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17">
         <v>500</v>
       </c>
       <c r="D17">
-        <v>247</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>251</v>
+        <v>495</v>
       </c>
       <c r="G17">
-        <v>0.496</v>
+        <v>0.01</v>
       </c>
       <c r="H17">
-        <v>0.4522184111315305</v>
+        <v>0.001269816025738696</v>
       </c>
       <c r="I17">
-        <v>0.5397815888684695</v>
+        <v>0.0187301839742613</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1112,7 +1109,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18">
         <v>500</v>
@@ -1139,10 +1136,10 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1150,37 +1147,37 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19">
         <v>500</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G19">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="H19">
-        <v>0.003256725293618782</v>
+        <v>0.001269816025738698</v>
       </c>
       <c r="I19">
-        <v>0.02274327470638122</v>
+        <v>0.0187301839742613</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1188,37 +1185,37 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20">
         <v>500</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>249</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>496</v>
+        <v>251</v>
       </c>
       <c r="G20">
-        <v>0.008</v>
+        <v>0.498</v>
       </c>
       <c r="H20">
-        <v>0.0001836026626924024</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I20">
-        <v>0.0158163973373076</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1226,37 +1223,37 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21">
         <v>500</v>
       </c>
       <c r="D21">
-        <v>246</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>254</v>
+        <v>499</v>
       </c>
       <c r="G21">
-        <v>0.492</v>
+        <v>0.002</v>
       </c>
       <c r="H21">
-        <v>0.4481347906835411</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>0.5358652093164589</v>
+        <v>0.00592</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1264,113 +1261,113 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22">
         <v>500</v>
       </c>
       <c r="D22">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>252</v>
+        <v>497</v>
       </c>
       <c r="G22">
-        <v>0.496</v>
+        <v>0.005</v>
       </c>
       <c r="H22">
-        <v>0.4521305787473543</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>0.5398694212526457</v>
+        <v>0.01086951637231636</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C23">
         <v>500</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="G23">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>0.00369119620560452</v>
       </c>
       <c r="I23">
-        <v>0.00592</v>
+        <v>0.02430880379439548</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C24">
         <v>500</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>497</v>
+        <v>250</v>
       </c>
       <c r="G24">
-        <v>0.006</v>
+        <v>0.5</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I24">
-        <v>0.0127760190132064</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1378,37 +1375,37 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C25">
         <v>500</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G25">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="H25">
-        <v>0.001269816025738698</v>
+        <v>0.009129762347397428</v>
       </c>
       <c r="I25">
-        <v>0.0187301839742613</v>
+        <v>0.03487023765260257</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1416,7 +1413,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C26">
         <v>500</v>
@@ -1443,10 +1440,10 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1454,7 +1451,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <v>500</v>
@@ -1463,28 +1460,28 @@
         <v>5</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G27">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="H27">
-        <v>0.001269816025738698</v>
+        <v>0.002858010547901262</v>
       </c>
       <c r="I27">
-        <v>0.0187301839742613</v>
+        <v>0.02114198945209874</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1492,37 +1489,37 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C28">
         <v>500</v>
       </c>
       <c r="D28">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>250</v>
+        <v>496</v>
       </c>
       <c r="G28">
-        <v>0.5</v>
+        <v>0.007</v>
       </c>
       <c r="H28">
-        <v>0.4561291748584872</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>0.5438708251415129</v>
+        <v>0.01404724417776211</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1530,37 +1527,37 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C29">
         <v>500</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>250</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>493</v>
+        <v>250</v>
       </c>
       <c r="G29">
-        <v>0.013</v>
+        <v>0.5</v>
       </c>
       <c r="H29">
-        <v>0.003256725293618782</v>
+        <v>0.4561291748584872</v>
       </c>
       <c r="I29">
-        <v>0.02274327470638122</v>
+        <v>0.5438708251415129</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1568,37 +1565,37 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C30">
         <v>500</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>494</v>
+        <v>249</v>
       </c>
       <c r="G30">
-        <v>0.011</v>
+        <v>0.502</v>
       </c>
       <c r="H30">
-        <v>0.002061110791571407</v>
+        <v>0.4581295258264922</v>
       </c>
       <c r="I30">
-        <v>0.01993888920842859</v>
+        <v>0.5458704741735079</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1606,37 +1603,37 @@
         <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C31">
         <v>500</v>
       </c>
       <c r="D31">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G31">
-        <v>0.494</v>
+        <v>0.496</v>
       </c>
       <c r="H31">
-        <v>0.4501323336716188</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I31">
-        <v>0.5378676663283812</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1644,37 +1641,37 @@
         <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C32">
         <v>500</v>
       </c>
       <c r="D32">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
         <v>248</v>
       </c>
       <c r="G32">
-        <v>0.504</v>
+        <v>0.503</v>
       </c>
       <c r="H32">
-        <v>0.4601305787473543</v>
+        <v>0.4591738581138466</v>
       </c>
       <c r="I32">
-        <v>0.5478694212526457</v>
+        <v>0.5468261418861534</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1682,45 +1679,45 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C33">
         <v>500</v>
       </c>
       <c r="D33">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G33">
-        <v>0.494</v>
+        <v>0.496</v>
       </c>
       <c r="H33">
-        <v>0.4501323336716188</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I33">
-        <v>0.5378676663283812</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C34">
         <v>500</v>
@@ -1747,86 +1744,86 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C35">
         <v>500</v>
       </c>
       <c r="D35">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G35">
-        <v>0.5</v>
+        <v>0.495</v>
       </c>
       <c r="H35">
-        <v>0.4561291748584872</v>
+        <v>0.4511752634341045</v>
       </c>
       <c r="I35">
-        <v>0.5438708251415129</v>
+        <v>0.5388247365658955</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C36">
         <v>500</v>
       </c>
       <c r="D36">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G36">
-        <v>0.502</v>
+        <v>0.496</v>
       </c>
       <c r="H36">
-        <v>0.4581295258264922</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I36">
-        <v>0.5458704741735079</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -1834,37 +1831,37 @@
         <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C37">
         <v>500</v>
       </c>
       <c r="D37">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G37">
-        <v>0.49</v>
+        <v>0.492</v>
       </c>
       <c r="H37">
-        <v>0.4461379499011075</v>
+        <v>0.4481347906835411</v>
       </c>
       <c r="I37">
-        <v>0.5338620500988925</v>
+        <v>0.5358652093164589</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -1872,37 +1869,37 @@
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C38">
         <v>500</v>
       </c>
       <c r="D38">
-        <v>246</v>
+        <v>3</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>253</v>
+        <v>497</v>
       </c>
       <c r="G38">
-        <v>0.493</v>
+        <v>0.006</v>
       </c>
       <c r="H38">
-        <v>0.4491773714989907</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>0.5368226285010094</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -1910,37 +1907,37 @@
         <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C39">
         <v>500</v>
       </c>
       <c r="D39">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G39">
-        <v>0.496</v>
+        <v>0.484</v>
       </c>
       <c r="H39">
-        <v>0.4521305787473543</v>
+        <v>0.4401516424741424</v>
       </c>
       <c r="I39">
-        <v>0.5398694212526457</v>
+        <v>0.5278483575258576</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -1948,37 +1945,37 @@
         <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C40">
         <v>500</v>
       </c>
       <c r="D40">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G40">
-        <v>0.496</v>
+        <v>0.494</v>
       </c>
       <c r="H40">
-        <v>0.4521305787473543</v>
+        <v>0.4501323336716188</v>
       </c>
       <c r="I40">
-        <v>0.5398694212526457</v>
+        <v>0.5378676663283812</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -1986,189 +1983,189 @@
         <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C41">
         <v>500</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="H41">
         <v>0</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C42">
         <v>500</v>
       </c>
       <c r="D42">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="F42">
-        <v>257</v>
+        <v>6</v>
       </c>
       <c r="G42">
-        <v>0.486</v>
+        <v>0.743</v>
       </c>
       <c r="H42">
-        <v>0.4421463755939478</v>
+        <v>0.7200440274317749</v>
       </c>
       <c r="I42">
-        <v>0.5298536244060521</v>
+        <v>0.7659559725682251</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C43">
         <v>500</v>
       </c>
       <c r="D43">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>260</v>
+        <v>499</v>
       </c>
       <c r="G43">
-        <v>0.48</v>
+        <v>0.002</v>
       </c>
       <c r="H43">
-        <v>0.4361642855685066</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>0.5238357144314933</v>
+        <v>0.00592</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C44">
         <v>500</v>
       </c>
       <c r="D44">
-        <v>246</v>
+        <v>7</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>254</v>
+        <v>493</v>
       </c>
       <c r="G44">
-        <v>0.492</v>
+        <v>0.014</v>
       </c>
       <c r="H44">
-        <v>0.4481347906835411</v>
+        <v>0.00369119620560452</v>
       </c>
       <c r="I44">
-        <v>0.5358652093164589</v>
+        <v>0.02430880379439548</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C45">
         <v>500</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="G45">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>0.007182857599697888</v>
       </c>
       <c r="I45">
-        <v>0.009538159551912971</v>
+        <v>0.03081714240030211</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2176,37 +2173,37 @@
         <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C46">
         <v>500</v>
       </c>
       <c r="D46">
-        <v>249</v>
+        <v>495</v>
       </c>
       <c r="E46">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>5</v>
       </c>
       <c r="G46">
-        <v>0.744</v>
+        <v>0.99</v>
       </c>
       <c r="H46">
-        <v>0.721210130296067</v>
+        <v>0.9812698160257387</v>
       </c>
       <c r="I46">
-        <v>0.766789869703933</v>
+        <v>0.9987301839742613</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2214,37 +2211,37 @@
         <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C47">
         <v>500</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2252,227 +2249,227 @@
         <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C48">
         <v>500</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G48">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>0.0001836026626924024</v>
       </c>
       <c r="I48">
-        <v>0.009538159551912971</v>
+        <v>0.0158163973373076</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C49">
         <v>500</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
-        <v>499</v>
+        <v>252</v>
       </c>
       <c r="G49">
-        <v>0.002</v>
+        <v>0.496</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I49">
-        <v>0.00592</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C50">
         <v>500</v>
       </c>
       <c r="D50">
-        <v>245</v>
+        <v>6</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>255</v>
+        <v>494</v>
       </c>
       <c r="G50">
-        <v>0.49</v>
+        <v>0.012</v>
       </c>
       <c r="H50">
-        <v>0.4461379499011075</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I50">
-        <v>0.5338620500988924</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C51">
         <v>500</v>
       </c>
       <c r="D51">
-        <v>494</v>
+        <v>249</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>6</v>
+        <v>251</v>
       </c>
       <c r="G51">
-        <v>0.988</v>
+        <v>0.498</v>
       </c>
       <c r="H51">
-        <v>0.9784462275337606</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I51">
-        <v>0.9975537724662393</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C52">
         <v>500</v>
       </c>
       <c r="D52">
+        <v>492</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
         <v>6</v>
       </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>494</v>
-      </c>
       <c r="G52">
-        <v>0.012</v>
+        <v>0.986</v>
       </c>
       <c r="H52">
-        <v>0.002446227533760637</v>
+        <v>0.9760716145080404</v>
       </c>
       <c r="I52">
-        <v>0.02155377246623937</v>
+        <v>0.9959283854919596</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" t="s">
         <v>16</v>
       </c>
-      <c r="B53" t="s">
-        <v>26</v>
-      </c>
       <c r="C53">
         <v>500</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G53">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="H53">
-        <v>0.001269816025738698</v>
+        <v>0</v>
       </c>
       <c r="I53">
-        <v>0.0187301839742613</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2480,37 +2477,37 @@
         <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C54">
         <v>500</v>
       </c>
       <c r="D54">
+        <v>252</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
         <v>248</v>
       </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <v>252</v>
-      </c>
       <c r="G54">
-        <v>0.496</v>
+        <v>0.504</v>
       </c>
       <c r="H54">
-        <v>0.4521305787473543</v>
+        <v>0.4601305787473543</v>
       </c>
       <c r="I54">
-        <v>0.5398694212526457</v>
+        <v>0.5478694212526457</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -2518,37 +2515,37 @@
         <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C55">
         <v>500</v>
       </c>
       <c r="D55">
-        <v>6</v>
+        <v>251</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>494</v>
+        <v>249</v>
       </c>
       <c r="G55">
-        <v>0.012</v>
+        <v>0.502</v>
       </c>
       <c r="H55">
-        <v>0.002446227533760637</v>
+        <v>0.4581295258264922</v>
       </c>
       <c r="I55">
-        <v>0.02155377246623937</v>
+        <v>0.5458704741735079</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -2556,37 +2553,37 @@
         <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C56">
         <v>500</v>
       </c>
       <c r="D56">
-        <v>249</v>
+        <v>6</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>251</v>
+        <v>494</v>
       </c>
       <c r="G56">
-        <v>0.498</v>
+        <v>0.012</v>
       </c>
       <c r="H56">
-        <v>0.4541295258264922</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I56">
-        <v>0.5418704741735079</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -2594,37 +2591,37 @@
         <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C57">
         <v>500</v>
       </c>
       <c r="D57">
-        <v>492</v>
+        <v>6</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>6</v>
+        <v>493</v>
       </c>
       <c r="G57">
-        <v>0.986</v>
+        <v>0.013</v>
       </c>
       <c r="H57">
-        <v>0.9760716145080404</v>
+        <v>0.003256725293618782</v>
       </c>
       <c r="I57">
-        <v>0.9959283854919596</v>
+        <v>0.02274327470638122</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -2632,37 +2629,37 @@
         <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C58">
         <v>500</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>497</v>
+        <v>249</v>
       </c>
       <c r="G58">
-        <v>0.006</v>
+        <v>0.501</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>0.4571731554706159</v>
       </c>
       <c r="I58">
-        <v>0.0127760190132064</v>
+        <v>0.5448268445293841</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -2670,37 +2667,37 @@
         <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C59">
         <v>500</v>
       </c>
       <c r="D59">
-        <v>252</v>
+        <v>491</v>
       </c>
       <c r="E59">
         <v>0</v>
       </c>
       <c r="F59">
-        <v>248</v>
+        <v>9</v>
       </c>
       <c r="G59">
-        <v>0.504</v>
+        <v>0.982</v>
       </c>
       <c r="H59">
-        <v>0.4601305787473543</v>
+        <v>0.9703346494262702</v>
       </c>
       <c r="I59">
-        <v>0.5478694212526457</v>
+        <v>0.9936653505737297</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -2708,37 +2705,37 @@
         <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C60">
         <v>500</v>
       </c>
       <c r="D60">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60">
-        <v>249</v>
+        <v>499</v>
       </c>
       <c r="G60">
-        <v>0.502</v>
+        <v>0.002</v>
       </c>
       <c r="H60">
-        <v>0.4581295258264922</v>
+        <v>0</v>
       </c>
       <c r="I60">
-        <v>0.5458704741735079</v>
+        <v>0.00592</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -2746,197 +2743,197 @@
         <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C61">
         <v>500</v>
       </c>
       <c r="D61">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G61">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="H61">
-        <v>0.002446227533760637</v>
+        <v>0</v>
       </c>
       <c r="I61">
-        <v>0.02155377246623937</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C62">
         <v>500</v>
       </c>
       <c r="D62">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>249</v>
       </c>
       <c r="F62">
-        <v>493</v>
+        <v>251</v>
       </c>
       <c r="G62">
-        <v>0.013</v>
+        <v>0.249</v>
       </c>
       <c r="H62">
-        <v>0.003256725293618782</v>
+        <v>0.2270647629132461</v>
       </c>
       <c r="I62">
-        <v>0.02274327470638122</v>
+        <v>0.2709352370867539</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C63">
         <v>500</v>
       </c>
       <c r="D63">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>249</v>
+        <v>499</v>
       </c>
       <c r="G63">
-        <v>0.501</v>
+        <v>0.002</v>
       </c>
       <c r="H63">
-        <v>0.4571731554706159</v>
+        <v>0</v>
       </c>
       <c r="I63">
-        <v>0.5448268445293841</v>
+        <v>0.00592</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C64">
         <v>500</v>
       </c>
       <c r="D64">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="F64">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G64">
-        <v>0.496</v>
+        <v>0.249</v>
       </c>
       <c r="H64">
-        <v>0.4521305787473543</v>
+        <v>0.2270647629132461</v>
       </c>
       <c r="I64">
-        <v>0.5398694212526457</v>
+        <v>0.2709352370867539</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C65">
         <v>500</v>
       </c>
       <c r="D65">
-        <v>497</v>
+        <v>245</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>255</v>
       </c>
       <c r="G65">
-        <v>0.994</v>
+        <v>0.49</v>
       </c>
       <c r="H65">
-        <v>0.9872239809867935</v>
+        <v>0.4461379499011075</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>0.5338620500988924</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C66">
         <v>500</v>
@@ -2963,314 +2960,314 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C67">
         <v>500</v>
       </c>
       <c r="D67">
-        <v>7</v>
+        <v>248</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>492</v>
+        <v>252</v>
       </c>
       <c r="G67">
-        <v>0.015</v>
+        <v>0.496</v>
       </c>
       <c r="H67">
-        <v>0.004516800347703961</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I67">
-        <v>0.02548319965229604</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B68" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C68">
         <v>500</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>248</v>
       </c>
       <c r="E68">
-        <v>245</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G68">
-        <v>0.255</v>
+        <v>0.497</v>
       </c>
       <c r="H68">
-        <v>0.2322082724285459</v>
+        <v>0.4531738581138466</v>
       </c>
       <c r="I68">
-        <v>0.2777917275714542</v>
+        <v>0.5408261418861534</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B69" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C69">
         <v>500</v>
       </c>
       <c r="D69">
-        <v>7</v>
+        <v>249</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69">
-        <v>493</v>
+        <v>251</v>
       </c>
       <c r="G69">
-        <v>0.014</v>
+        <v>0.498</v>
       </c>
       <c r="H69">
-        <v>0.00369119620560452</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I69">
-        <v>0.02430880379439548</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C70">
         <v>500</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="E70">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G70">
-        <v>0.248</v>
+        <v>0.498</v>
       </c>
       <c r="H70">
-        <v>0.2255449933902551</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I70">
-        <v>0.2704550066097449</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" t="s">
         <v>18</v>
       </c>
-      <c r="B71" t="s">
-        <v>23</v>
-      </c>
       <c r="C71">
         <v>500</v>
       </c>
       <c r="D71">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G71">
-        <v>0.494</v>
+        <v>0.498</v>
       </c>
       <c r="H71">
-        <v>0.4501323336716188</v>
+        <v>0.4541295258264922</v>
       </c>
       <c r="I71">
-        <v>0.5378676663283812</v>
+        <v>0.5418704741735079</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C72">
         <v>500</v>
       </c>
       <c r="D72">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>252</v>
+        <v>500</v>
       </c>
       <c r="G72">
-        <v>0.496</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>0.4521305787473543</v>
+        <v>0</v>
       </c>
       <c r="I72">
-        <v>0.5398694212526457</v>
+        <v>0</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L72" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C73">
         <v>500</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73">
         <v>494</v>
       </c>
       <c r="G73">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="H73">
-        <v>0.002061110791571407</v>
+        <v>0.002446227533760637</v>
       </c>
       <c r="I73">
-        <v>0.01993888920842859</v>
+        <v>0.02155377246623937</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L73" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C74">
         <v>500</v>
       </c>
       <c r="D74">
-        <v>249</v>
+        <v>2</v>
       </c>
       <c r="E74">
         <v>0</v>
       </c>
       <c r="F74">
-        <v>251</v>
+        <v>498</v>
       </c>
       <c r="G74">
-        <v>0.498</v>
+        <v>0.004</v>
       </c>
       <c r="H74">
-        <v>0.4541295258264922</v>
+        <v>0</v>
       </c>
       <c r="I74">
-        <v>0.5418704741735079</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3278,37 +3275,37 @@
         <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C75">
         <v>500</v>
       </c>
       <c r="D75">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G75">
-        <v>0.498</v>
+        <v>0.494</v>
       </c>
       <c r="H75">
-        <v>0.4542173560984032</v>
+        <v>0.4501323336716188</v>
       </c>
       <c r="I75">
-        <v>0.5417826439015968</v>
+        <v>0.5378676663283812</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3316,37 +3313,37 @@
         <v>19</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C76">
         <v>500</v>
       </c>
       <c r="D76">
-        <v>249</v>
+        <v>2</v>
       </c>
       <c r="E76">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>251</v>
+        <v>498</v>
       </c>
       <c r="G76">
-        <v>0.498</v>
+        <v>0.004</v>
       </c>
       <c r="H76">
-        <v>0.4541295258264922</v>
+        <v>0</v>
       </c>
       <c r="I76">
-        <v>0.5418704741735079</v>
+        <v>0.009538159551912971</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3354,1139 +3351,607 @@
         <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C77">
         <v>500</v>
       </c>
       <c r="D77">
-        <v>250</v>
+        <v>3</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77">
-        <v>249</v>
+        <v>497</v>
       </c>
       <c r="G77">
-        <v>0.501</v>
+        <v>0.006</v>
       </c>
       <c r="H77">
-        <v>0.4571731554706159</v>
+        <v>0</v>
       </c>
       <c r="I77">
-        <v>0.5448268445293841</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L77" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C78">
         <v>500</v>
       </c>
       <c r="D78">
-        <v>251</v>
+        <v>497</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="G78">
-        <v>0.502</v>
+        <v>0.994</v>
       </c>
       <c r="H78">
-        <v>0.4581295258264922</v>
+        <v>0.9872239809867935</v>
       </c>
       <c r="I78">
-        <v>0.5458704741735079</v>
+        <v>1</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L78" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C79">
         <v>500</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>500</v>
+        <v>249</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>0.501</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>0.4571731554706159</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>0.5448268445293841</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C80">
         <v>500</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>251</v>
       </c>
       <c r="E80">
         <v>0</v>
       </c>
       <c r="F80">
-        <v>499</v>
+        <v>249</v>
       </c>
       <c r="G80">
-        <v>0.002</v>
+        <v>0.502</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>0.4581295258264922</v>
       </c>
       <c r="I80">
-        <v>0.00592</v>
+        <v>0.5458704741735079</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L80" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B81" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C81">
         <v>500</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>491</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81">
-        <v>499</v>
+        <v>9</v>
       </c>
       <c r="G81">
-        <v>0.002</v>
+        <v>0.982</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>0.9703346494262702</v>
       </c>
       <c r="I81">
-        <v>0.00592</v>
+        <v>0.9936653505737297</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L81" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B82" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C82">
         <v>500</v>
       </c>
       <c r="D82">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="G82">
-        <v>0.488</v>
+        <v>0.499</v>
       </c>
       <c r="H82">
-        <v>0.444141811476063</v>
+        <v>0.4551731554706159</v>
       </c>
       <c r="I82">
-        <v>0.5318581885239371</v>
+        <v>0.5428268445293841</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L82" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C83">
         <v>500</v>
       </c>
       <c r="D83">
-        <v>248</v>
+        <v>3</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83">
-        <v>252</v>
+        <v>496</v>
       </c>
       <c r="G83">
-        <v>0.496</v>
+        <v>0.007</v>
       </c>
       <c r="H83">
-        <v>0.4521305787473543</v>
+        <v>0</v>
       </c>
       <c r="I83">
-        <v>0.5398694212526457</v>
+        <v>0.01404724417776211</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C84">
         <v>500</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>248</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
       <c r="F84">
-        <v>497</v>
+        <v>252</v>
       </c>
       <c r="G84">
-        <v>0.006</v>
+        <v>0.496</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>0.4521305787473543</v>
       </c>
       <c r="I84">
-        <v>0.0127760190132064</v>
+        <v>0.5398694212526457</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B85" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C85">
         <v>500</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>249</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85">
-        <v>498</v>
+        <v>250</v>
       </c>
       <c r="G85">
-        <v>0.004</v>
+        <v>0.499</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>0.4551731554706159</v>
       </c>
       <c r="I85">
-        <v>0.009538159551912971</v>
+        <v>0.5428268445293841</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B86" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C86">
         <v>500</v>
       </c>
       <c r="D86">
+        <v>3</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
         <v>497</v>
       </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86">
-        <v>3</v>
-      </c>
       <c r="G86">
-        <v>0.994</v>
+        <v>0.006</v>
       </c>
       <c r="H86">
-        <v>0.9872239809867935</v>
+        <v>0</v>
       </c>
       <c r="I86">
-        <v>1</v>
+        <v>0.0127760190132064</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C87">
         <v>500</v>
       </c>
       <c r="D87">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G87">
-        <v>0.498</v>
+        <v>0.495</v>
       </c>
       <c r="H87">
-        <v>0.4541295258264922</v>
+        <v>0.4511752634341045</v>
       </c>
       <c r="I87">
-        <v>0.5418704741735079</v>
+        <v>0.5388247365658955</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C88">
         <v>500</v>
       </c>
       <c r="D88">
-        <v>6</v>
+        <v>250</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88">
-        <v>494</v>
+        <v>249</v>
       </c>
       <c r="G88">
-        <v>0.012</v>
+        <v>0.501</v>
       </c>
       <c r="H88">
-        <v>0.002446227533760637</v>
+        <v>0.4571731554706159</v>
       </c>
       <c r="I88">
-        <v>0.02155377246623937</v>
+        <v>0.5448268445293841</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L88" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B89" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C89">
         <v>500</v>
       </c>
       <c r="D89">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F89">
         <v>251</v>
       </c>
       <c r="G89">
-        <v>0.497</v>
+        <v>0.495</v>
       </c>
       <c r="H89">
-        <v>0.4531738581138466</v>
+        <v>0.4512631855540924</v>
       </c>
       <c r="I89">
-        <v>0.5408261418861534</v>
+        <v>0.5387368144459076</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L89" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C90">
         <v>500</v>
       </c>
       <c r="D90">
-        <v>497</v>
+        <v>248</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90">
-        <v>3</v>
+        <v>251</v>
       </c>
       <c r="G90">
-        <v>0.994</v>
+        <v>0.497</v>
       </c>
       <c r="H90">
-        <v>0.9872239809867935</v>
+        <v>0.4531738581138466</v>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>0.5408261418861534</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B91" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C91">
         <v>500</v>
       </c>
       <c r="D91">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E91">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F91">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G91">
         <v>0.5</v>
       </c>
       <c r="H91">
-        <v>0.4563050105365796</v>
+        <v>0.4562170044263437</v>
       </c>
       <c r="I91">
-        <v>0.5436949894634203</v>
+        <v>0.5437829955736563</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B92" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C92">
         <v>500</v>
       </c>
       <c r="D92">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="E92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92">
-        <v>496</v>
+        <v>249</v>
       </c>
       <c r="G92">
-        <v>0.007</v>
+        <v>0.5</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>0.4562170044263437</v>
       </c>
       <c r="I92">
-        <v>0.01404724417776211</v>
+        <v>0.5437829955736563</v>
       </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L92" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12">
-      <c r="A93" t="s">
-        <v>21</v>
-      </c>
-      <c r="B93" t="s">
-        <v>23</v>
-      </c>
-      <c r="C93">
-        <v>500</v>
-      </c>
-      <c r="D93">
-        <v>250</v>
-      </c>
-      <c r="E93">
-        <v>0</v>
-      </c>
-      <c r="F93">
-        <v>250</v>
-      </c>
-      <c r="G93">
-        <v>0.5</v>
-      </c>
-      <c r="H93">
-        <v>0.4561291748584872</v>
-      </c>
-      <c r="I93">
-        <v>0.5438708251415129</v>
-      </c>
-      <c r="J93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K93" t="s">
-        <v>27</v>
-      </c>
-      <c r="L93" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12">
-      <c r="A94" t="s">
-        <v>21</v>
-      </c>
-      <c r="B94" t="s">
-        <v>24</v>
-      </c>
-      <c r="C94">
-        <v>500</v>
-      </c>
-      <c r="D94">
-        <v>251</v>
-      </c>
-      <c r="E94">
-        <v>0</v>
-      </c>
-      <c r="F94">
-        <v>249</v>
-      </c>
-      <c r="G94">
-        <v>0.502</v>
-      </c>
-      <c r="H94">
-        <v>0.4581295258264922</v>
-      </c>
-      <c r="I94">
-        <v>0.5458704741735079</v>
-      </c>
-      <c r="J94" t="b">
-        <v>1</v>
-      </c>
-      <c r="K94" t="s">
-        <v>27</v>
-      </c>
-      <c r="L94" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12">
-      <c r="A95" t="s">
-        <v>21</v>
-      </c>
-      <c r="B95" t="s">
-        <v>25</v>
-      </c>
-      <c r="C95">
-        <v>500</v>
-      </c>
-      <c r="D95">
-        <v>250</v>
-      </c>
-      <c r="E95">
-        <v>0</v>
-      </c>
-      <c r="F95">
-        <v>250</v>
-      </c>
-      <c r="G95">
-        <v>0.5</v>
-      </c>
-      <c r="H95">
-        <v>0.4561291748584872</v>
-      </c>
-      <c r="I95">
-        <v>0.5438708251415129</v>
-      </c>
-      <c r="J95" t="b">
-        <v>1</v>
-      </c>
-      <c r="K95" t="s">
-        <v>27</v>
-      </c>
-      <c r="L95" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12">
-      <c r="A96" t="s">
-        <v>21</v>
-      </c>
-      <c r="B96" t="s">
-        <v>26</v>
-      </c>
-      <c r="C96">
-        <v>500</v>
-      </c>
-      <c r="D96">
-        <v>7</v>
-      </c>
-      <c r="E96">
-        <v>1</v>
-      </c>
-      <c r="F96">
-        <v>492</v>
-      </c>
-      <c r="G96">
-        <v>0.015</v>
-      </c>
-      <c r="H96">
-        <v>0.004516800347703959</v>
-      </c>
-      <c r="I96">
-        <v>0.02548319965229604</v>
-      </c>
-      <c r="J96" t="b">
-        <v>1</v>
-      </c>
-      <c r="K96" t="s">
-        <v>27</v>
-      </c>
-      <c r="L96" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12">
-      <c r="A97" t="s">
-        <v>22</v>
-      </c>
-      <c r="B97" t="s">
-        <v>23</v>
-      </c>
-      <c r="C97">
-        <v>500</v>
-      </c>
-      <c r="D97">
-        <v>251</v>
-      </c>
-      <c r="E97">
-        <v>0</v>
-      </c>
-      <c r="F97">
-        <v>249</v>
-      </c>
-      <c r="G97">
-        <v>0.502</v>
-      </c>
-      <c r="H97">
-        <v>0.4581295258264922</v>
-      </c>
-      <c r="I97">
-        <v>0.5458704741735079</v>
-      </c>
-      <c r="J97" t="b">
-        <v>1</v>
-      </c>
-      <c r="K97" t="s">
-        <v>27</v>
-      </c>
-      <c r="L97" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12">
-      <c r="A98" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98" t="s">
-        <v>24</v>
-      </c>
-      <c r="C98">
-        <v>500</v>
-      </c>
-      <c r="D98">
-        <v>249</v>
-      </c>
-      <c r="E98">
-        <v>1</v>
-      </c>
-      <c r="F98">
-        <v>250</v>
-      </c>
-      <c r="G98">
-        <v>0.499</v>
-      </c>
-      <c r="H98">
-        <v>0.4551731554706159</v>
-      </c>
-      <c r="I98">
-        <v>0.5428268445293841</v>
-      </c>
-      <c r="J98" t="b">
-        <v>1</v>
-      </c>
-      <c r="K98" t="s">
-        <v>27</v>
-      </c>
-      <c r="L98" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12">
-      <c r="A99" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99" t="s">
-        <v>25</v>
-      </c>
-      <c r="C99">
-        <v>500</v>
-      </c>
-      <c r="D99">
-        <v>250</v>
-      </c>
-      <c r="E99">
-        <v>1</v>
-      </c>
-      <c r="F99">
-        <v>249</v>
-      </c>
-      <c r="G99">
-        <v>0.501</v>
-      </c>
-      <c r="H99">
-        <v>0.4571731554706159</v>
-      </c>
-      <c r="I99">
-        <v>0.5448268445293841</v>
-      </c>
-      <c r="J99" t="b">
-        <v>1</v>
-      </c>
-      <c r="K99" t="s">
-        <v>27</v>
-      </c>
-      <c r="L99" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12">
-      <c r="A100" t="s">
-        <v>22</v>
-      </c>
-      <c r="B100" t="s">
-        <v>26</v>
-      </c>
-      <c r="C100">
-        <v>500</v>
-      </c>
-      <c r="D100">
-        <v>246</v>
-      </c>
-      <c r="E100">
-        <v>3</v>
-      </c>
-      <c r="F100">
-        <v>251</v>
-      </c>
-      <c r="G100">
-        <v>0.495</v>
-      </c>
-      <c r="H100">
-        <v>0.4512631855540924</v>
-      </c>
-      <c r="I100">
-        <v>0.5387368144459076</v>
-      </c>
-      <c r="J100" t="b">
-        <v>1</v>
-      </c>
-      <c r="K100" t="s">
-        <v>27</v>
-      </c>
-      <c r="L100" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12">
-      <c r="A101" t="s">
-        <v>23</v>
-      </c>
-      <c r="B101" t="s">
-        <v>24</v>
-      </c>
-      <c r="C101">
-        <v>500</v>
-      </c>
-      <c r="D101">
-        <v>6</v>
-      </c>
-      <c r="E101">
-        <v>1</v>
-      </c>
-      <c r="F101">
-        <v>493</v>
-      </c>
-      <c r="G101">
-        <v>0.013</v>
-      </c>
-      <c r="H101">
-        <v>0.003256725293618782</v>
-      </c>
-      <c r="I101">
-        <v>0.02274327470638122</v>
-      </c>
-      <c r="J101" t="b">
-        <v>1</v>
-      </c>
-      <c r="K101" t="s">
-        <v>27</v>
-      </c>
-      <c r="L101" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12">
-      <c r="A102" t="s">
-        <v>23</v>
-      </c>
-      <c r="B102" t="s">
-        <v>25</v>
-      </c>
-      <c r="C102">
-        <v>500</v>
-      </c>
-      <c r="D102">
-        <v>491</v>
-      </c>
-      <c r="E102">
-        <v>2</v>
-      </c>
-      <c r="F102">
-        <v>7</v>
-      </c>
-      <c r="G102">
-        <v>0.984</v>
-      </c>
-      <c r="H102">
-        <v>0.9733459811791949</v>
-      </c>
-      <c r="I102">
-        <v>0.9946540188208051</v>
-      </c>
-      <c r="J102" t="b">
-        <v>1</v>
-      </c>
-      <c r="K102" t="s">
-        <v>27</v>
-      </c>
-      <c r="L102" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12">
-      <c r="A103" t="s">
-        <v>23</v>
-      </c>
-      <c r="B103" t="s">
-        <v>26</v>
-      </c>
-      <c r="C103">
-        <v>500</v>
-      </c>
-      <c r="D103">
-        <v>251</v>
-      </c>
-      <c r="E103">
-        <v>1</v>
-      </c>
-      <c r="F103">
-        <v>248</v>
-      </c>
-      <c r="G103">
-        <v>0.503</v>
-      </c>
-      <c r="H103">
-        <v>0.4591738581138466</v>
-      </c>
-      <c r="I103">
-        <v>0.5468261418861534</v>
-      </c>
-      <c r="J103" t="b">
-        <v>1</v>
-      </c>
-      <c r="K103" t="s">
-        <v>27</v>
-      </c>
-      <c r="L103" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12">
-      <c r="A104" t="s">
-        <v>24</v>
-      </c>
-      <c r="B104" t="s">
-        <v>25</v>
-      </c>
-      <c r="C104">
-        <v>500</v>
-      </c>
-      <c r="D104">
-        <v>250</v>
-      </c>
-      <c r="E104">
-        <v>1</v>
-      </c>
-      <c r="F104">
-        <v>249</v>
-      </c>
-      <c r="G104">
-        <v>0.501</v>
-      </c>
-      <c r="H104">
-        <v>0.4571731554706159</v>
-      </c>
-      <c r="I104">
-        <v>0.5448268445293841</v>
-      </c>
-      <c r="J104" t="b">
-        <v>1</v>
-      </c>
-      <c r="K104" t="s">
-        <v>27</v>
-      </c>
-      <c r="L104" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12">
-      <c r="A105" t="s">
-        <v>24</v>
-      </c>
-      <c r="B105" t="s">
-        <v>26</v>
-      </c>
-      <c r="C105">
-        <v>500</v>
-      </c>
-      <c r="D105">
-        <v>249</v>
-      </c>
-      <c r="E105">
-        <v>1</v>
-      </c>
-      <c r="F105">
-        <v>250</v>
-      </c>
-      <c r="G105">
-        <v>0.499</v>
-      </c>
-      <c r="H105">
-        <v>0.4551731554706159</v>
-      </c>
-      <c r="I105">
-        <v>0.5428268445293841</v>
-      </c>
-      <c r="J105" t="b">
-        <v>1</v>
-      </c>
-      <c r="K105" t="s">
-        <v>27</v>
-      </c>
-      <c r="L105" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12">
-      <c r="A106" t="s">
-        <v>25</v>
-      </c>
-      <c r="B106" t="s">
-        <v>26</v>
-      </c>
-      <c r="C106">
-        <v>500</v>
-      </c>
-      <c r="D106">
-        <v>250</v>
-      </c>
-      <c r="E106">
-        <v>2</v>
-      </c>
-      <c r="F106">
-        <v>248</v>
-      </c>
-      <c r="G106">
-        <v>0.502</v>
-      </c>
-      <c r="H106">
-        <v>0.4582173560984033</v>
-      </c>
-      <c r="I106">
-        <v>0.5457826439015967</v>
-      </c>
-      <c r="J106" t="b">
-        <v>1</v>
-      </c>
-      <c r="K106" t="s">
-        <v>27</v>
-      </c>
-      <c r="L106" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO_matrix/pairwise_matches.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>A</t>
   </si>
@@ -52,16 +52,13 @@
     <t>opening_noise_k</t>
   </si>
   <si>
-    <t>PPO_1004</t>
-  </si>
-  <si>
-    <t>PPO_859</t>
-  </si>
-  <si>
-    <t>PPO_926</t>
-  </si>
-  <si>
-    <t>PPO_1005</t>
+    <t>PPO_2001</t>
+  </si>
+  <si>
+    <t>PPO_2003</t>
+  </si>
+  <si>
+    <t>PPO_2004</t>
   </si>
   <si>
     <t>center</t>
@@ -425,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -471,75 +468,75 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>500</v>
       </c>
       <c r="D2">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>250</v>
+        <v>496</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.008</v>
       </c>
       <c r="H2">
-        <v>0.4561291748584872</v>
+        <v>0.0001836026626924024</v>
       </c>
       <c r="I2">
-        <v>0.5438708251415129</v>
+        <v>0.0158163973373076</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
         <v>16</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>500</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>251</v>
+        <v>496</v>
       </c>
       <c r="G3">
-        <v>0.251</v>
+        <v>0.008</v>
       </c>
       <c r="H3">
-        <v>0.2287165572578903</v>
+        <v>0.0001836026626924024</v>
       </c>
       <c r="I3">
-        <v>0.2732834427421097</v>
+        <v>0.0158163973373076</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" t="s">
         <v>16</v>
-      </c>
-      <c r="L3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -547,151 +544,37 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>500</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G4">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.0001836026626924024</v>
       </c>
       <c r="I4">
-        <v>0.009538159551912971</v>
+        <v>0.0158163973373076</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" t="s">
         <v>16</v>
-      </c>
-      <c r="L4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5">
-        <v>500</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>493</v>
-      </c>
-      <c r="G5">
-        <v>0.014</v>
-      </c>
-      <c r="H5">
-        <v>0.00369119620560452</v>
-      </c>
-      <c r="I5">
-        <v>0.02430880379439548</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>500</v>
-      </c>
-      <c r="D6">
-        <v>247</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>253</v>
-      </c>
-      <c r="G6">
-        <v>0.494</v>
-      </c>
-      <c r="H6">
-        <v>0.4501323336716188</v>
-      </c>
-      <c r="I6">
-        <v>0.5378676663283812</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>500</v>
-      </c>
-      <c r="D7">
-        <v>492</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>0.985</v>
-      </c>
-      <c r="H7">
-        <v>0.9745168003477039</v>
-      </c>
-      <c r="I7">
-        <v>0.995483199652296</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
